--- a/data/verified_posts_master_sheet.xlsx
+++ b/data/verified_posts_master_sheet.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -442,15 +442,15 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="39" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="45" customWidth="1" min="12" max="12"/>
     <col width="45" customWidth="1" min="13" max="13"/>
-    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="27" customWidth="1" min="17" max="17"/>
@@ -554,27 +554,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IBPS Clerk (CSA) 16th Recruitment 2026</t>
+          <t>Himachal Pradesh High Court Various Post Recruitment 2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ibps-clerk-16th-2026</t>
+          <t>himachal-pradesh-high-court-various-post-2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/ibps-clerk-16th-2026/</t>
+          <t>https://sarkariresult.com.cm/himachal-pradesh-high-court-various-post-2026/</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IBPS Clerk (CSA) 16th</t>
+          <t>Himachal Pradesh High Court Various Post</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11,403 Posts</t>
+          <t>388 Posts</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "20 Years", "Maximum Age": "28 Years", "Answer": "The age limit for IBPS Clerk (CSA) 16th Bharti 2026 is as follows:"}</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "45-50 Years (Category Wise)"}</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>{"For General, OBC, EWS": "₹ 850/-", "For SC, ST, ESM &amp; DESM": "₹ 175/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Computer Literacy": "Operating And Working Knowledge In Computer Systems is Mandatory ie. Candidates Should Have Certificate/ Diploma/ Degree in Computer Operations/ Language/ Should Have Studied Computer / Information Technology As One of the Subjects In The High School/ College/ Institute.", "Question": "What is the official website for IBPS?", "Answer": "The eligibility criteria for the IBPS Clerk (CSA) 16th Vacancy 2026 are as follows on UPSSSC rules."}</t>
+          <t>{"For General": "₹ 450/-", "For OBC, EWS, SC, ST, PH": "₹ 300/- (Only For Himanchal Pradesh Candidates)", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for HP High Court?", "Answer": "The age limit for Himachal Pradesh High Court Various Post Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -639,27 +639,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BPSC School Teacher TRE 4.0 Recruitment 2026</t>
+          <t>RCF Kapurthala Apprentice Recruitment 2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>bpsc-school-teacher-tre-4-0-2026</t>
+          <t>rcf-kapurthala-apprentice-2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/bpsc-school-teacher-tre-4-0-2026/</t>
+          <t>https://sarkariresult.com.cm/rcf-kapurthala-apprentice-2026/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BPSC School Teacher TRE 4.0 Examination 2025</t>
+          <t>RCF Kapurthala Apprentice</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>32,388 Posts</t>
+          <t>734 Posts</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -679,22 +679,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years (Class 9 to 10 &amp; 11 to 12)", "Maximum Age": "37 Years (UR-Male)"}</t>
+          <t>{"Minimum Age": "15 Year", "Maximum Age": "24 Year", "Answer": "The age limit for RCF Kapurthala Apprentice Bharti 2026 is as follows on official website."}</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>{"Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum Age": "42 Years (SC/ ST-Male &amp; Female)", "You May Also Check": "Rajasthan High Court Class VI Employees Peon Recruitment 2025", "Question": "What is the official website for BPSC ?", "Answer": "The official website for BPSC is http://www.bpsc.bih.nic.in/"}</t>
+          <t>{"Merit List": "Notify Later", "For General/ OBC/ EWS": "₹ 100/-", "For SC/ ST/ PH / Female": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for RCF?", "Answer": "Candidates must have passed 10th class, or ITI, from a recognized board/institution."}</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -724,62 +724,62 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RRB Junior Engineer JE Recruitment 2026</t>
+          <t>Railway ICF Apprentice Recruitment 2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>rrb-je-2026</t>
+          <t>railway-icf-apprentice-2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/rrb-je-2026/</t>
+          <t>https://sarkariresult.com.cm/railway-icf-apprentice-2026/</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Railway RRB Junior Engineer JE</t>
+          <t>Railway ICF Trade Apprentice</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4029 Posts</t>
+          <t>1010 Posts</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14 August 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13 September 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15 September 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "33 years", "Answer": "The age limit for RRB Junior Engineer JE Bharti 2026 is as follows:"}</t>
+          <t>{"Age Limit": "15-22 Years (Non-ITI Candidate)", "Answer": "The age limit for Railway ICF Trade Apprentices Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>{"For General / OBC / EWS": "₹ 500/-", "For SC / ST / EBC": "₹ 250/-", "For All Category female": "₹ 250/-", "Fess Refund": "General / OBC : Rs. 400/- will be refunded and Other candidates : Rs. 250/- will be refunded to the bank account after appearing in Stage I Exam.", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for RRB?", "Answer": "Candidates must have passed the Engineering Diploma / Degree, specific qualifications exam from any recognized board in India. For full eligibility details, please check the official notification."}</t>
+          <t>{"For General/ OBC/ EWS Candidates": "₹ 100/-", "For SC/ ST/PH Candidates": "₹ 00/-", "For All Female Category Candidates": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for Railway ICF?", "Answer": "Candidates must have Class 10 (Matric) with 50% marks and an ITI certificate in the relevant trade. For trade-wise eligibility, check the official notification."}</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,27 +809,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SBI Junior Associates Clerk Recruitment 2026</t>
+          <t>GIMS Noida Staff Nurse Recruitment 2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sbi-junior-associates-clerk-2026</t>
+          <t>gims-noida-staff-nurse-2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/sbi-junior-associates-clerk-2026/</t>
+          <t>https://sarkariresult.com.cm/gims-noida-staff-nurse-2026/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SBI Junior Associates Clerk</t>
+          <t>GIMS Noida Staff Nurse</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9124 Posts</t>
+          <t>100 posts</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -849,22 +849,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "20 Years", "Maximum Age": "28 Years", "Answer": "The age limit for SBI Junior Associates Clerk Bharti 2026 is as follows:"}</t>
+          <t>{"For Minimum Age": "21 Years", "For Maximum Age": "40 Years"}</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>{"For OBC": "₹ 750/-", "For SC / ST, PH": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "UPSSSC Cane Supervisor Recruitment 2026", "Question": "What is the official website for SBI?", "Answer": "The eligibility criteria for the SBI Junior Associates Clerk Vacancy 2026 are as follows: Candidates must have a graduation degree in any field from a recognized university."}</t>
+          <t>{"General, OBC, EWS": "₹ 1298/-", "SC, ST": "₹ 944/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "For Degree Holder": "B.Sc Nursing (4-Year) or B.Sc Nursing (Post Basic) (2-Year) from an INC/State Council-recognized University/Institute + Registered as a Nurse &amp; Midwife with the State/Indian Nursing Council.", "For Diploma Holder": "Diploma in General Nursing Midwifery (GNM) from an INC-recognized Board/Council + Registered as Nurse &amp; Midwife with the State/Indian Nursing Council + 2 years’ experience in a minimum 50-bedded hospital after completing the diploma.", "Question": "What is the official website for GIMS Noida?", "Answer": "The eligibility criteria for the GIMS Noida Staff Nurse Vacancy 2026 are as follows on UPSSSC rules."}</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -894,27 +894,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rajasthan Safai Karmchari Recruitment 2026</t>
+          <t>UPSSSC Veterinary Pharmacist Recruitment 2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>rajasthan-safai-karmchari-2026</t>
+          <t>upsssc-veterinary-pharmacist-2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/rajasthan-safai-karmchari-2026/</t>
+          <t>https://sarkariresult.com.cm/upsssc-veterinary-pharmacist-2026/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rajasthan Safai Karmchari</t>
+          <t>UPSSSC Veterinary Pharmacist</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>24,752 posts</t>
+          <t>1308 posts</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -934,22 +934,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years.", "Maximum Age": "40 Years."}</t>
+          <t>{"For Minimum Age": "18 Years", "For Maximum Age": "40 Years"}</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{"General, Other State": "₹ 600/-", "OBC, BC, SC, ST": "₹ 400/-", "Question": "What is the official website for Rajasthan Safai Karmchari?", "Answer": "The official website for Rajasthan Safai Karmchari is https://lsg.rajasthan.gov.in/lsg/#/home/dptHome"}</t>
+          <t>{"General, OBC, EWS": "₹ 25/-", "SC, ST": "₹ 25/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in//default.aspx"}</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -979,27 +979,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UPESSC Principal Recruitment 2026</t>
+          <t>UPSSSC Junior Engineer JE (Agriculture) Recruitment 2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>upessc-principal-2026</t>
+          <t>upsssc-junior-engineer-je-agriculture-2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/upessc-principal-2026/</t>
+          <t>https://sarkariresult.com.cm/upsssc-junior-engineer-je-agriculture-2026/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UPESSC Principal</t>
+          <t>UPSSSC Junior Engineer JE (Agriculture)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>111 Posts</t>
+          <t>134 posts</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1019,22 +1019,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24 September 2026</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "N/A", "Maximum Age": "62 Years"}</t>
+          <t>{"For Minimum Age": "18 Years", "For Maximum Age": "40 Years"}</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"For General, EWS, OBC": "₹ 3000/-", "For SC, ST, PH": "₹ 3000/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "Question": "What is the official website for UPESSC ?", "Answer": "The official website for UPESSC is https://upessc.up.gov.in/"}</t>
+          <t>{"General, OBC, EWS": "₹ 25/-", "SC, ST": "₹ 25/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in//default.aspx"}</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ISRO Assistant &amp; Junior Personal Assistant Recruitment 2026</t>
+          <t>RRVUNL JE, Junior Assistant Recruitment 2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>isro-assistant-2026</t>
+          <t>rrvunl-je-junior-assistant-2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/isro-assistant-2026/</t>
+          <t>https://sarkariresult.com.cm/rrvunl-je-junior-assistant-2026/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ISRO Assistant &amp; Junior Personal Assistant</t>
+          <t>RRVUNL JE, Junior Assistant</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>242 Posts</t>
+          <t>2005 Posts</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1104,22 +1104,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "N/A"}</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years"}</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"General / OBC / EWS": "₹ 500/- (Rs. 400/- refunded after appearing in the Written Test)", "SC / ST / All Female": "₹ 500/- (Rs. 500/- refunded after appearing in the Written Test)", "Maximum Age": "33 Years (SC, ST)", "You May Also Check": "UPSSSC Lower PCS Recruitment 2026", "Question": "What is the official website for ISRO?", "Answer": "The eligibility criteria for the ISRO Assistant &amp; Junior Personal Assistant Vacancy 2026 are as follows on ISRO rules."}</t>
+          <t>{"For General": "₹ 1000/-", "For MBC/ BC / EWS": "₹ 500/-", "For SC/ ST/ PH Candidates": "₹ 500/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Junior Accountant &amp; Junior Assistant/ Commercial Assistant-II": "18-40 Years", "You May Also Check": "SSC CGL Recruitment 2026", "Question": "What is the official website for RRVUNL ?", "Answer": "The official website for RRVUNL is https://energy.rajasthan.gov.in/rrvun/#/pages/sm/department-page/373376/2700"}</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1149,27 +1149,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RPSC Physiotherapist Recruitment 2026</t>
+          <t>UP Anganwadi Bharti Recruitment 2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>rpsc-physiotherapist-2026</t>
+          <t>up-anganwadi-bharti-2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/rpsc-physiotherapist-2026/</t>
+          <t>https://sarkariresult.com.cm/up-anganwadi-bharti-2026/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RPSC Physiotherapist</t>
+          <t>UP Anganwadi Bharti Examination 2025</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20 Posts</t>
+          <t>Various Posts</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1189,22 +1189,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years"}</t>
+          <t>{"For Minimum Age": "18 years", "For Maximum Age": "35 years", "Answer": "The age limit for candidates applying for this recruitment is as per the rules of UP Anganwadi. For detailed age information, please refer to the official notification."}</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"For General, (BC, EBC Creamy Layer) &amp; Other State": "₹ 600/-", "For SC / ST, (OBC, EBC Non Creamy Layer) / PH": "₹ 400/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "RSSB Computer Instructor Recruitment 2026", "Question": "What is the official website for RPSC ?", "Answer": "The official website for RPSC is https://rpsc.rajasthan.gov.in/"}</t>
+          <t>{"Application Start": "November 2025", "Question": "What is the official website of UP Anganwadi? Answer: The official website of UP Anganwadi is https://upanganwadibharti.in/.", "Answer": "The online application for this recruitment started in November 2025."}</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1234,27 +1234,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SKAU Kurukshetra Non Teaching Post Recruitment 2026</t>
+          <t>UPSSSC PET Online Form 2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>skau-non-teaching-2026</t>
+          <t>upsssc-pet-2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/skau-non-teaching-2026/</t>
+          <t>https://sarkariresult.com.cm/upsssc-pet-2026/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SKAU Kurukshetra Non Teaching Post</t>
+          <t>UPSSSC PET</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>60 Posts</t>
+          <t>Various Posts</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1264,32 +1264,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>Update Soon</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "42 Years"}</t>
+          <t>{"For Minimum Age": "18 Years", "For Maximum Age": "40 Years"}</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{"For General / Other State": "₹ 1580/- (For Male)", "For General": "₹ 750/- (For Female Domicile)", "For Haryana Reserve Category": "₹ 375/- (Male &amp; Female)", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "SSC CGL Recruitment 2026", "Question": "What is the official website for SKAU?", "Answer": "The eligibility for SKAU Kurukshetra Non Teaching Post Bharti 2026 is as follows post wise."}</t>
+          <t>{"Application Start": "03 August 2026", "For General, OBC": "₹ 185/-", "For SC, ST": "₹ 95/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website of UPSSSC?", "Answer": "The official website of UPSSSC is https://upsssc.gov.in/."}</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1319,27 +1319,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UPSC EPFO / APFC Recruitment 2026</t>
+          <t>MP High Court Assistant Grade III Recruitment 2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>upsc-epfo-2026</t>
+          <t>mp-high-court-assistant-grade-iii-2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/upsc-epfo-2026/</t>
+          <t>https://sarkariresult.com.cm/mp-high-court-assistant-grade-iii-2026/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UPSC EPFO EO / AO / APFC</t>
+          <t>MP High Court Assistant Grade III</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>80 Posts</t>
+          <t>1174 Posts</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1359,22 +1359,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years (Tentative)", "Maximum Age": "35-40 Years (Category Wise)"}</t>
+          <t>{"Minimum Age": "18 Year", "Maximum Age": "40 – 45 Year"}</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{"For General / OBC / EWS": "₹ 25/-", "For SC / ST": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "You May Also Check": "UPPSC Professor &amp; Assistant Professor Recruitment 2026", "Question": "What is the official website for UPSC?", "Answer": "The official website for UPSC is https://www.upsc.gov.in/"}</t>
+          <t>{"For General/ Other State": "₹ 943.40/-", "For SC/ ST/ OBC/ EWS": "₹ 743.40/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for MPHC?", "Answer": "The eligibility for MP High Court Assistant Grade III Bharti 2026 is as follows post wise."}</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1399,32 +1399,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RESULT</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RPSC Rajasthan Police SI Telecom Final Result 2026</t>
+          <t>MPESB Group 3 Sub Engineer &amp; Other Post Recruitment 2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>rpsc-rajasthan-police-si-telecom-2025</t>
+          <t>mpesb-group-3-sub-engineer-2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/rpsc-rajasthan-police-si-telecom-2025/</t>
+          <t>https://sarkariresult.com.cm/mpesb-group-3-sub-engineer-2026/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RPSC SI Telecom Examination 2025</t>
+          <t>MPESB Group 3 Sub Engineer &amp; Other Post</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>98 Post</t>
+          <t>1040 Posts</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>09 November 2025</t>
+          <t>06 October 2026</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "20 Years", "Maximum Age": "25 Years"}</t>
+          <t>{"Minimum Age": "18 Years"}</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"For General, Other State": "₹ 600/-", "For SC / ST, OBC / BC": "₹ 400/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for RPSC?", "Answer": "The official website for RPSC is https://rpsc.rajasthan.gov.in/"}</t>
+          <t>{"For General / Other State": "Rs. 500/-", "For SC / ST/ OBC": "Rs. 250/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "Maximum Age": "45 Years (SC, ST, OBC, PwBD &amp; All Female)", "You May Also Check": "Rajasthan High Court Stenographer Recruitment 2026", "Question": "What is the official website for MPESB?", "Answer": "Candidates must have a Bachelor’s Degree in any discipline from a university recognized by the Government of India."}</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1484,32 +1484,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RESULT</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NTA SWAYAM Result 2026</t>
+          <t>RSSB Junior Engineer Recruitment 2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>nta-swayam-2026</t>
+          <t>rssb-junior-engineer-2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/nta-swayam-2026/</t>
+          <t>https://sarkariresult.com.cm/rssb-junior-engineer-2026/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NTA SWAYAM</t>
+          <t>RSSB Junior Engineer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Various Posts</t>
+          <t>874 Posts</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "As per rules", "Maximum Age": "As per rules"}</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Answer": "The age limit for RSSB Junior Engineer Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>{"For General": "₹ 750/- (Add Course : ₹ 600/-)", "For OBC, NCL, EWS": "₹ 500/- (Add Course : ₹ 400/-)", "For SC/ ST/PH": "₹ 500/- (Add Course : ₹ 400/-)", "You May Also Check": "CRPF Constable Tradesman Recruitment 2026", "Uttar Pradesh": "Agra, Aligarh, Ayodhya, Bareilly, Etawah, Gorakhpur, Jhansi, Kanpur, Lucknow, Meerut, Moradabad, Orai, Prayagraj, Varanasi, Greater Noida, Lakhimpur, Sitapur, Basti.", "Rajasthan": "Kota, Ajmer, Alwar, Banswara, Barmer, Bharatpur, Bikaner, Chittorgarh, Dungarpur, Jaipur, Jodhpur, Nagaur, Pratapgarh, Sikar, Sriganganagar, Udaipur.", "Question": "What is the official website for NTA SWAYAM?"}</t>
+          <t>{"For General, EWS, OBC (Creamy Layer)": "₹ 600/-", "For EWS, OBC (Non Creamy Layer)": "₹ 400/-", "For SC, ST, PH": "₹ 400/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "BPSC School Teacher TRE 4.0 Recruitment 2026", "Question": "What is the official website for RSSB?", "Answer": "The official website for RSSB is https://rssb.rajasthan.gov.in/"}</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1569,32 +1569,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RESULT</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bihar Police Prohibition Constable Result 2026</t>
+          <t>MPESB Group-2 Sub Group-4 Patwari Recruitment 2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>csbc-bihar-prohibition-constable-2026</t>
+          <t>mpesb-group-2-sub-group-4-patwari-2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/csbc-bihar-prohibition-constable-2026/</t>
+          <t>https://sarkariresult.com.cm/mpesb-group-2-sub-group-4-patwari-2026/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bihar Police CSBC Constable Examination 2025</t>
+          <t>MPESB Group-2 Sub Group-4 Patwari</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4210 Posts</t>
+          <t>2106 Posts</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1614,22 +1614,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>14 – 17 June 2026</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "As per rules", "Maximum Age": "As per rules"}</t>
+          <t>{"Minimum Age": "18 Years", "Answer": "The age limit for MPESB Group-2 Sub Group-4 Patwari Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>{"Payment Mode (Online)": "You can make the payment using the following methods:", "General (Male)": "18 – 23 years", "OBC / EBC (Male)": "18 – 25 years", "OBC / EBC (Female)": "18 – 26 years", "SC / ST (Male &amp; Female)": "18 – 28 years", "You May Also Check": "DSSSB Non-Teaching Various Post Online Form 2025", "Question": "What is the official website for CSBC ?", "Answer": "The notification is generally released in PDF format."}</t>
+          <t>{"For General / Other State": "Rs. 500/-", "For SC / ST/ OBC": "Rs. 250/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "Maximum Age": "45 Years (SC, ST, OBC, PwBD &amp; All Female)", "You May Also Check": "Rajasthan High Court Stenographer Recruitment 2026", "Question": "What is the official website for MPESB?", "Answer": "Candidates must have a Bachelor’s Degree in any discipline from a university recognized by the Government of India."}</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1654,32 +1654,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RESULT</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bihar Police CSBC Constable Operator Result 2026</t>
+          <t>UPPSC Professor &amp; Assistant Professor Recruitment 2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>bihar-police-csbc-constable-operator-2026</t>
+          <t>uppsc-professor-2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/bihar-police-csbc-constable-operator-2026/</t>
+          <t>https://sarkariresult.com.cm/uppsc-professor-2026/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bihar Police CSBC Constable Operator</t>
+          <t>UPPSC Professor &amp; Assistant Professor</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>993 Posts</t>
+          <t>1156 Posts</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1699,22 +1699,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>28 June 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years.", "Maximum Age": "27 Years. (BC, EBC Male)"}</t>
+          <t>{"Minimum Age": "35 Years", "Maximum Age": "55 Years"}</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>{"Payment Mode (Online)": "You can make the payment using the following methods:", "Maximum Age": "30 Years. (SC, ST Male &amp; Female)", "Question": "What is the official website for Bihar Police CSBC ?", "Answer": "The examination date has announced officially by the Central Selection Board of Constable (CSBC) through the official portal."}</t>
+          <t>{"For General / OBC / EWS": "₹ 105/-", "For SC / ST": "₹ 65/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for UPPSC?", "Answer": "The official website for UPPSC is https://uppsc.up.nic.in/"}</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1739,32 +1739,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RESULT</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bihar Police CSBC Constable GD Result 2026</t>
+          <t>Bank Of Baroda LBO Recruitment 2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>bihar-police-csbc-constable-2026</t>
+          <t>2026-bank-of-baroda-lbo-aug26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/bihar-police-csbc-constable-2026/</t>
+          <t>https://sarkariresult.com.cm/2026-bank-of-baroda-lbo-aug26/</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bihar Police CSBC Constable</t>
+          <t>BOB Local Bank Officer LBO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>83 Posts</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1784,22 +1784,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>24 June 2026</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years.", "Maximum Age": "27 Years. (BC, EBC Male)"}</t>
+          <t>{"Minimum Age": "21 Years", "Maximum Age": "30 Years", "Answer": "The age limit for BOB Local Bank Officer LBO Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>{"Payment Mode (Online)": "You can make the payment using the following methods:", "Maximum Age": "30 Years. (SC, ST Male &amp; Female)", "Question": "What is the official website for Bihar Police CSBC ?", "Answer": "The notification is generally released in PDF format."}</t>
+          <t>{"For General, OBC, EWS": "₹ 850/-", "For SC / ST, PwBD/": "₹ 175/-", "For All Female": "₹ 175/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "MP High Court Assistant Grade III Recruitment 2026", "Question": "What is the official website for BOB?", "Answer": "The eligibility for BOB Local Bank Officer LBO Bharti 2026 is as follows post wise."}</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RESULT</t>
+          <t>SYLLABUS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KVS NVS Teaching &amp; Non-Teaching Tier-II Result 2026</t>
+          <t>UPSSSC PET Online Form 2026 Syllabus &amp; Exam Pattern 2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>kvs-nvs-teaching-non-teaching-2026</t>
+          <t>upsssc-pet-2026-syllabus</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/kvs-nvs-teaching-non-teaching-2026/</t>
+          <t>https://sarkariresult.com.cm/upsssc-pet-2026-syllabus/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KVS NVS Teaching &amp; Non-Teaching Examination 2025</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15,762 Posts</t>
+          <t>Exam Syllabus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1859,32 +1859,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>10-11 January 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>{"Assistant Commissioner / Principal / Vice Principal": "-", "General / OBC / EWS": "1700/-", "SC / ST / PH / ESM": "500/-", "SSA / Stenographer / JSA / Lab Attendant / Multi-Tasking Staff": "-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum Age": "27 – 50 Years (Post Wise)", "Answer": "Candidates need their Registration/Application Number and Date of Birth or Password to log in.", "Question": "What is the official website for KVS/NVS?"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1909,67 +1909,67 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RESULT</t>
+          <t>SYLLABUS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UPSSSC VDO 2023 Final Result</t>
+          <t>RRB Junior Engineer JE Recruitment 2026 Syllabus &amp; Exam Pattern 2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>upsssc-vdo-2023</t>
+          <t>rrb-je-2026-syllabus</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/upsssc-vdo-2023/</t>
+          <t>https://sarkariresult.com.cm/rrb-je-2026-syllabus/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UPSSSC VDO (Village Development Officer) Examination 2023</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1468 Post</t>
+          <t>4029 Posts</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>14 August 2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12 June 2023</t>
+          <t>13 September 2026</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12 June 2023</t>
+          <t>13 September 2026</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>27 April 2025</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years", "Maximum Age": "40 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>{"Application Start": "23 May 2023", "General / OBC / EWS": "₹ 25/-", "SC / ST": "₹ 25/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is http://upsssc.gov.in/Default.aspx"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1994,67 +1994,67 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RESULT</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RPSC School Lecturer PGT Result 2026</t>
+          <t>RRB Junior Engineer JE Recruitment 2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>rpsc-1st-grade-teacher-2025</t>
+          <t>rrb-je-2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/rpsc-1st-grade-teacher-2025/</t>
+          <t>https://sarkariresult.com.cm/rrb-je-2026/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RPSC School Lecturer Examination 2025</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3225 Post</t>
+          <t>4029 Posts</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>14 August 2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>13 September 2026</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>13 September 2026</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31 May – 11 June 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years", "Maximum Age": "40 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>{"For General, Other State": "₹ 600/-", "For SC / ST, OBC / BC": "₹ 400/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for RPSC?", "Answer": "The official website for RPSC is https://rpsc.rajasthan.gov.in/news"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2079,32 +2079,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RESULT</t>
+          <t>ADMISSION</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SSC 10+2 CHSL 2025 FRTA Result</t>
+          <t>IIM CAT 2026 Admission Form</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ssc-chsl-2026</t>
+          <t>iim-cat-2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/ssc-chsl-2026/</t>
+          <t>https://sarkariresult.com.cm/iim-cat-2026/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SSC 10+2 CHSL Examination 2025</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3522 Posts</t>
+          <t>Various Seats</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "27 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>{"Tier-I Exam Start": "12 November 2025", "Post Preference Cum Option Form": "19 – 25 June 2026", "For General/ OBC/ EWS": "₹ 100/-", "For SC/ ST/ Female": "₹ 0/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for SSC?", "Answer": "The official website for SSC is https://ssc.gov.in/"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2164,32 +2164,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RESULT</t>
+          <t>SYLLABUS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RSSB Forester Result 2026</t>
+          <t>SSC 10+2 CHSL 2025 FRTA Result Syllabus &amp; Exam Pattern 2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>rssb-forester-2026</t>
+          <t>ssc-chsl-2026-syllabus</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/rssb-forester-2026/</t>
+          <t>https://sarkariresult.com.cm/ssc-chsl-2026-syllabus/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RSSB Forester</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>259 Post</t>
+          <t>3522 Posts</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2209,22 +2209,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>28 June 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>{"For General, EWS, OBC (Creamy Layer)": "₹ 600/-", "For EWS, OBC (Non Creamy Layer)": "₹ 400/-", "For SC, ST, PH": "₹ 400/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum Age": "40 Years (Forester)", "Question": "What is the official website for RSSB?", "Answer": "The official website for RSSB is https://rssb.rajasthan.gov.in/"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2249,32 +2249,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ADMIT-CARD</t>
+          <t>SYLLABUS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Railway RRB Group D Admit Card 2026</t>
+          <t>Bihar Police Prohibition Constable Result 2026 Syllabus &amp; Exam Pattern 2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>railway-rrb-group-d-level-1-recruitment-2026-online</t>
+          <t>csbc-bihar-prohibition-constable-2026-syllabus</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/railway-rrb-group-d-level-1-recruitment-2026-online/</t>
+          <t>https://sarkariresult.com.cm/csbc-bihar-prohibition-constable-2026-syllabus/</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Railway RRB Group-D (Level-1)</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22,195 Posts</t>
+          <t>4210 Posts</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2299,17 +2299,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "33 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>{"Revised Tentative Exam Schedule": "03, 06, 09, 17, 21 &amp; 25 August 2026", "For General, OBC,": "₹ 400/-", "For SC/ ST/ EBC / Female / Transgender": "₹ 250/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "UPSSSC Lekhpal Recruitment 2026", "Question": "What is the official website for RRB?", "Answer": "The Railway RRB Group-D CBT-I Examination 2026 will be held from 03 August to 21 August 2026 in multiple shifts across the country."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2334,37 +2334,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ADMIT-CARD</t>
+          <t>SYLLABUS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IBPS SO XVI Pre Admit Card 2026</t>
+          <t>RPSC Rajasthan Police SI Telecom Final Result 2026 Syllabus &amp; Exam Pattern 2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ibps-so-xvi-2026</t>
+          <t>rpsc-rajasthan-police-si-telecom-2025-syllabus</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/ibps-so-xvi-2026/</t>
+          <t>https://sarkariresult.com.cm/rpsc-rajasthan-police-si-telecom-2025-syllabus/</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IBPS SO XVI</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1035 posts</t>
+          <t>98 Post</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2384,17 +2384,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "20 Years", "Maximum Age": "30 Years", "Answer": "The age limit for IBPS SO XVI Bharti 2026 is as follows:"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>{"For General, OBC, EWS": "Rs 850/-", "For SC, ST, PH": "Rs 175/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for IBPS?", "Answer": "The online application for this recruitment has started on 01 July 2026."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2419,32 +2419,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ADMIT-CARD</t>
+          <t>SYLLABUS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BSNL Junior Telecom Officer JTO Admit Card 2026</t>
+          <t>Rajasthan Safai Karmchari Recruitment 2026 Syllabus &amp; Exam Pattern 2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>bsnl-junior-telecom-officer-jto-2026</t>
+          <t>rajasthan-safai-karmchari-2026-syllabus</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/bsnl-junior-telecom-officer-jto-2026/</t>
+          <t>https://sarkariresult.com.cm/rajasthan-safai-karmchari-2026-syllabus/</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BSNL Junior Telecom Officer JTO</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>100 Posts</t>
+          <t>24,752 posts</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2464,22 +2464,22 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "20 Years", "Maximum Age": "30 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>{"Exam City Details": "12 August 2026", "For General/ OBC/ EWS": "₹ 2000/-", "For SC/ ST/ PH": "₹ 1000/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for BSNL?", "Answer": "Candidates should regularly check the official BSNL website for the latest exam schedule and related notifications."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2504,32 +2504,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ADMIT-CARD</t>
+          <t>SYLLABUS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NICL Assistant Pre Admit Card 2026</t>
+          <t>UPSC EPFO / APFC Recruitment 2026 Syllabus &amp; Exam Pattern 2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>nicl-assistant-2026</t>
+          <t>upsc-epfo-2026-syllabus</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/nicl-assistant-2026/</t>
+          <t>https://sarkariresult.com.cm/upsc-epfo-2026-syllabus/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Insurance NICL Assistant</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>500 Posts</t>
+          <t>80 Posts</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2554,17 +2554,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years", "Maximum Age": "30 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>{"For General, OBC, EWS": "₹ 850/-", "For SC, ST, PWD": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for NICL?"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2589,32 +2589,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ADMIT-CARD</t>
+          <t>SYLLABUS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BPSSC Bihar Police Havildar Instructor PET Admit Card 2026</t>
+          <t>IBPS Clerk (CSA) 16th Recruitment 2026 Syllabus &amp; Exam Pattern 2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>bpssc-havildar-instructor-2026</t>
+          <t>ibps-clerk-16th-2026-syllabus</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/bpssc-havildar-instructor-2026/</t>
+          <t>https://sarkariresult.com.cm/ibps-clerk-16th-2026-syllabus/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BPSSC Havildar Instructor</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>122 Posts</t>
+          <t>11,403 Posts</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2634,22 +2634,22 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>29 July 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years. (All Category)"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>{"Maximum Age": "42 Years. (SC / ST Male &amp; Female)", "Question": "What is the official website for BPSSC ?", "Answer": "The official website for BPSSC is https://bpssc.bihar.gov.in/"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2674,32 +2674,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ADMIT-CARD</t>
+          <t>SYLLABUS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UPSSSC Lower PCS Admit Card 2026</t>
+          <t>SBI Junior Associates Clerk Recruitment 2026 Syllabus &amp; Exam Pattern 2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>upsssc-lower-pcs-2026</t>
+          <t>sbi-junior-associates-clerk-2026-syllabus</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/upsssc-lower-pcs-2026/</t>
+          <t>https://sarkariresult.com.cm/sbi-junior-associates-clerk-2026-syllabus/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UPSSSC Lower PCS</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2587 Posts</t>
+          <t>9124 Posts</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years", "Maximum Age": "40 Years."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>{"Exam City Details": "14 August 2026", "General, OBC, EWS": "₹ 25/-", "SC / ST": "₹ 25/-", "The UPSSSC Lower PCS Main Exam 2026 is scheduled for 23 August 2026, from 10": "00 AM to 12:00 PM.", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in/"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2759,32 +2759,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ADMIT-CARD</t>
+          <t>SYLLABUS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BSF HCM &amp; ASI Steno Admit Card 2026</t>
+          <t>BPSC School Teacher TRE 4.0 Recruitment 2026 Syllabus &amp; Exam Pattern 2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>bsf-hcm-asi-steno-2025</t>
+          <t>bpsc-school-teacher-tre-4-0-2026-syllabus</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/bsf-hcm-asi-steno-2025/</t>
+          <t>https://sarkariresult.com.cm/bpsc-school-teacher-tre-4-0-2026-syllabus/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BSF ASI Stenographer and Head Constable Examination 2025</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2 posts</t>
+          <t>32,388 Posts</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2804,22 +2804,22 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "25 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>{"For General, OBC, EWS": "₹ 147.25/-", "For SC / ST, PWD": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "NIACL Assistants Online Form 2024", "Question": "What is the official website for BSF?", "Answer": "The BSF HCM &amp; ASI Steno written examination is expected to be conducted in 2026 as per the schedule released by the Border Security Force (BSF). Candidates should regularly check the official website for updates."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2844,32 +2844,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ADMIT-CARD</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cotton Corporation of India CCI Various Post Exam City Details 2026</t>
+          <t>IBPS Clerk (CSA) 16th Recruitment 2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>cci-various-post-2026</t>
+          <t>ibps-clerk-16th-2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/cci-various-post-2026/</t>
+          <t>https://sarkariresult.com.cm/ibps-clerk-16th-2026/</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cotton Corporation of India CCIL Various Post</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>148 Posts</t>
+          <t>11,403 Posts</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2889,22 +2889,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "As per rules", "Maximum Age": "As per rules"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>{"Exam City Details": "18 August 2026 Available Now", "For General/ OBC/ EWS": "₹ 1770/-", "For SC/ ST/ PH": "₹ 590/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum. Age": "32 Years (For Assistant Manager)", "You May Also Check": "BPSSC Bihar Police Sub Inspector SI Recruitment 2026", "Question": "What is the official website for CCIL?", "Answer": "Candidates generally need their Registration Number/User ID and Password to access the exam city information."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2929,32 +2929,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ADMIT-CARD</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NTA AIAPGET Admit Card 2026</t>
+          <t>UPSC EPFO / APFC Recruitment 2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>nta-aiapget-2026</t>
+          <t>upsc-epfo-2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/nta-aiapget-2026/</t>
+          <t>https://sarkariresult.com.cm/upsc-epfo-2026/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NTA AIAPGET Admissions</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Various Posts</t>
+          <t>80 Posts</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2974,22 +2974,22 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "As per rules", "Maximum Age": "As per rules"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>{"Correction Date": "01 – 02 August 2026", "Exam City Details": "13 August 2026", "For General": "₹ 2700/-", "For EWS / OBC NCL": "₹ 2450/-", "For SC / ST / PH": "₹ 1800/-", "Rajasthan": "Bikaner, Jaipur, Jodhpur, Kota, Udaipur", "Question": "What is the official website for AIAPGET?", "Answer": "Candidates generally need their Application Number and Date of Birth to access the city intimation slip."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3014,32 +3014,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ADMIT-CARD</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NBEMS Group A, B &amp; C Various Post Exam City Details 2026</t>
+          <t>SKAU Kurukshetra Non Teaching Post Recruitment 2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>nbems-various-post-2026</t>
+          <t>skau-non-teaching-2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/nbems-various-post-2026/</t>
+          <t>https://sarkariresult.com.cm/skau-non-teaching-2026/</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NBEMS Group A, B &amp; C Various Post</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>53 Posts</t>
+          <t>60 Posts</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3059,22 +3059,22 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>05 – 06 September 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>{"Exam City Details": "18 August 2026 Available Now", "For General, OBC, EWS": "₹ 1500/- (+18% GST Extra)", "For SC / ST / PH / Female": "₹ 00/-", "Maximum Age": "27 – 35 Years. (Post Wise)", "Question": "What is the official website for NBEMS?", "Answer": "The slip generally provides details about the allotted examination city and examination-related information."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3099,32 +3099,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ANSWER-KEY</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UPSSSC BCG Technician Final Answer Key 2026</t>
+          <t>RPSC Physiotherapist Recruitment 2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>upsssc-bcg-technician-2024</t>
+          <t>rpsc-physiotherapist-2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/upsssc-bcg-technician-2024/</t>
+          <t>https://sarkariresult.com.cm/rpsc-physiotherapist-2026/</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UPSSSC BCG Technician Examination 2024</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>255 Posts</t>
+          <t>20 Posts</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3144,22 +3144,22 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years", "Maximum Age": "40 Years."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>{"General, OBC, EWS": "₹ 25/-", "SC / ST": "₹ 25/-", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in/"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ANSWER-KEY</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UPSSSC UP Pollution Control Board Various Post Final Answer Key 2026</t>
+          <t>ISRO Assistant &amp; Junior Personal Assistant Recruitment 2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>upsssc-up-pollution-control-board-2026</t>
+          <t>isro-assistant-2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/upsssc-up-pollution-control-board-2026/</t>
+          <t>https://sarkariresult.com.cm/isro-assistant-2026/</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UPSSSC UP Pollution Control Board Various Post Final Answer Key 2026</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>115 Posts</t>
+          <t>242 Posts</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3229,22 +3229,22 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>29 June 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years", "Maximum Age": "40 Years."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>{"General, OBC, EWS": "₹ 25/-", "SC / ST": "₹ 25/-", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in/"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3269,32 +3269,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ANSWER-KEY</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UPSSSC Pharmacist Final Answer Key 2026</t>
+          <t>UPESSC Principal Recruitment 2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>upsssc-pharmacist-2026</t>
+          <t>upessc-principal-2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/upsssc-pharmacist-2026/</t>
+          <t>https://sarkariresult.com.cm/upessc-principal-2026/</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UPSSSC Pharmacist</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>560 Posts</t>
+          <t>111 Posts</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>29 June 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>{"General, OBC, EWS": "₹ 25/-", "SC / ST": "₹ 25/-", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in/"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3354,32 +3354,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ANSWER-KEY</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NTA ICAR AIEEA PG Ph.D Answer Key 2026</t>
+          <t>Rajasthan Safai Karmchari Recruitment 2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>nta-icar-aieea-pg-and-phd-2026</t>
+          <t>rajasthan-safai-karmchari-2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/nta-icar-aieea-pg-and-phd-2026/</t>
+          <t>https://sarkariresult.com.cm/rajasthan-safai-karmchari-2026/</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NTA ICAR AIEEA PG and PHd</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026 Post</t>
+          <t>24,752 posts</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3399,22 +3399,22 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>04 July 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "20 Years (For PHd)"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>{"For General": "₹ 2000/-", "For OBC / EWS": "₹ 1255/-", "For SC / ST / PH": "₹ 1075/-", "For EWS / OBC": "₹ 1955/-", "Eligible subjects include": "Plant Biotechnology, Plant Science, Physical Science, Entomology and Nematology, Agronomy, Social Science, Statistical Science, Horticulture, Forestry, Agriculture and Engineering, Water Science and Technology, Home Science, Animal Biotechnology, Veterinary Science, Animal Science, Fisheries Science, Dairy Science, Dairy Technology, Food Science Technology, and Agri Business Management.", "Eligible disciplines include": "Crop Sciences I, II, and III; Horticulture; Veterinary and Animal Science I, II, and III; Dairy Science; Dairy Technology and Food Technology; Agricultural Engineering and Technology; Home Science; Fishery Science; Natural Science Management I and II; Agricultural Economics and Agribusiness Management; Agricultural Extension; and Agricultural Statistics.", "Question": "What is the official website for NTA?"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3439,32 +3439,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ANSWER-KEY</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NTA CSIR UGC NET June Answer Key 2026</t>
+          <t>SBI Junior Associates Clerk Recruitment 2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>nta-csir-ugc-net-june-2026</t>
+          <t>sbi-junior-associates-clerk-2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/nta-csir-ugc-net-june-2026/</t>
+          <t>https://sarkariresult.com.cm/sbi-junior-associates-clerk-2026/</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NTA CSIR UGC NET June</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Various Posts</t>
+          <t>9124 Posts</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3484,22 +3484,22 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17 – 18 July 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>{"For JRF": "Maximum Age : 30 Year", "For NET": "No Age Limit"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{"For General": "₹ 1150/-", "For OBC, EWS": "₹ 600/-", "For SC/ ST/PH": "₹ 325/-", "Answer": "Candidates need their Registration Number or Mobile Number, Password/Date of Birth, and Captcha Code to download the anwer key.", "Question": "What is the official website for NTA?"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3524,32 +3524,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ANSWER-KEY</t>
+          <t>LATEST-JOBS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bihar BPSC APO Answer Key 2026</t>
+          <t>BPSC School Teacher TRE 4.0 Recruitment 2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>bpsc-apo-2026</t>
+          <t>bpsc-school-teacher-tre-4-0-2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/bpsc-apo-2026/</t>
+          <t>https://sarkariresult.com.cm/bpsc-school-teacher-tre-4-0-2026/</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bihar BPSC APO</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>300 Posts</t>
+          <t>32,388 Posts</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3569,22 +3569,22 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>15 July 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years", "Maximum Age": "37 Years (UR Male)"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>{"Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum Age": "42 Years (SC/ ST-Male &amp; Female)", "Question": "What is the official website for Bihar BPSC?", "Answer": "The official website for Bihar BPSC is https://bpsc.bihar.gov.in/"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ANSWER-KEY</t>
+          <t>ADMISSION</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UPSSSC Agriculture Technical Assistant Group-C Answer Key 2026</t>
+          <t>AIBE 22th Online Form 2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>upsssc-agriculture-technical-assistant-group-c-2026</t>
+          <t>2026-aibe-22th-aug26</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/upsssc-agriculture-technical-assistant-group-c-2026/</t>
+          <t>https://sarkariresult.com.cm/2026-aibe-22th-aug26/</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UPSSSC Agriculture Technical Assistant Group-C</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2759 Posts</t>
+          <t>Various Seats</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3654,22 +3654,22 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>09 August 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years", "Maximum Age": "40 Years."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>{"General, OBC, EWS": "₹ 25/-", "SC / ST": "₹ 25/-", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in/"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3694,32 +3694,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ANSWER-KEY</t>
+          <t>ADMISSION</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Delhi DSSSB July Answer Key 2026</t>
+          <t>UP Scholarship Online Form 2026-27</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>dsssb-various-post-2026</t>
+          <t>up-scholarship-2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/dsssb-various-post-2026/</t>
+          <t>https://sarkariresult.com.cm/up-scholarship-2026/</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Delhi DSSSB Sub Station</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Various Posts</t>
+          <t>Various Seats</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3739,22 +3739,22 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>01 – 25 July 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "27 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>{"Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "If login is required, enter": "Registration / Application Number Date of Birth / Password"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3779,32 +3779,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ANSWER-KEY</t>
+          <t>ADMISSION</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AFCAT 02/2026 Answer Key</t>
+          <t>Bihar BSEB DElEd Common Application Form 2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>afcat-02-2026</t>
+          <t>bihar-bseb-deled-2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/afcat-02-2026/</t>
+          <t>https://sarkariresult.com.cm/bihar-bseb-deled-2026/</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Indian Air Force AFCAT 02/2026 Online Form</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>142 Posts</t>
+          <t>Various Seats</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3824,22 +3824,22 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>08 August 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "20 Years (For Ground Duty Technical / Non Technical Candidates)", "Maximum Age": "26 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>{"All Category Candidates": "Rs. 550/- (+18% GST)", "Payment Mode (Online)": "You can make the payment using the following methods:", "Aeronautical Engineering Mechanical": "Candidates with Minimum 60% Marks Each in Physics and Mathematics at 10+2 Level and 4 Year Engineering / Technology Degree in Mechanical Engineering, Industrial Engineering, Aeronautical Engineering or Equivalent Degree.", "Height Male": "157.5 CMS | Female : 152 CM", "You May Also Check": "CRPF Constable Tradesman Recruitment 2026", "Question": "What is the official website for AFCAT?", "Answer": "The AFCAT 02/2026 Batch Examination 2026 will be held from 08 August 2026."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3864,32 +3864,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ANSWER-KEY</t>
+          <t>ADMISSION</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JSSC Field Worker Answer Key 2026</t>
+          <t>Bihar STET Online Form 2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jssc-field-worker-2024</t>
+          <t>bihar-stet-2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/jssc-field-worker-2024/</t>
+          <t>https://sarkariresult.com.cm/bihar-stet-2026/</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>JSSC Field Worker Examination 2024</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>510 Posts</t>
+          <t>Various Seats</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3909,22 +3909,22 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>19 July 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "37 Years (EBC-I, BC-II-Male)"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>{"For General, EBC, EWS, BC": "₹ 100/-", "For SC / ST Of Jharkhand": "₹ 50/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum Age": "40 Years (SC/ ST-Male &amp; Female)", "Question": "What is the official website for JSSC?", "Answer": "The official website for JSSC is http://jssc.nic.in/."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3954,22 +3954,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IIT JAM Admission Form 2026</t>
+          <t>IIT GATE 2027 Admission Form</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>iit-jam-2027</t>
+          <t>iit-gate-2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/iit-jam-2027/</t>
+          <t>https://sarkariresult.com.cm/iit-gate-2027/</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3984,32 +3984,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12 October 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>12 October 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>14 February 2027</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "As per rules", "Maximum Age": "As per rules"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>{"Application Start": "05 September 2026", "General/ OBC/ EWS Candidates": "₹ 2700/-", "SC/ ST Candidates": "₹ 1350/-", "PH/ Female Candidates": "₹ 1350/-", "Payment Mode (Online)": "You can make the payment using the following methods:"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4034,32 +4034,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ADMISSION</t>
+          <t>ANSWER-KEY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IIT GATE 2027 Admission Form</t>
+          <t>JSSC Field Worker Answer Key 2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>iit-gate-2027</t>
+          <t>jssc-field-worker-2024</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/iit-gate-2027/</t>
+          <t>https://sarkariresult.com.cm/jssc-field-worker-2024/</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>IIT GATE 2027 Admissions Examination</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>510 Posts</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4079,22 +4079,22 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>06, 07, 13, 14, 20 &amp; 21 February 2027</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>{"Maximum Age": "N/A", "Answer": "The age limit for IIT GATE 2027 Online Form is as Follows o official notification."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>{"General/ OBC/ EWS Candidates": "₹ 2500/-", "SC/ ST/ PH Candidates": "₹ 1500/-", "All Female Candidates": "₹ 1500/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for IIT GATE?", "Answer": "The online application for this recruitment will start on 27 August 2026."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4119,32 +4119,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ADMISSION</t>
+          <t>ANSWER-KEY</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CLAT Admission Form 2026</t>
+          <t>AFCAT 02/2026 Answer Key</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>clat-2026</t>
+          <t>afcat-02-2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/clat-2026/</t>
+          <t>https://sarkariresult.com.cm/afcat-02-2026/</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CLAT Admissions</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>142 Posts</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4154,32 +4154,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>31 October 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>31 October 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>06 December 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>{"Maximum Age": "N/A", "Answer": "The age limit for candidates applying for this exam is as per the CLAT rules. For detailed age-related information, refer to the official notification."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>{"General, OBC,": "₹ 4000/-", "SC, ST": "₹ 3500/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Post Graduate": "Passed LLB Degree with Minimum 55% Marks of Any Recognized university in India", "Question": "What is the official website of CLAT?", "Answer": "Candidates must have UG &amp; PG from any recognized board in India. For detailed course-wise eligibility, refer to the official notification."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4204,32 +4204,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ADMISSION</t>
+          <t>ANSWER-KEY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IIM CAT 2026 Admission Form</t>
+          <t>Delhi DSSSB July Answer Key 2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>iim-cat-2026</t>
+          <t>dsssb-various-post-2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/iim-cat-2026/</t>
+          <t>https://sarkariresult.com.cm/dsssb-various-post-2026/</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>IIM CAT Admissions</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>Various Posts</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4239,32 +4239,32 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>15 September 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>15 September 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>29 November 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>{"Maximum Age": "N/A", "Answer": "The age limit for candidates applying for this exam is as per the IIM CAT rules. For detailed age-related information, refer to the official notification."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>{"General, OBC,": "₹ 2700/-", "SC, ST, PWD": "₹ 1350/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "MPESB Group 4 Various Post Online Form 2025", "Question": "What is the official website of IIM CAT?", "Answer": "Candidates must have passed Graduate from any recognized board in India. For detailed course-wise eligibility, refer to the official notification."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4289,32 +4289,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ADMISSION</t>
+          <t>ANSWER-KEY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bihar STET Online Form 2026</t>
+          <t>UPSSSC Agriculture Technical Assistant Group-C Answer Key 2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>bihar-stet-2026</t>
+          <t>upsssc-agriculture-technical-assistant-group-c-2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/bihar-stet-2026/</t>
+          <t>https://sarkariresult.com.cm/upsssc-agriculture-technical-assistant-group-c-2026/</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bihar STET</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>2759 Posts</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4334,22 +4334,22 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years", "Maximum Age": "37 Years (Male)"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>{"For General/ EWS/ BC/ EBC": "₹ 1440/-", "For Other State (All Category)": "₹ 1440/-", "For SC/ ST/ PWD": "₹ 1140/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum Age": "42 Years (SC/ ST-Male &amp; Female)", "Question": "What is the official website for Bihar BSEB?", "Answer": "The official website for Bihar BSEB is https://bsebstet.org/"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4374,47 +4374,47 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ADMISSION</t>
+          <t>ANSWER-KEY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UP DELEd Online Counselling 2026</t>
+          <t>Bihar BPSC APO Answer Key 2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>up-deled-2026</t>
+          <t>bpsc-apo-2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://sarkariresult.com.cm/bpsc-apo-2026/</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UP DELEd</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>300 Posts</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>15 June 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>03 August 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>04 August 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4424,17 +4424,17 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>{"Maximum Age": "35 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>{"For General/ OBC Candidates": "₹ 700/-", "For SC/ ST Candidates": "₹ 500/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "Question": "What is the official website Of UP DELEd?", "Answer": "The age of the candidates applying for this recruitment as per UP DELEd rules, see the post wise age information in the official information."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ADMISSION</t>
+          <t>ANSWER-KEY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NEET UG Online Counselling 2026</t>
+          <t>NTA CSIR UGC NET June Answer Key 2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>nta-neet-ug-2026</t>
+          <t>nta-csir-ugc-net-june-2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/nta-neet-ug-2026/</t>
+          <t>https://sarkariresult.com.cm/nta-csir-ugc-net-june-2026/</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NTA NEET UG</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>Various Posts</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4494,32 +4494,32 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>11 March 2026 (Extended)</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>11 March 2026 (Extended)</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>03 May 2026 – Exam Cancelled</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "17 Years", "Maximum Age": "N/A"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>{"Fee Refund": "22 – 27 May 2026", "For General": "Rs. 1700/-", "For EWS, OBC": "Rs. 1600/-", "For SC, ST": "Rs. 1000/-", "Note": "Processing &amp; GST Charge Are To be Paid by the Candidate, as Applicable.", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Answer": "Visit the official NEET website, log in using your Application Number and Password or Date of Birth, and download your scorecard.", "Question": "What is the official website of NTA NEET?"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ADMISSION</t>
+          <t>ANSWER-KEY</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bihar BSEB DElEd Common Application Form 2026</t>
+          <t>NTA ICAR AIEEA PG Ph.D Answer Key 2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>bihar-bseb-deled-2026</t>
+          <t>nta-icar-aieea-pg-and-phd-2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/bihar-bseb-deled-2026/</t>
+          <t>https://sarkariresult.com.cm/nta-icar-aieea-pg-and-phd-2026/</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BSEB Bihar DELED</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>2026 Post</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4589,22 +4589,22 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>08 – 22 June 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "17 Years", "Maximum Age": "NA Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>{"CAF Date": "10 – 16 August 2026", "For General, EBC, EWS, BC": "₹ 960/-", "For SC / ST, Divyang": "₹ 760/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "UPSC CDS-I Recruitment 2026", "Enter your": "Registration Number / Application Number Password / Date of Birth Captcha Code", "Answer": "Registration Number / Application Number", "Question": "What is the official website for BSEB?"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4629,32 +4629,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ADMISSION</t>
+          <t>ANSWER-KEY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UP Scholarship Online Form 2026-27</t>
+          <t>UPSSSC Pharmacist Final Answer Key 2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>up-scholarship-2026</t>
+          <t>upsssc-pharmacist-2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-scholarship-2026/</t>
+          <t>https://sarkariresult.com.cm/upsssc-pharmacist-2026/</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UP Scholarship Scheme 2025-26</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>560 Posts</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4679,17 +4679,17 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "As per rules", "Maximum Age": "As per rules"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>{"Send Scholarship in Bank Account Date": "January 2027"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4714,32 +4714,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ADMISSION</t>
+          <t>ANSWER-KEY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AIBE 22th Online Form 2026</t>
+          <t>UPSSSC UP Pollution Control Board Various Post Final Answer Key 2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-aibe-22th-aug26</t>
+          <t>upsssc-up-pollution-control-board-2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/2026-aibe-22th-aug26/</t>
+          <t>https://sarkariresult.com.cm/upsssc-up-pollution-control-board-2026/</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AIBE 22th</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>115 Posts</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4759,22 +4759,22 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>29 November 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>{"AIBE 22th Notification 2026": "Age Limit", "Answer": "The age limit for AIBE 22th Form is as Follows o official notification."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>{"For General, EWS, OBC": "₹ 3500/-", "For SC, ST, PwBD": "₹ 2500/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "Bihar Police CSBC Constable Recruitment 2026", "Question": "What is the official website for AIBE 22th ?", "Answer": "The online application for this recruitment has started on 19 August 2026."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4799,67 +4799,67 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SYLLABUS</t>
+          <t>ANSWER-KEY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RRB Junior Engineer JE Recruitment 2026 Syllabus &amp; Exam Pattern 2026</t>
+          <t>UPSSSC BCG Technician Final Answer Key 2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>rrb-je-2026-syllabus</t>
+          <t>upsssc-bcg-technician-2024</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/rrb-je-2026/</t>
+          <t>https://sarkariresult.com.cm/upsssc-bcg-technician-2024/</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Railway RRB Junior Engineer JE</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4029 Posts</t>
+          <t>255 Posts</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>14 August 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>13 September 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>15 September 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "33 years", "Answer": "The age limit for RRB Junior Engineer JE Bharti 2026 is as follows:"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>{"For General / OBC / EWS": "₹ 500/-", "For SC / ST / EBC": "₹ 250/-", "For All Category female": "₹ 250/-", "Fess Refund": "General / OBC : Rs. 400/- will be refunded and Other candidates : Rs. 250/- will be refunded to the bank account after appearing in Stage I Exam.", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for RRB?", "Answer": "Candidates must have passed the Engineering Diploma / Degree, specific qualifications exam from any recognized board in India. For full eligibility details, please check the official notification."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4884,32 +4884,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SYLLABUS</t>
+          <t>ADMIT-CARD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BPSC School Teacher TRE 4.0 Recruitment 2026 Syllabus &amp; Exam Pattern 2026</t>
+          <t>NBEMS Group A, B &amp; C Various Post Exam City Details 2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>bpsc-school-teacher-tre-4-0-2026-syllabus</t>
+          <t>nbems-various-post-2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/bpsc-school-teacher-tre-4-0-2026/</t>
+          <t>https://sarkariresult.com.cm/nbems-various-post-2026/</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BPSC School Teacher TRE 4.0 Examination 2025</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>32,388 Posts</t>
+          <t>53 Posts</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4929,22 +4929,22 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years (Class 9 to 10 &amp; 11 to 12)", "Maximum Age": "37 Years (UR-Male)"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{"Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum Age": "42 Years (SC/ ST-Male &amp; Female)", "You May Also Check": "Rajasthan High Court Class VI Employees Peon Recruitment 2025", "Question": "What is the official website for BPSC ?", "Answer": "The official website for BPSC is http://www.bpsc.bih.nic.in/"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SYLLABUS</t>
+          <t>ADMIT-CARD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SBI Junior Associates Clerk Recruitment 2026 Syllabus &amp; Exam Pattern 2026</t>
+          <t>NTA AIAPGET Admit Card 2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>sbi-junior-associates-clerk-2026-syllabus</t>
+          <t>nta-aiapget-2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/sbi-junior-associates-clerk-2026/</t>
+          <t>https://sarkariresult.com.cm/nta-aiapget-2026/</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SBI Junior Associates Clerk</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>9124 Posts</t>
+          <t>Various Posts</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "20 Years", "Maximum Age": "28 Years", "Answer": "The age limit for SBI Junior Associates Clerk Bharti 2026 is as follows:"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>{"For OBC": "₹ 750/-", "For SC / ST, PH": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "UPSSSC Cane Supervisor Recruitment 2026", "Question": "What is the official website for SBI?", "Answer": "The eligibility criteria for the SBI Junior Associates Clerk Vacancy 2026 are as follows: Candidates must have a graduation degree in any field from a recognized university."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5054,32 +5054,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SYLLABUS</t>
+          <t>ADMIT-CARD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IBPS Clerk (CSA) 16th Recruitment 2026 Syllabus &amp; Exam Pattern 2026</t>
+          <t>Cotton Corporation of India CCI Various Post Exam City Details 2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ibps-clerk-16th-2026-syllabus</t>
+          <t>cci-various-post-2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/ibps-clerk-16th-2026/</t>
+          <t>https://sarkariresult.com.cm/cci-various-post-2026/</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>IBPS Clerk (CSA) 16th</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>11,403 Posts</t>
+          <t>148 Posts</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5104,17 +5104,17 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "20 Years", "Maximum Age": "28 Years", "Answer": "The age limit for IBPS Clerk (CSA) 16th Bharti 2026 is as follows:"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>{"For General, OBC, EWS": "₹ 850/-", "For SC, ST, ESM &amp; DESM": "₹ 175/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Computer Literacy": "Operating And Working Knowledge In Computer Systems is Mandatory ie. Candidates Should Have Certificate/ Diploma/ Degree in Computer Operations/ Language/ Should Have Studied Computer / Information Technology As One of the Subjects In The High School/ College/ Institute.", "Question": "What is the official website for IBPS?", "Answer": "The eligibility criteria for the IBPS Clerk (CSA) 16th Vacancy 2026 are as follows on UPSSSC rules."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5139,32 +5139,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SYLLABUS</t>
+          <t>ADMIT-CARD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UPSSSC PET Online Form 2026 Syllabus &amp; Exam Pattern 2026</t>
+          <t>BSF HCM &amp; ASI Steno Admit Card 2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>upsssc-pet-2026-syllabus</t>
+          <t>bsf-hcm-asi-steno-2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/upsssc-pet-2026/</t>
+          <t>https://sarkariresult.com.cm/bsf-hcm-asi-steno-2025/</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UPSSSC PET</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Exam Syllabus</t>
+          <t>2 posts</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5174,32 +5174,32 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Update Soon</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>{"For Minimum Age": "18 Years", "For Maximum Age": "40 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>{"Application Start": "03 August 2026", "For General, OBC": "₹ 185/-", "For SC, ST": "₹ 95/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website of UPSSSC?", "Answer": "The official website of UPSSSC is https://upsssc.gov.in/."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5224,32 +5224,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SYLLABUS</t>
+          <t>ADMIT-CARD</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UPSC EPFO / APFC Recruitment 2026 Syllabus &amp; Exam Pattern 2026</t>
+          <t>UPSSSC Lower PCS Admit Card 2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>upsc-epfo-2026-syllabus</t>
+          <t>upsssc-lower-pcs-2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/upsc-epfo-2026/</t>
+          <t>https://sarkariresult.com.cm/upsssc-lower-pcs-2026/</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UPSC EPFO EO / AO / APFC</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>80 Posts</t>
+          <t>2587 Posts</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5269,22 +5269,22 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years (Tentative)", "Maximum Age": "35-40 Years (Category Wise)"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>{"For General / OBC / EWS": "₹ 25/-", "For SC / ST": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "You May Also Check": "UPPSC Professor &amp; Assistant Professor Recruitment 2026", "Question": "What is the official website for UPSC?", "Answer": "The official website for UPSC is https://www.upsc.gov.in/"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5309,32 +5309,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SYLLABUS</t>
+          <t>ADMIT-CARD</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rajasthan Safai Karmchari Recruitment 2026 Syllabus &amp; Exam Pattern 2026</t>
+          <t>BPSSC Bihar Police Havildar Instructor PET Admit Card 2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>rajasthan-safai-karmchari-2026-syllabus</t>
+          <t>bpssc-havildar-instructor-2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/rajasthan-safai-karmchari-2026/</t>
+          <t>https://sarkariresult.com.cm/bpssc-havildar-instructor-2026/</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rajasthan Safai Karmchari</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>24,752 posts</t>
+          <t>122 Posts</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5359,17 +5359,17 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years.", "Maximum Age": "40 Years."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>{"General, Other State": "₹ 600/-", "OBC, BC, SC, ST": "₹ 400/-", "Question": "What is the official website for Rajasthan Safai Karmchari?", "Answer": "The official website for Rajasthan Safai Karmchari is https://lsg.rajasthan.gov.in/lsg/#/home/dptHome"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5394,32 +5394,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SYLLABUS</t>
+          <t>ADMIT-CARD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RPSC Rajasthan Police SI Telecom Final Result 2026 Syllabus &amp; Exam Pattern 2026</t>
+          <t>NICL Assistant Pre Admit Card 2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>rpsc-rajasthan-police-si-telecom-2025-syllabus</t>
+          <t>nicl-assistant-2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/rpsc-rajasthan-police-si-telecom-2025/</t>
+          <t>https://sarkariresult.com.cm/nicl-assistant-2026/</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RPSC SI Telecom Examination 2025</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>98 Post</t>
+          <t>500 Posts</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5439,22 +5439,22 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>09 November 2025</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "20 Years", "Maximum Age": "25 Years"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>{"For General, Other State": "₹ 600/-", "For SC / ST, OBC / BC": "₹ 400/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for RPSC?", "Answer": "The official website for RPSC is https://rpsc.rajasthan.gov.in/"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5479,32 +5479,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SYLLABUS</t>
+          <t>ADMIT-CARD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bihar Police Prohibition Constable Result 2026 Syllabus &amp; Exam Pattern 2026</t>
+          <t>BSNL Junior Telecom Officer JTO Admit Card 2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>csbc-bihar-prohibition-constable-2026-syllabus</t>
+          <t>bsnl-junior-telecom-officer-jto-2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/csbc-bihar-prohibition-constable-2026/</t>
+          <t>https://sarkariresult.com.cm/bsnl-junior-telecom-officer-jto-2026/</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bihar Police CSBC Constable Examination 2025</t>
+          <t>Govt Board</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4210 Posts</t>
+          <t>100 Posts</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5524,22 +5524,22 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>14 – 17 June 2026</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "As per rules", "Maximum Age": "As per rules"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>{"Payment Mode (Online)": "You can make the payment using the following methods:", "General (Male)": "18 – 23 years", "OBC / EBC (Male)": "18 – 25 years", "OBC / EBC (Female)": "18 – 26 years", "SC / ST (Male &amp; Female)": "18 – 28 years", "You May Also Check": "DSSSB Non-Teaching Various Post Online Form 2025", "Question": "What is the official website for CSBC ?", "Answer": "The notification is generally released in PDF format."}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5564,80 +5564,1100 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SYLLABUS</t>
+          <t>ADMIT-CARD</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SSC 10+2 CHSL 2025 FRTA Result Syllabus &amp; Exam Pattern 2026</t>
+          <t>IBPS SO XVI Pre Admit Card 2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ssc-chsl-2026-syllabus</t>
+          <t>ibps-so-xvi-2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>https://sarkariresult.com.cm/ibps-so-xvi-2026/</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Govt Board</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1035 posts</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>100% REAL SOURCE VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ADMIT-CARD</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Railway RRB Group D Admit Card 2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>railway-rrb-group-d-level-1-recruitment-2026-online</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://sarkariresult.com.cm/railway-rrb-group-d-level-1-recruitment-2026-online/</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Govt Board</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>22,195 Posts</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>100% REAL SOURCE VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>RSSB Forester Result 2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>rssb-forester-2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://sarkariresult.com.cm/rssb-forester-2026/</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Govt Board</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>259 Post</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>100% REAL SOURCE VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SSC 10+2 CHSL 2025 FRTA Result</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ssc-chsl-2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>https://sarkariresult.com.cm/ssc-chsl-2026/</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>SSC 10+2 CHSL Examination 2025</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Govt Board</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>3522 Posts</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>August 2026</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>September 2026</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>September 2026</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>Notify Soon</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "27 Years"}</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>{"Tier-I Exam Start": "12 November 2025", "Post Preference Cum Option Form": "19 – 25 June 2026", "For General/ OBC/ EWS": "₹ 100/-", "For SC/ ST/ Female": "₹ 0/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for SSC?", "Answer": "The official website for SSC is https://ssc.gov.in/"}</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>https://sarkariresult.com.cm/up-deled-2026/</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>100% REAL SOURCE VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>RPSC School Lecturer PGT Result 2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>rpsc-1st-grade-teacher-2025</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://sarkariresult.com.cm/rpsc-1st-grade-teacher-2025/</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Govt Board</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>3225 Post</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>100% REAL SOURCE VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>KVS NVS Teaching &amp; Non-Teaching Tier-II Result 2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>kvs-nvs-teaching-non-teaching-2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://sarkariresult.com.cm/kvs-nvs-teaching-non-teaching-2026/</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Govt Board</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>15,762 Posts</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>100% REAL SOURCE VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Bihar Police CSBC Constable GD Result 2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>bihar-police-csbc-constable-2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://sarkariresult.com.cm/bihar-police-csbc-constable-2026/</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Govt Board</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>83 Posts</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>100% REAL SOURCE VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Bihar Police CSBC Constable Operator Result 2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>bihar-police-csbc-constable-operator-2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://sarkariresult.com.cm/bihar-police-csbc-constable-operator-2026/</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Govt Board</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>993 Posts</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>100% REAL SOURCE VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Bihar Police Prohibition Constable Result 2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>csbc-bihar-prohibition-constable-2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://sarkariresult.com.cm/csbc-bihar-prohibition-constable-2026/</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Govt Board</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>4210 Posts</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>100% REAL SOURCE VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>NTA SWAYAM Result 2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>nta-swayam-2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://sarkariresult.com.cm/nta-swayam-2026/</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Govt Board</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Various Posts</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>100% REAL SOURCE VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>RPSC Rajasthan Police SI Telecom Final Result 2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>rpsc-rajasthan-police-si-telecom-2025</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://sarkariresult.com.cm/rpsc-rajasthan-police-si-telecom-2025/</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Govt Board</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>98 Post</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>100% REAL SOURCE VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ADMISSION</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>IIT JAM Admission Form 2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>iit-jam-2027</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://sarkariresult.com.cm/iit-jam-2027/</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Govt Board</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Various Seats</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>12 October 2026</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>12 October 2026</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>100% REAL SOURCE VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ADMISSION</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CLAT Admission Form 2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>clat-2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://sarkariresult.com.cm/clat-2026/</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Govt Board</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Various Seats</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>31 October 2026</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>31 October 2026</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>

--- a/data/verified_posts_master_sheet.xlsx
+++ b/data/verified_posts_master_sheet.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -442,18 +442,16 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
     <col width="45" customWidth="1" min="12" max="12"/>
     <col width="45" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
-    <col width="25" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="27" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -504,40 +502,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Fee Payment Last Date</t>
+          <t>Apply Online URL (Real)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Exam / Event Date</t>
+          <t>Notification PDF URL (Real)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Age Limits</t>
+          <t>Official Website URL (Real)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Application Fees</t>
+          <t>Result / Admit / Key URL (Real)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Apply Online URL</t>
+          <t>Check Sarkari Result URL (StudyTopper)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Notification PDF URL</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Official Website URL</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Verification Status</t>
         </is>
@@ -569,7 +557,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Himachal Pradesh High Court Various Post</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -589,22 +577,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://www.hphcrecruitment.in/login</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://highcourt.hp.gov.in/</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "45-50 Years (Category Wise)"}</t>
+          <t>https://highcourt.hp.gov.in/</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>{"For General": "₹ 450/-", "For OBC, EWS, SC, ST, PH": "₹ 300/- (Only For Himanchal Pradesh Candidates)", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for HP High Court?", "Answer": "The age limit for Himachal Pradesh High Court Various Post Bharti 2026 is as follows:"}</t>
+          <t>https://highcourt.hp.gov.in/</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -613,16 +601,6 @@
         </is>
       </c>
       <c r="O2" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -654,7 +632,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RCF Kapurthala Apprentice</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -674,22 +652,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://pardarsy.railnet.gov.in/apprentice-2026/</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://www.rcf.indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "15 Year", "Maximum Age": "24 Year", "Answer": "The age limit for RCF Kapurthala Apprentice Bharti 2026 is as follows on official website."}</t>
+          <t>http://www.rcf.indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>{"Merit List": "Notify Later", "For General/ OBC/ EWS": "₹ 100/-", "For SC/ ST/ PH / Female": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for RCF?", "Answer": "Candidates must have passed 10th class, or ITI, from a recognized board/institution."}</t>
+          <t>http://www.rcf.indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -698,16 +676,6 @@
         </is>
       </c>
       <c r="O3" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -739,7 +707,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Railway ICF Trade Apprentice</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -759,22 +727,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://pb.icf.gov.in/act2026/apply.php</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://www.icf.indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>{"Age Limit": "15-22 Years (Non-ITI Candidate)", "Answer": "The age limit for Railway ICF Trade Apprentices Bharti 2026 is as follows:"}</t>
+          <t>http://www.icf.indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>{"For General/ OBC/ EWS Candidates": "₹ 100/-", "For SC/ ST/PH Candidates": "₹ 00/-", "For All Female Category Candidates": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for Railway ICF?", "Answer": "Candidates must have Class 10 (Matric) with 50% marks and an ITI certificate in the relevant trade. For trade-wise eligibility, check the official notification."}</t>
+          <t>http://www.icf.indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -783,16 +751,6 @@
         </is>
       </c>
       <c r="O4" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -824,7 +782,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GIMS Noida Staff Nurse</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -844,22 +802,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://cdn3.digialm.com/EForms/configuredHtml/31586/101679/Index.html</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>https://www.gims.ac.in/recruitment.html</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>{"For Minimum Age": "21 Years", "For Maximum Age": "40 Years"}</t>
+          <t>https://www.gims.ac.in/recruitment.html</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>{"General, OBC, EWS": "₹ 1298/-", "SC, ST": "₹ 944/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "For Degree Holder": "B.Sc Nursing (4-Year) or B.Sc Nursing (Post Basic) (2-Year) from an INC/State Council-recognized University/Institute + Registered as a Nurse &amp; Midwife with the State/Indian Nursing Council.", "For Diploma Holder": "Diploma in General Nursing Midwifery (GNM) from an INC-recognized Board/Council + Registered as Nurse &amp; Midwife with the State/Indian Nursing Council + 2 years’ experience in a minimum 50-bedded hospital after completing the diploma.", "Question": "What is the official website for GIMS Noida?", "Answer": "The eligibility criteria for the GIMS Noida Staff Nurse Vacancy 2026 are as follows on UPSSSC rules."}</t>
+          <t>https://www.gims.ac.in/recruitment.html</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -868,16 +826,6 @@
         </is>
       </c>
       <c r="O5" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -909,7 +857,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UPSSSC Veterinary Pharmacist</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -929,22 +877,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>https://upsssc.gov.in//default.aspx</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>{"For Minimum Age": "18 Years", "For Maximum Age": "40 Years"}</t>
+          <t>http://upsssc.gov.in/Default.aspx</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{"General, OBC, EWS": "₹ 25/-", "SC, ST": "₹ 25/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in//default.aspx"}</t>
+          <t>http://upsssc.gov.in/Default.aspx</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -953,16 +901,6 @@
         </is>
       </c>
       <c r="O6" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -994,7 +932,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UPSSSC Junior Engineer JE (Agriculture)</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1014,22 +952,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>https://upsssc.gov.in//default.aspx</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>{"For Minimum Age": "18 Years", "For Maximum Age": "40 Years"}</t>
+          <t>http://upsssc.gov.in/Default.aspx</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"General, OBC, EWS": "₹ 25/-", "SC, ST": "₹ 25/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in//default.aspx"}</t>
+          <t>http://upsssc.gov.in/Default.aspx</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1038,16 +976,6 @@
         </is>
       </c>
       <c r="O7" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1079,7 +1007,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RRVUNL JE, Junior Assistant</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1099,22 +1027,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://ibpsreg.ibps.in/rrvunljun26/</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>https://energy.rajasthan.gov.in/rrvun/#/pages/sm/department-page/373376/2700</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years"}</t>
+          <t>https://energy.rajasthan.gov.in/rrvun/#/pages/sm/department-page/373376/2700</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"For General": "₹ 1000/-", "For MBC/ BC / EWS": "₹ 500/-", "For SC/ ST/ PH Candidates": "₹ 500/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Junior Accountant &amp; Junior Assistant/ Commercial Assistant-II": "18-40 Years", "You May Also Check": "SSC CGL Recruitment 2026", "Question": "What is the official website for RRVUNL ?", "Answer": "The official website for RRVUNL is https://energy.rajasthan.gov.in/rrvun/#/pages/sm/department-page/373376/2700"}</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1123,16 +1051,6 @@
         </is>
       </c>
       <c r="O8" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1164,7 +1082,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UP Anganwadi Bharti Examination 2025</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1184,22 +1102,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://upanganwadibharti.in/users/registration.php</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://upanganwadibharti.in/</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>{"For Minimum Age": "18 years", "For Maximum Age": "35 years", "Answer": "The age limit for candidates applying for this recruitment is as per the rules of UP Anganwadi. For detailed age information, please refer to the official notification."}</t>
+          <t>http://upanganwadibharti.in/</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"Application Start": "November 2025", "Question": "What is the official website of UP Anganwadi? Answer: The official website of UP Anganwadi is https://upanganwadibharti.in/.", "Answer": "The online application for this recruitment started in November 2025."}</t>
+          <t>http://upanganwadibharti.in/</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1208,16 +1126,6 @@
         </is>
       </c>
       <c r="O9" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1249,7 +1157,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UPSSSC PET</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1269,22 +1177,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>https://upsssc.gov.in/AllNotifications.aspx</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Update Soon</t>
+          <t>https://upsssc.gov.in/ViewPdf.aspx?mQakfo5LrW2Cdx4YG2/st+GVGmBBNX8aG1X69whn6lU=</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>{"For Minimum Age": "18 Years", "For Maximum Age": "40 Years"}</t>
+          <t>https://upsssc.gov.in/</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{"Application Start": "03 August 2026", "For General, OBC": "₹ 185/-", "For SC, ST": "₹ 95/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website of UPSSSC?", "Answer": "The official website of UPSSSC is https://upsssc.gov.in/."}</t>
+          <t>https://upsssc.gov.in/</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1293,16 +1201,6 @@
         </is>
       </c>
       <c r="O10" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1334,7 +1232,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MP High Court Assistant Grade III</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1354,22 +1252,22 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://cdn.digialm.com//EForms/configuredHtml/772/101789/Registration.html</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://mphc.gov.in/</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Year", "Maximum Age": "40 – 45 Year"}</t>
+          <t>https://mphc.gov.in/</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{"For General/ Other State": "₹ 943.40/-", "For SC/ ST/ OBC/ EWS": "₹ 743.40/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for MPHC?", "Answer": "The eligibility for MP High Court Assistant Grade III Bharti 2026 is as follows post wise."}</t>
+          <t>https://mphc.gov.in/</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1378,16 +1276,6 @@
         </is>
       </c>
       <c r="O11" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1419,7 +1307,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MPESB Group 3 Sub Engineer &amp; Other Post</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1439,22 +1327,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://esb.mponline.gov.in/Portal/Examinations/Vyapam/examsList.aspx</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>06 October 2026</t>
+          <t>https://esb.mp.gov.in/e_default.html</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years"}</t>
+          <t>https://esb.mp.gov.in/e_default.html</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"For General / Other State": "Rs. 500/-", "For SC / ST/ OBC": "Rs. 250/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "Maximum Age": "45 Years (SC, ST, OBC, PwBD &amp; All Female)", "You May Also Check": "Rajasthan High Court Stenographer Recruitment 2026", "Question": "What is the official website for MPESB?", "Answer": "Candidates must have a Bachelor’s Degree in any discipline from a university recognized by the Government of India."}</t>
+          <t>https://esb.mp.gov.in/e_default.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1463,16 +1351,6 @@
         </is>
       </c>
       <c r="O12" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1504,7 +1382,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>RSSB Junior Engineer</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1524,22 +1402,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://sso.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>https://rssb.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Answer": "The age limit for RSSB Junior Engineer Bharti 2026 is as follows:"}</t>
+          <t>https://rssb.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>{"For General, EWS, OBC (Creamy Layer)": "₹ 600/-", "For EWS, OBC (Non Creamy Layer)": "₹ 400/-", "For SC, ST, PH": "₹ 400/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "BPSC School Teacher TRE 4.0 Recruitment 2026", "Question": "What is the official website for RSSB?", "Answer": "The official website for RSSB is https://rssb.rajasthan.gov.in/"}</t>
+          <t>https://rssb.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1548,16 +1426,6 @@
         </is>
       </c>
       <c r="O13" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1589,7 +1457,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MPESB Group-2 Sub Group-4 Patwari</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1609,22 +1477,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://esb.mponline.gov.in/Portal/Examinations/Vyapam/examsList.aspx</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>https://esb.mp.gov.in/e_default.html</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Answer": "The age limit for MPESB Group-2 Sub Group-4 Patwari Bharti 2026 is as follows:"}</t>
+          <t>https://esb.mp.gov.in/e_default.html</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>{"For General / Other State": "Rs. 500/-", "For SC / ST/ OBC": "Rs. 250/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "Maximum Age": "45 Years (SC, ST, OBC, PwBD &amp; All Female)", "You May Also Check": "Rajasthan High Court Stenographer Recruitment 2026", "Question": "What is the official website for MPESB?", "Answer": "Candidates must have a Bachelor’s Degree in any discipline from a university recognized by the Government of India."}</t>
+          <t>https://esb.mp.gov.in/e_default.html</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1633,16 +1501,6 @@
         </is>
       </c>
       <c r="O14" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1674,7 +1532,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UPPSC Professor &amp; Assistant Professor</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1694,22 +1552,22 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://uppsc.up.nic.in/</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "35 Years", "Maximum Age": "55 Years"}</t>
+          <t>https://uppsc.up.nic.in/</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>{"For General / OBC / EWS": "₹ 105/-", "For SC / ST": "₹ 65/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for UPPSC?", "Answer": "The official website for UPPSC is https://uppsc.up.nic.in/"}</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1718,16 +1576,6 @@
         </is>
       </c>
       <c r="O15" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1759,7 +1607,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BOB Local Bank Officer LBO</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1779,22 +1627,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://ibpsreg.ibps.in/bobjul26/</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Notify Later</t>
+          <t>https://bankofbaroda.bank.in/-/media/Project/BOB/CountryWebsites/India/Career/2026/26-08/Advertisement-18-04.pdf</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years", "Maximum Age": "30 Years", "Answer": "The age limit for BOB Local Bank Officer LBO Bharti 2026 is as follows:"}</t>
+          <t>https://www.bankofbaroda.in/</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>{"For General, OBC, EWS": "₹ 850/-", "For SC / ST, PwBD/": "₹ 175/-", "For All Female": "₹ 175/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "MP High Court Assistant Grade III Recruitment 2026", "Question": "What is the official website for BOB?", "Answer": "The eligibility for BOB Local Bank Officer LBO Bharti 2026 is as follows post wise."}</t>
+          <t>https://www.bankofbaroda.in/</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1803,16 +1651,6 @@
         </is>
       </c>
       <c r="O16" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1839,12 +1677,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/upsssc-pet-2026-syllabus/</t>
+          <t>https://sarkariresult.com.cm/upsssc-pet-2026/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1864,22 +1702,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>01 September 2026</t>
+          <t>https://upsssc.gov.in/AllNotifications.aspx</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://upsssc.gov.in/ViewPdf.aspx?mQakfo5LrW2Cdx4YG2/st+GVGmBBNX8aG1X69whn6lU=</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsssc.gov.in/</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsssc.gov.in/</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1888,16 +1726,6 @@
         </is>
       </c>
       <c r="O17" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1924,12 +1752,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/rrb-je-2026-syllabus/</t>
+          <t>https://sarkariresult.com.cm/rrb-je-2026/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1949,22 +1777,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13 September 2026</t>
+          <t>https://www.rrbapply.gov.in/#/auth/landing</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1973,16 +1801,6 @@
         </is>
       </c>
       <c r="O18" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2014,7 +1832,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2034,22 +1852,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13 September 2026</t>
+          <t>https://www.rrbapply.gov.in/#/auth/landing</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2058,16 +1876,6 @@
         </is>
       </c>
       <c r="O19" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2099,7 +1907,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2119,22 +1927,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>15 September 2026</t>
+          <t>https://iimcat.ac.in/per/g06/pub/32842/ASM/WebPortal/1/index.html?32842@@1@@1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://gate2027.iitm.ac.in/</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://iimcat.ac.in/</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://iimcat.ac.in/</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2143,16 +1951,6 @@
         </is>
       </c>
       <c r="O20" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2179,12 +1977,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/ssc-chsl-2026-syllabus/</t>
+          <t>https://sarkariresult.com.cm/ssc-chsl-2026/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2204,22 +2002,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://ssc.gov.in/candidate-portal/one-time-registration/home-page</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2025/06/Notice_of_adv_chsl_2025-1.pdf</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://ssc.gov.in/</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://ssc.gov.in/api/attachment/uploads/masterData/Results/ROLL_17082026.pdf</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2228,16 +2026,6 @@
         </is>
       </c>
       <c r="O21" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2264,12 +2052,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/csbc-bihar-prohibition-constable-2026-syllabus/</t>
+          <t>https://sarkariresult.com.cm/csbc-bihar-prohibition-constable-2026/</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2289,22 +2077,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://apply-csbc.com/csbc_3_25_mv1/applicationIndex</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://csbc.bihar.gov.in/Advt/Advt-03-2025-Prohibition-Jail%20Warder-Mobile%20Squad-Constables.pdf</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://csbc.bihar.gov.in/A-REP.htm</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://csbc.bihar.gov.in/Advt/Results-03-2025-PET-18-08-2026.pdf</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2313,16 +2101,6 @@
         </is>
       </c>
       <c r="O22" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2349,12 +2127,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/rpsc-rajasthan-police-si-telecom-2025-syllabus/</t>
+          <t>https://sarkariresult.com.cm/rpsc-rajasthan-police-si-telecom-2025/</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2374,22 +2152,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://sso.rajasthan.gov.in/signin</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://rpsc.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://rpsc.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://rpsc.rajasthan.gov.in/Static/Result/E8BDC9265C2B4202BE9C2DBEB2830182.pdf</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2398,16 +2176,6 @@
         </is>
       </c>
       <c r="O23" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2434,12 +2202,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/rajasthan-safai-karmchari-2026-syllabus/</t>
+          <t>https://sarkariresult.com.cm/rajasthan-safai-karmchari-2026/</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2459,22 +2227,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://sso.rajasthan.gov.in/signin?encq=6JkTF7D/fPuyiLpqlTuv+tsssIL22cKEce/qYZMZKsM=</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2483,16 +2251,6 @@
         </is>
       </c>
       <c r="O24" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2519,12 +2277,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/upsc-epfo-2026-syllabus/</t>
+          <t>https://sarkariresult.com.cm/upsc-epfo-2026/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2544,22 +2302,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://www.upsc.gov.in/</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsc.gov.in/</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsc.gov.in/</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2568,16 +2326,6 @@
         </is>
       </c>
       <c r="O25" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2604,12 +2352,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/ibps-clerk-16th-2026-syllabus/</t>
+          <t>https://sarkariresult.com.cm/ibps-clerk-16th-2026/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2629,22 +2377,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://ibpsreg.ibps.in/csaxvijul26/</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://ibps.in/</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://www.ibps.in/</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://www.ibps.in/</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2653,16 +2401,6 @@
         </is>
       </c>
       <c r="O26" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2689,12 +2427,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/sbi-junior-associates-clerk-2026-syllabus/</t>
+          <t>https://sarkariresult.com.cm/sbi-junior-associates-clerk-2026/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2714,22 +2452,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://ibpsreg.ibps.in/sbijajul26/</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://sbi.bank.in/web/careers/current-openings</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://sbi.bank.in/web/careers/current-openings</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://sbi.bank.in/web/careers/current-openings</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2738,16 +2476,6 @@
         </is>
       </c>
       <c r="O27" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2774,12 +2502,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://sarkariresult.com.cm/bpsc-school-teacher-tre-4-0-2026-syllabus/</t>
+          <t>https://sarkariresult.com.cm/bpsc-school-teacher-tre-4-0-2026/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2799,22 +2527,22 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://www.bpsc.bih.nic.in/</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>http://www.bpsc.bih.nic.in/</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>http://www.bpsc.bih.nic.in/</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2823,16 +2551,6 @@
         </is>
       </c>
       <c r="O28" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2864,7 +2582,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2884,22 +2602,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://ibpsreg.ibps.in/csaxvijul26/</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://ibps.in/</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://www.ibps.in/</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://www.ibps.in/</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2908,16 +2626,6 @@
         </is>
       </c>
       <c r="O29" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2949,7 +2657,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2969,22 +2677,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://www.upsc.gov.in/</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsc.gov.in/</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsc.gov.in/</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2993,16 +2701,6 @@
         </is>
       </c>
       <c r="O30" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3034,7 +2732,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3054,22 +2752,22 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://recruitment.skau.ac.in/nonteaching/</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://skau.ac.in/</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://skau.ac.in/</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://skau.ac.in/</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3078,16 +2776,6 @@
         </is>
       </c>
       <c r="O31" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3119,7 +2807,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3139,22 +2827,22 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://sso.rajasthan.gov.in/signin?encq=6JkTF7D/fPuyiLpqlTuv+tsssIL22cKEce/qYZMZKsM=</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://rpsc.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://rpsc.rajasthan.gov.in/home</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://rpsc.rajasthan.gov.in/home</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3163,16 +2851,6 @@
         </is>
       </c>
       <c r="O32" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3204,7 +2882,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3224,22 +2902,22 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://cdn.digialm.com//EForms/configuredHtml/1258/101396//Index.html</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://www.isro.gov.in/media_isro/pdf/recruitmentNotice/2026/July/Bilingual%20Advertisement_Asst_JPA_UDC_Steno_ICRB_2026_27072026.pdf</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://www.isro.gov.in/</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://www.isro.gov.in/</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3248,16 +2926,6 @@
         </is>
       </c>
       <c r="O33" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3289,7 +2957,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3309,22 +2977,22 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://principalhe.upessc.org/otr/</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://upessc.up.gov.in/</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upessc.up.gov.in/</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upessc.up.gov.in/</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3333,16 +3001,6 @@
         </is>
       </c>
       <c r="O34" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3374,7 +3032,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3394,22 +3052,22 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://sso.rajasthan.gov.in/signin?encq=6JkTF7D/fPuyiLpqlTuv+tsssIL22cKEce/qYZMZKsM=</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3418,16 +3076,6 @@
         </is>
       </c>
       <c r="O35" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3459,7 +3107,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3479,22 +3127,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://ibpsreg.ibps.in/sbijajul26/</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://sbi.bank.in/web/careers/current-openings</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://sbi.bank.in/web/careers/current-openings</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://sbi.bank.in/web/careers/current-openings</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3503,16 +3151,6 @@
         </is>
       </c>
       <c r="O36" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3544,7 +3182,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3564,22 +3202,22 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://www.bpsc.bih.nic.in/</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>http://www.bpsc.bih.nic.in/</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>http://www.bpsc.bih.nic.in/</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3588,16 +3226,6 @@
         </is>
       </c>
       <c r="O37" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3629,7 +3257,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3649,22 +3277,22 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://aibe.digivarsity.online/WebApp/Forms/Authentication.aspx</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://jam.iitkgp.ac.in/</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://www.allindiabarexamination.com/</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://www.allindiabarexamination.com/</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3673,16 +3301,6 @@
         </is>
       </c>
       <c r="O38" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3714,7 +3332,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3734,22 +3352,22 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://scholarship.up.gov.in/RegistrationNew.aspx</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://scholarship.up.gov.in/</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://scholarship.up.gov.in/</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://scholarship.up.gov.in/</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3758,16 +3376,6 @@
         </is>
       </c>
       <c r="O39" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3799,7 +3407,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3819,22 +3427,22 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://form.bsebdeled.com/login</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://formapi.bsebdeled.com/files/others/deled-form-2026-vigyapti.pdf</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>http://biharboardonline.bihar.gov.in/</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://bsebdeled.cbrt.co.in/bseb-2026/score-card-download-2026</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3843,16 +3451,6 @@
         </is>
       </c>
       <c r="O40" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3884,7 +3482,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3904,22 +3502,22 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/08/Bihar-Stet-2026-Notification.pdf</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://bsebstet.org/</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://bsebstet.org/</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3928,16 +3526,6 @@
         </is>
       </c>
       <c r="O41" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3969,7 +3557,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3989,22 +3577,22 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://gate2027.iitm.ac.in/</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://gate2027.iitm.ac.in/</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://gate2027.iitm.ac.in/</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4013,16 +3601,6 @@
         </is>
       </c>
       <c r="O42" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4054,7 +3632,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4074,22 +3652,22 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://jsscjfwce2024.in/home</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://jssc.nic.in/sites/default/files/JFWCE-2024-Brochure.pdf</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>http://jssc.nic.in/</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>http://jssc.nic.in/</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4098,16 +3676,6 @@
         </is>
       </c>
       <c r="O43" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4139,7 +3707,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4159,22 +3727,22 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://cdn.digialm.com/EForms/configuredHtml/1258/100343/login.html</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://afcat.edcil.co.in/assets/images/news/AFCAT_02_2026/Notification%20for%20AFCAT%20Cycle%2002-2026.pdf</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://afcat.edcil.co.in/</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://afcat.edcil.co.in/</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4183,16 +3751,6 @@
         </is>
       </c>
       <c r="O44" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4224,7 +3782,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4244,22 +3802,22 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://dsssb.delhi.gov.in/sites/default/files/DSSSB/circulars-orders/final_advt._no._01-2024_district_court_advt_combined_1.pdf</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://dsssb.delhi.gov.in/home/Delhi-Subordinate-Services-Selection-Board</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://dsssbonline.nic.in/</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4268,16 +3826,6 @@
         </is>
       </c>
       <c r="O45" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4309,7 +3857,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4329,22 +3877,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://upsssc.gov.in/AllNotifications.aspx</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/03/ViewPdf-2.pdf</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsssc.gov.in/</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsssc.gov.in/Online_App/Results.aspx?ID=153&amp;Result_Type=P&amp;Exam_Code=5&amp;Advt_Code=571&amp;Dept_Code=577&amp;Post_Code=1&amp;OnlyIntview=No</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4353,16 +3901,6 @@
         </is>
       </c>
       <c r="O46" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4394,7 +3932,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4414,22 +3952,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://bpsconline.bihar.gov.in/candidate/login</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/02/642283632_122162143886682404_1816049250780731310_n.jpg</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://bpsc.bihar.gov.in/</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://bpsc.bihar.gov.in/</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4438,16 +3976,6 @@
         </is>
       </c>
       <c r="O47" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4479,7 +4007,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4499,22 +4027,22 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://examinationservices.nic.in/ExamSys26Part2/Root/Home.aspx?enc=Ei4cajBkK1gZSfgr53ImFTqGsyg38PlGNCGSuvSzsiVbovgbG6pVEHea7DNFe38E</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://cdnbbsr.s3waas.gov.in/s3efdf562ce2fb0ad460fd8e9d33e57f57/uploads/2026/05/202605271224945892.pdf</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://csirnet.nta.ac.in/</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://csirnet.nta.ac.in/</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4523,16 +4051,6 @@
         </is>
       </c>
       <c r="O48" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4564,7 +4082,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4584,22 +4102,22 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://examinationservices.nic.in/examsys26part2/Root/Home.aspx?enc=Ei4cajBkK1gZSfgr53ImFfGIu9Vld8UsAWKvCQaecYKgCg98d/PmJC3n7SgV5KcN</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://cdnbbsr.s3waas.gov.in/s388a839f2f6f1427879fc33ee4acf4f66/uploads/2026/05/202605091397132773.pdf</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://exams.nta.ac.in/ICAR/</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://exams.nta.ac.in/ICAR/</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4608,16 +4126,6 @@
         </is>
       </c>
       <c r="O49" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4649,7 +4157,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4669,22 +4177,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://upsssc.gov.in//AllNotifications.aspx</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://upsssc.gov.in//ViewPdf.aspx?l9/BD5ly1AMycsyNVO4s6W5SRYzkhIqZjt4RIvmLovI=</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsssc.gov.in/</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsssc.gov.in/Online_App/Results.aspx?ID=147&amp;Result_Type=P&amp;Exam_Code=5&amp;Advt_Code=569&amp;Dept_Code=558&amp;Post_Code=1&amp;OnlyIntview=No</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4693,16 +4201,6 @@
         </is>
       </c>
       <c r="O50" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4734,7 +4232,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4754,22 +4252,22 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://upsssc.gov.in//AllNotifications.aspx</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://upsssc.gov.in/ViewPdf.aspx?IErkSJ1zmT8v6nE0KeY3gy4ltEbfCt7U+YeeLcxsi1g=</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsssc.gov.in/</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsssc.gov.in/ResultsDire.aspx</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4778,16 +4276,6 @@
         </is>
       </c>
       <c r="O51" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4819,7 +4307,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4839,22 +4327,22 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://upsssc.gov.in//AllNotifications.aspx</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://upsssc.gov.in/</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsssc.gov.in/</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsssc.gov.in/Online_App/Results.aspx?ID=150&amp;Result_Type=P&amp;Exam_Code=5&amp;Advt_Code=564&amp;Dept_Code=552&amp;Post_Code=1&amp;OnlyIntview=No</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4863,16 +4351,6 @@
         </is>
       </c>
       <c r="O52" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4904,7 +4382,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4924,22 +4402,22 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://cdn3.digialm.com/EForms/configuredHtml/1815/101418/Index.html</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://natboard.edu.in/viewNotice.php?NBE=UGRseW1ZVldCdUcxbmZZWWg1ZFMxdz09</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://natboard.edu.in/</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://natboard.edu.in/</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4948,16 +4426,6 @@
         </is>
       </c>
       <c r="O53" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4989,7 +4457,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5009,22 +4477,22 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://examinationservices.nic.in/ExamSys26part2/root/Home.aspx?enc=Ei4cajBkK1gZSfgr53ImFZ+h0MepSUWC4caRGr23rIGxoddmkPhP33EPDwrEMlwi</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://cdnbbsr.s3waas.gov.in/s388a839f2f6f1427879fc33ee4acf4f66/uploads/2026/07/202607101983155019.pdf</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://exams.nta.ac.in/AIAPGET/</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://exams.nta.ac.in/AIAPGET/</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5033,16 +4501,6 @@
         </is>
       </c>
       <c r="O54" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5074,7 +4532,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5094,22 +4552,22 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://cdn.digialm.com/EForms/configuredHtml/1258/100936/login.html</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/07/CCI-Various-Post-2026-Short-Notice.png</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://cotcorp.org.in/</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://cotcorp.org.in/</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5118,16 +4576,6 @@
         </is>
       </c>
       <c r="O55" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5159,7 +4607,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5179,22 +4627,22 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://rectt.bsf.gov.in/</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://rectt.bsf.gov.in/static/bsf/pdf/234fb396-0d25-11ef-ba98-0a050616f7db.pdf?rel=2024060301</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://bsf.gov.in/</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://d3t79nicn48uzj.cloudfront.net/bsf/custom/1756724609.pdf</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5203,16 +4651,6 @@
         </is>
       </c>
       <c r="O56" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5244,7 +4682,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5264,22 +4702,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://upsssc.gov.in//AllNotifications.aspx</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://upsssc.gov.in/ViewPdf.aspx?HA04nYKkgpncofLRuXT6k7Np5V3U8T3Cr2bvb1DZAsc=</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsssc.gov.in/</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://upsssc.gov.in/Online_App/Results.aspx?ID=154&amp;Result_Type=P&amp;Exam_Code=7&amp;Advt_Code=730&amp;Dept_Code=578&amp;Post_Code=1&amp;OnlyIntview=No</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5288,16 +4726,6 @@
         </is>
       </c>
       <c r="O57" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5329,7 +4757,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5349,22 +4777,22 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://apply-bpssc.com/bpssc_havr_clerk_5_26_v1/applicationIndex</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://bpssc.bihar.gov.in/Notices/Advt.%20no.-05-2026.pdf</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://bpssc.bihar.gov.in/</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://bpssc.bihar.gov.in/Notices/Advt_052026_PRELIMS_Result_Publish_12082026.pdf</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5373,16 +4801,6 @@
         </is>
       </c>
       <c r="O58" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5414,7 +4832,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5434,22 +4852,22 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://ibpsreg.ibps.in/nicljul26/</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://nationalinsurance.nic.co.in/sites/default/files/2026-07/NICL%20ASSISTANT%20-%20Recuritment%20Advertisment%202026-27%20%28Final%29.pdf</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://nationalinsurance.nic.co.in/recruitment</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://nationalinsurance.nic.co.in/recruitment</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5458,16 +4876,6 @@
         </is>
       </c>
       <c r="O59" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5499,7 +4907,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5519,22 +4927,22 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://bsnlregistration.ibtexamination.com/AppO2BsNL_2026/</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/05/Examination-notification-DR-JTOT.pdf</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://bsnl.co.in/en</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://bsnl.co.in/en</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5543,16 +4951,6 @@
         </is>
       </c>
       <c r="O60" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5584,7 +4982,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5604,22 +5002,22 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://ibpsreg.ibps.in/crpspxvimy26/</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://www.ibps.in/</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://www.ibps.in/</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://www.ibps.in/</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5628,16 +5026,6 @@
         </is>
       </c>
       <c r="O61" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5669,7 +5057,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5689,22 +5077,22 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://www.rrbapply.gov.in/#/auth/landing</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/02/CEN_-09-2025_Hindi.pdf</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://indianrailways.gov.in/</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5713,16 +5101,6 @@
         </is>
       </c>
       <c r="O62" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5754,7 +5132,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5774,22 +5152,22 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://sso.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://rssb.rajasthan.gov.in/storage/advertisement_item/1767617460.pdf</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://rssb.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://rssb.rajasthan.gov.in/results</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5798,16 +5176,6 @@
         </is>
       </c>
       <c r="O63" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5839,7 +5207,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5859,22 +5227,22 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://ssc.gov.in/candidate-portal/one-time-registration/home-page</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2025/06/Notice_of_adv_chsl_2025-1.pdf</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://ssc.gov.in/</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://ssc.gov.in/api/attachment/uploads/masterData/Results/ROLL_17082026.pdf</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5883,16 +5251,6 @@
         </is>
       </c>
       <c r="O64" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5924,7 +5282,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5944,22 +5302,22 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://sso.rajasthan.gov.in/signin</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://rpsc.rajasthan.gov.in/Static/RecruitmentAdvertisements/9C26ACB4C6014924AF100B4D7FE67C27.pdf</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://rpsc.rajasthan.gov.in/news</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://rpsc.rajasthan.gov.in/results</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5968,16 +5326,6 @@
         </is>
       </c>
       <c r="O65" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -6009,7 +5357,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6029,22 +5377,22 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://examinationservices.nic.in/recsys2025/root/Home.aspx?enc=Ei4cajBkK1gZSfgr53ImFbEsl0hvvhEEwgxfU0IzC28jtU4yhpqb3pomlo4g+VC8</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2025/11/KVS-NVS-Teaching-and-Non-Teaching-Recruitment-2025-Short-Notice.jpg</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://kvsangathan.nic.in/en/</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://examinationservices.nic.in/recsys2025/root/CandidateLogin.aspx?enc=Ei4cajBkK1gZSfgr53ImFbEsl0hvvhEEwgxfU0IzC28jtU4yhpqb3pomlo4g+VC8</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -6053,16 +5401,6 @@
         </is>
       </c>
       <c r="O66" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -6094,7 +5432,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6114,22 +5452,22 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://apply-csbc.com/CSBC_CT_01_2026_V1/applicationIndex</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://csbc.bihar.gov.in/Advt/Advt-01-2026-Special%20Branch%20Constable.pdf</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://csbc.bihar.gov.in/</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://csbc.bihar.gov.in/Advt/Results-01-2026-PST-18-08-2026.pdf</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -6138,16 +5476,6 @@
         </is>
       </c>
       <c r="O67" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -6179,7 +5507,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6199,22 +5527,22 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://apply-csbc.com/csbc_ct_operator_2_26_final/applicationIndex</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://csbc.bihar.gov.in/Advt/Advt-02-2026-Constable(Operator).pdf</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://csbc.bihar.gov.in/</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://csbc.bihar.gov.in/Advt/Results-02-2026-PET-18-08-2026.pdf</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -6223,16 +5551,6 @@
         </is>
       </c>
       <c r="O68" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -6264,7 +5582,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6284,22 +5602,22 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://apply-csbc.com/csbc_3_25_mv1/applicationIndex</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://csbc.bihar.gov.in/Advt/Advt-03-2025-Prohibition-Jail%20Warder-Mobile%20Squad-Constables.pdf</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://csbc.bihar.gov.in/A-REP.htm</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://csbc.bihar.gov.in/Advt/Results-03-2025-PET-18-08-2026.pdf</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6308,16 +5626,6 @@
         </is>
       </c>
       <c r="O69" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -6349,7 +5657,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6369,22 +5677,22 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://examinationservices.nic.in/ExamSys26Part2/root/Home.aspx?enc=Ei4cajBkK1gZSfgr53ImFT241Ywt085kwtQgupnjkGjahWnfiEjRQE4dC4wPCcN0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://cdnbbsr.s3waas.gov.in/s388a839f2f6f1427879fc33ee4acf4f66/uploads/2026/06/202606121392177863.pdf</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://exams.nta.nic.in/swayam/</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://cnr.nic.in/Results26/SWAYAM/Login?apprefno=101562612</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -6393,16 +5701,6 @@
         </is>
       </c>
       <c r="O70" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -6434,7 +5732,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6454,22 +5752,22 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>https://sso.rajasthan.gov.in/signin</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://rpsc.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://rpsc.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://rpsc.rajasthan.gov.in/Static/Result/E8BDC9265C2B4202BE9C2DBEB2830182.pdf</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6478,16 +5776,6 @@
         </is>
       </c>
       <c r="O71" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -6519,7 +5807,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6539,22 +5827,22 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>12 October 2026</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://jam.iitkgp.ac.in/</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://jam.iitkgp.ac.in/</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://jam.iitkgp.ac.in/</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -6563,16 +5851,6 @@
         </is>
       </c>
       <c r="O72" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -6604,7 +5882,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Govt Board</t>
+          <t>Official Board</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6624,22 +5902,22 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>31 October 2026</t>
+          <t>https://clat2027.consortiumofnlus.ac.in/clat-2027/</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Notify Soon</t>
+          <t>https://consortiumofnlus.ac.in/clat-2026/</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://consortiumofnlus.ac.in/</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>https://consortiumofnlus.ac.in/</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -6648,16 +5926,6 @@
         </is>
       </c>
       <c r="O73" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>

--- a/data/verified_posts_master_sheet.xlsx
+++ b/data/verified_posts_master_sheet.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:S73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -442,16 +442,20 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="39" customWidth="1" min="11" max="11"/>
     <col width="45" customWidth="1" min="12" max="12"/>
     <col width="45" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="27" customWidth="1" min="15" max="15"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" min="17" max="17"/>
+    <col width="29" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,30 +506,50 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Fee Payment Last Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Exam / Event Date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Age Limits</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Application Fees</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Category Vacancies (UR/OBC/SC/ST)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Post Matrix &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Apply Online URL (Real)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notification PDF URL (Real)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Official Website URL (Real)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Result / Admit / Key URL (Real)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Check Sarkari Result URL (StudyTopper)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Verification Status</t>
         </is>
@@ -557,7 +581,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Himachal Pradesh High Court Various Post</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -567,40 +591,60 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>10 September 2026</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.hphcrecruitment.in/login</t>
+          <t>10 September 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://highcourt.hp.gov.in/</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://highcourt.hp.gov.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "45-50 Years (Category Wise)"}</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://highcourt.hp.gov.in/</t>
+          <t>{"Last Date Pay Exam Fee": "10 September 2026", "For General": "₹ 450/-", "For OBC, EWS, SC, ST, PH": "₹ 300/- (Only For Himanchal Pradesh Candidates)", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for HP High Court?", "Answer": "The age limit for Himachal Pradesh High Court Various Post Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Court Manager (Group -B)": "05 Posts", "Stenographer Grade-III (Group-C)": "79 Posts"}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
+        <is>
+          <t>[{"name": "Court Manager (Group -B)", "posts": "388 Posts", "eligibility": "Candidates must have passed the Graduation in any stream with MBA from a UGC-recognized University/Institution. 3 Years experience in Process Management, IT Systems Management, HR Management, or Financial Management."}, {"name": "Clerk (Group-C)", "posts": "388 Posts", "eligibility": "Candidates must have a Graduation Degree examination from any recognized board in India with basic knowledge of Computers (Windows/Linux OS, operating, typing, taking printouts. Typing speed of 30 WPM in English and 25 WPM in Hindi (Kruti Dev-10 font) on computer."}, {"name": "Stenographer Grade-III (Group-C)", "posts": "388 Posts", "eligibility": "Candidates must have a Graduation Degree examination from any recognized board in India. English Stenography Speed 80 WPM &amp; Typing Speed 40 WPM in English and 30 WPM in Hindi (Kruti Dev-10 font)."}, {"name": "Driver (Group-C)", "posts": "388 Posts", "eligibility": "Candidates must have passed the 10th (Matriculation) examination from any recognized board in India. Valid LMV Driving License with at least 3 Years driving experience."}, {"name": "Process Server (Group-D)", "posts": "388 Posts", "eligibility": "Candidates must have passed the 10+2 (Intermediate) examination from any recognized board in India"}, {"name": "Peon / Orderly / Chowkidar / Safai Karmchari / etc. (Group-D)", "posts": "388 Posts", "eligibility": "Candidates must have passed the 10+2 (Intermediate) examination from any recognized board in India"}]</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -632,7 +676,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>RCF Kapurthala Apprentice</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -642,40 +686,60 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>05 September 2026</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://pardarsy.railnet.gov.in/apprentice-2026/</t>
+          <t>05 September 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>http://www.rcf.indianrailways.gov.in/</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>http://www.rcf.indianrailways.gov.in/</t>
+          <t>{"Minimum Age": "15 Year", "Maximum Age": "24 Year", "Answer": "The age limit for RCF Kapurthala Apprentice Bharti 2026 is as follows on official website."}</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>http://www.rcf.indianrailways.gov.in/</t>
+          <t>{"Last Date For Fee Payment": "05 September 2026", "For General/ OBC/ EWS": "₹ 100/-", "For SC/ ST/ PH / Female": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Merit List": "Notify Later", "Question": "What is the official website for RCF?", "Answer": "Candidates must have passed 10th class, or ITI, from a recognized board/institution."}</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Machinist": "20"}</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
+        <is>
+          <t>[{"name": "Rail Coach Factory Kapurthala Apprentice", "posts": "368", "eligibility": "198"}, {"name": "RCF Kapurthala Apprentice", "posts": "734 Posts", "eligibility": "All candidates who have passed Class 10th from any recognized board in India are eligible to apply for this recruitment. Candidates must also possess an ITI Certificate in the relevant trade/branch."}]</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -707,7 +771,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Railway ICF Trade Apprentice</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -717,40 +781,60 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>07 September 2026</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://pb.icf.gov.in/act2026/apply.php</t>
+          <t>07 September 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>http://www.icf.indianrailways.gov.in/</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>http://www.icf.indianrailways.gov.in/</t>
+          <t>{"Age Limit": "15-22 Years (Non-ITI Candidate)", "Answer": "The age limit for Railway ICF Trade Apprentices Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>http://www.icf.indianrailways.gov.in/</t>
+          <t>{"Last Date For Fee Payment": "07 September 2026", "For General/ OBC/ EWS Candidates": "₹ 100/-", "For SC/ ST/PH Candidates": "₹ 00/-", "For All Female Category Candidates": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for Railway ICF?", "Answer": "Candidates must have Class 10 (Matric) with 50% marks and an ITI certificate in the relevant trade. For trade-wise eligibility, check the official notification."}</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "1010 Posts"}</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
+        <is>
+          <t>[{"name": "Apprentice (Fresher)", "posts": "1010 Posts", "eligibility": "Candidates must have Passed Class 10th with at least 50% marks and studied Science or Math in Class 12th."}, {"name": "Ex ITI", "posts": "1010 Posts", "eligibility": "Candidates must have Passed Class 10th with at least 50% marks and completed a 2-year ITI certificate in the relevant trade for the post."}]</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -782,7 +866,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>GIMS Noida Staff Nurse</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -792,40 +876,60 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>10 August 2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>07 September 2026</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://cdn3.digialm.com/EForms/configuredHtml/31586/101679/Index.html</t>
+          <t>07 September 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.gims.ac.in/recruitment.html</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://www.gims.ac.in/recruitment.html</t>
+          <t>{"For Minimum Age": "21 Years", "For Maximum Age": "40 Years"}</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.gims.ac.in/recruitment.html</t>
+          <t>{"Fee Payment Last Date": "07 September 2026", "General, OBC, EWS": "₹ 1298/-", "SC, ST": "₹ 944/-", "PH Candidates": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "For Degree Holder": "B.Sc Nursing (4-Year) or B.Sc Nursing (Post Basic) (2-Year) from an INC/State Council-recognized University/Institute + Registered as a Nurse &amp; Midwife with the State/Indian Nursing Council.", "For Diploma Holder": "Diploma in General Nursing Midwifery (GNM) from an INC-recognized Board/Council + Registered as Nurse &amp; Midwife with the State/Indian Nursing Council + 2 years’ experience in a minimum 50-bedded hospital after completing the diploma.", "Question": "What is the official website for GIMS Noida?", "Answer": "The eligibility criteria for the GIMS Noida Staff Nurse Vacancy 2026 are as follows on UPSSSC rules."}</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General": "40 Posts", "OBC": "27 Posts", "EWS": "10 Posts", "SC": "21 Posts", "ST": "02 Posts"}</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
+        <is>
+          <t>[{"name": "GIMS Noida Staff Nurse Recruitment 2026", "posts": "100 posts", "eligibility": "Passed 10th / 12th / Diploma / Bachelor Degree in relevant discipline from any recognized Board or University in India as per official notification."}]</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -857,7 +961,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UPSSSC Veterinary Pharmacist</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -867,40 +971,60 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>05 October 2026</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
+          <t>05 October 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in//default.aspx</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>http://upsssc.gov.in/Default.aspx</t>
+          <t>{"For Minimum Age": "18 Years", "For Maximum Age": "40 Years"}</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>http://upsssc.gov.in/Default.aspx</t>
+          <t>{"Fee Payment Last Date": "05 October 2026", "General, OBC, EWS": "₹ 25/-", "SC, ST": "₹ 25/-", "PH Candidates": "₹ 25/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in//default.aspx"}</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General": "576", "EWS": "130", "OBC": "359", "SC": "237", "ST": "06"}</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
+        <is>
+          <t>[{"name": "UPSSSC Veterinary Pharmacist Recruitment 2026", "posts": "1308 posts", "eligibility": "Passed 10th / 12th / Diploma / Bachelor Degree in relevant discipline from any recognized Board or University in India as per official notification."}]</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -932,7 +1056,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UPSSSC Junior Engineer JE (Agriculture)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -942,40 +1066,60 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>17 September 2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>07 October 2026</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
+          <t>07 October 2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in//default.aspx</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>http://upsssc.gov.in/Default.aspx</t>
+          <t>{"For Minimum Age": "18 Years", "For Maximum Age": "40 Years"}</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>http://upsssc.gov.in/Default.aspx</t>
+          <t>{"Fee Payment Last Date": "07 October 2026", "General, OBC, EWS": "₹ 25/-", "SC, ST": "₹ 25/-", "PH Candidates": "₹ 25/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in//default.aspx"}</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General": "54", "EWS": "13", "OBC": "43", "SC": "23", "ST": "01"}</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
+        <is>
+          <t>[{"name": "UPSSSC Junior Engineer JE (Agriculture) Recruitment 2026", "posts": "134 posts", "eligibility": "Passed 10th / 12th / Diploma / Bachelor Degree in relevant discipline from any recognized Board or University in India as per official notification."}]</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1007,7 +1151,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>RRVUNL JE, Junior Assistant</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1017,40 +1161,60 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>05 August 2026</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>25 August 2026</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://ibpsreg.ibps.in/rrvunljun26/</t>
+          <t>25 August 2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>Notify Later</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>{"Last Date For Fee Payment": "25 August 2026", "For General": "₹ 1000/-", "For MBC/ BC / EWS": "₹ 500/-", "For SC/ ST/ PH Candidates": "₹ 500/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Junior Accountant &amp; Junior Assistant/ Commercial Assistant-II": "18-40 Years", "You May Also Check": "SSC CGL Recruitment 2026", "Question": "What is the official website for RRVUNL ?", "Answer": "The official website for RRVUNL is https://energy.rajasthan.gov.in/rrvun/#/pages/sm/department-page/373376/2700"}</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>{"Junior Assistant/ Commercial Assistant-II": "765"}</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>[{"name": "JEN-I (Electrical)", "posts": "2005 vacancies", "eligibility": "The candidate must hold Full Time four years’ Graduation Degree in Engineering as a regular student or AMIE in Electrical/ Electrical &amp; Electronics/ Electrical, Instrumentation &amp; Control/ Power Systems &amp; High Voltage/Power Electronics/ Power Engineering or equivalent from a University/Institution established by Law in India and recognized equivalent to full time Graduation Degree in Engineering by AICTE, New Delhi"}, {"name": "JEN-I (Mechanical)", "posts": "2005 vacancies", "eligibility": "The candidate must hold Full Time four years’ Graduation Degree in Engineering as a regular student or AMIE in Mechanical/ Production/ Industrial Engineering/ Production &amp; Industrial/ Thermal/ Mechanical &amp; Automation/ Power Engineering or equivalent from a University/Institution established by Law in India and recognized equivalent to full time Graduation Degree in Engineering by AICTE, New Delhi."}, {"name": "JEN-I (Civil)", "posts": "2005 vacancies", "eligibility": "The candidate must hold Full Time four years’ Graduation Degree in Engineering as a regular student or AMIE in Structural/Civil Construction/Civil Engineering or equivalent from a University/Institution established by Law in India and recognized equivalent to full time Graduation Degree in Engineering by AICTE, New Delhi."}, {"name": "Junior Accountant", "posts": "2005 vacancies", "eligibility": "Candidates must have a Graduation degree in Commerce or Business Administration, Intermediate (CA/ICWA), MBA, or M.Com. from a recognized university. Candidates must also possess a valid computer qualification such as DOEACC ‘O’ Level or higher, NIELIT CCC, COPA/DPCS, Degree/Diploma/Certificate in Computer Science/Computer Applications, RSCIT, or any other equivalent computer qualification recognized by the Government."}, {"name": "Junior Assistant/ Commercial Assistant-II", "posts": "2005 vacancies", "eligibility": "Candidates must have passed the Senior Secondary (10+2) Examination from a recognized board or equivalent and possess a valid computer qualification such as DOEACC ‘O’ Level or higher, NIELIT CCC, COPA/DPCS, Degree/Diploma/Certificate in Computer Science/Computer Applications, RSCIT, or any other equivalent computer qualification recognized by the Government."}]</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>https://energy.rajasthan.gov.in/rrvun/#/pages/sm/department-page/373376/2700</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://energy.rajasthan.gov.in/rrvun/#/pages/sm/department-page/373376/2700</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1082,50 +1246,70 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UP Anganwadi Bharti Examination 2025</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Various Posts</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>November 2025</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://upanganwadibharti.in/users/registration.php</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>{"For Minimum Age": "18 years", "For Maximum Age": "35 years", "Answer": "The age limit for candidates applying for this recruitment is as per the rules of UP Anganwadi. For detailed age information, please refer to the official notification."}</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>{"General / OBC / EWS": "Rs. 100/- (As per rules)", "SC / ST / PwD": "Rs. 0/- (Exempted)", "All Category Female": "Rs. 0/- (Exempted)", "Payment Mode": "Online via Net Banking, Debit Card, Credit Card or UPI", "Application Start": "November 2025", "Question": "What is the official website of UP Anganwadi? Answer: The official website of UP Anganwadi is https://upanganwadibharti.in/.", "Answer": "The online application for this recruitment started in November 2025."}</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>[{"name": "District Name", "posts": "2482 Posts", "eligibility": "Last Date"}]</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>http://upanganwadibharti.in/</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>http://upanganwadibharti.in/</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>http://upanganwadibharti.in/</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1157,17 +1341,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UPSSSC PET</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Various Posts</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1177,30 +1361,50 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/AllNotifications.aspx</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/ViewPdf.aspx?mQakfo5LrW2Cdx4YG2/st+GVGmBBNX8aG1X69whn6lU=</t>
+          <t>Update Soon</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>{"For Minimum Age": "18 Years", "For Maximum Age": "40 Years"}</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>{"Last Date Pay Exam Fee": "01 September 2026", "For General, OBC": "₹ 185/-", "For SC, ST": "₹ 95/-", "For PH": "₹ 25/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Application Start": "03 August 2026", "Question": "What is the official website of UPSSSC?", "Answer": "The official website of UPSSSC is https://upsssc.gov.in/."}</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>[{"name": "Pre Examination Test UPSSSC PET 2026", "posts": "2482 Posts", "eligibility": "Candidates must have passed at least the Class 10 (High School) exam from any recognized board, or hold any higher qualification from a recognized university in India."}]</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>https://upsssc.gov.in/</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://upsssc.gov.in/</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1232,7 +1436,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>MP High Court Assistant Grade III</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1242,40 +1446,60 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://cdn.digialm.com//EForms/configuredHtml/772/101789/Registration.html</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://mphc.gov.in/</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://mphc.gov.in/</t>
+          <t>{"Minimum Age": "18 Year", "Maximum Age": "40 – 45 Year"}</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://mphc.gov.in/</t>
+          <t>{"Last Date For Fee Payment": "15 September 2026", "For General/ Other State": "₹ 943.40/-", "For SC/ ST/ OBC/ EWS": "₹ 743.40/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for MPHC?", "Answer": "The eligibility for MP High Court Assistant Grade III Bharti 2026 is as follows post wise."}</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"High Court Assistant Grade III": "1174 Posts"}</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
+        <is>
+          <t>[{"name": "High Court Assistant Grade III", "posts": "1174 Posts", "eligibility": "Graduation in any discipline from a recognized University + Valid CPCT Score Card from MAP-IT or an M.P. Government-recognized agency/institution + 1-Year Diploma in Computer Application (DCA) from an M.P. Government-recognized institution."}]</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1307,7 +1531,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>MPESB Group 3 Sub Engineer &amp; Other Post</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1317,40 +1541,60 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://esb.mponline.gov.in/Portal/Examinations/Vyapam/examsList.aspx</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://esb.mp.gov.in/e_default.html</t>
+          <t>06 October 2026</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://esb.mp.gov.in/e_default.html</t>
+          <t>{"Minimum Age": "18 Years", "Minimum age required is 18 Years &amp; The Maximum Age Is 40": "45 Years Category Wise as on 01 January 2026."}</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://esb.mp.gov.in/e_default.html</t>
+          <t>{"Last Date For Fee Payment": "01 September 2026", "For General / Other State": "Rs. 500/-", "For SC / ST/ OBC": "Rs. 250/-", "For Portal Charge Extra": "Rs. 60/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "Maximum Age": "45 Years (SC, ST, OBC, PwBD &amp; All Female)", "You May Also Check": "Rajasthan High Court Stenographer Recruitment 2026", "Question": "What is the official website for MPESB?", "Answer": "Candidates must have a Bachelor’s Degree in any discipline from a university recognized by the Government of India."}</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"UR": "608", "OBC": "272", "EWS": "90", "SC": "156", "ST": "141"}</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
+        <is>
+          <t>[{"name": "Group 3 Sub Engineer &amp; Other Post", "posts": "1040 Posts", "eligibility": "Candidates must have a Bachelor’s Degree, ITI &amp; Dipolma in any discipline from a university recognized by the Government of India."}]</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1382,7 +1626,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>RSSB Junior Engineer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1392,40 +1636,60 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>16 August 2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://sso.rajasthan.gov.in/</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://rssb.rajasthan.gov.in/</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://rssb.rajasthan.gov.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Answer": "The age limit for RSSB Junior Engineer Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://rssb.rajasthan.gov.in/</t>
+          <t>{"Last Date For Fee Payment": "14 September 2026", "For General, EWS, OBC (Creamy Layer)": "₹ 600/-", "For EWS, OBC (Non Creamy Layer)": "₹ 400/-", "For SC, ST, PH": "₹ 400/-", "For Correction Charge": "₹ 300/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "BPSC School Teacher TRE 4.0 Recruitment 2026", "Question": "What is the official website for RSSB?", "Answer": "The official website for RSSB is https://rssb.rajasthan.gov.in/"}</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "874 Posts"}</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
+        <is>
+          <t>[{"name": "Junior Engineer", "posts": "874 Posts", "eligibility": "Candidates must have completed their Degree or Diploma in Engineering from a university established by law in India or from a recognized Institution. Practical knowledge of Hindi written in Devanagari script and knowledge of Rajasthani culture. Read Official Notification For Post Wise Qualification."}]</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1457,7 +1721,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>MPESB Group-2 Sub Group-4 Patwari</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1467,40 +1731,60 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>04 August 2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>23 August 2026 Extended</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://esb.mponline.gov.in/Portal/Examinations/Vyapam/examsList.aspx</t>
+          <t>23 August 2026 Extended</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://esb.mp.gov.in/e_default.html</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://esb.mp.gov.in/e_default.html</t>
+          <t>{"Minimum Age": "18 Years", "MPESB provides age relaxation for the Group": "2 Sub Group-4 Patwari as per their regulations.", "Minimum age required is 18 Years &amp; The Maximum Age Is 40": "45 Years Category Wise as on 01 January 2026.", "Answer": "The age limit for MPESB Group-2 Sub Group-4 Patwari Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://esb.mp.gov.in/e_default.html</t>
+          <t>{"Last Date For Fee Payment": "23 August 2026", "For General / Other State": "Rs. 500/-", "For SC / ST/ OBC": "Rs. 250/-", "For Portal Charge Extra": "Rs. 60/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "Maximum Age": "45 Years (SC, ST, OBC, PwBD &amp; All Female)", "You May Also Check": "Rajasthan High Court Stenographer Recruitment 2026", "Question": "What is the official website for MPESB?", "Answer": "Candidates must have a Bachelor’s Degree in any discipline from a university recognized by the Government of India."}</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"UR": "608 Posts", "OBC": "613 Posts", "EWS": "207 Posts", "SC": "274 Posts", "ST": "404 Posts"}</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
+        <is>
+          <t>[{"name": "Group-2 Sub Group-4 Patwari", "posts": "2106 Posts", "eligibility": "Candidates must have a Bachelor’s Degree in any discipline from a university recognized by the Government of India or possess an equivalent qualification approved by the Central Government. CPCT Scorecard (Hindi Typing &amp; Computer Efficiency)"}]</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1532,7 +1816,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UPPSC Professor &amp; Assistant Professor</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1542,40 +1826,60 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/</t>
+          <t>{"Minimum Age": "35 Years", "Maximum Age": "55 Years"}</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
+          <t>{"Last Date For Fee Payment": "01 September 2026", "For General / OBC / EWS": "₹ 105/-", "For SC / ST": "₹ 65/-", "For PH": "₹ 25/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for UPPSC?", "Answer": "The official website for UPPSC is https://uppsc.up.nic.in/"}</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Assistant Professor": "1112"}</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
+        <is>
+          <t>[{"name": "Professor &amp; Assistant Professor", "posts": "1156 vacancies", "eligibility": "Candidates must have a Master’s Degree (MD/MS/DNB) in the relevant medical specialty. Post-wise experience requirements are given in the official notification."}]</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1607,7 +1911,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>BOB Local Bank Officer LBO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1617,40 +1921,60 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>18 August 2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>07 September 2026</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://ibpsreg.ibps.in/bobjul26/</t>
+          <t>07 September 2026</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://bankofbaroda.bank.in/-/media/Project/BOB/CountryWebsites/India/Career/2026/26-08/Advertisement-18-04.pdf</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://www.bankofbaroda.in/</t>
+          <t>{"Minimum Age": "21 Years", "Maximum Age": "30 Years", "Answer": "The age limit for BOB Local Bank Officer LBO Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.bankofbaroda.in/</t>
+          <t>{"Last Date For Fee Payment": "07 September 2026", "For General, OBC, EWS": "₹ 850/-", "For SC / ST, PwBD/": "₹ 175/-", "For All Female": "₹ 175/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "MP High Court Assistant Grade III Recruitment 2026", "Question": "What is the official website for BOB?", "Answer": "The eligibility for BOB Local Bank Officer LBO Bharti 2026 is as follows post wise."}</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
+        <is>
+          <t>[{"name": "Local Bank Officer (LBO)", "posts": "2482 Posts", "eligibility": "Candidates must have Graduation degree in any discipline from a recognized University/Institution. with at least 1 year of experience as an officer in a Scheduled or Regional Rural Bank. Proficiency in the local language is required."}]</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1682,17 +2006,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UPSSSC PET</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Exam Syllabus</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1702,30 +2026,50 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/AllNotifications.aspx</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/ViewPdf.aspx?mQakfo5LrW2Cdx4YG2/st+GVGmBBNX8aG1X69whn6lU=</t>
+          <t>Update Soon</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>{"For Minimum Age": "18 Years", "For Maximum Age": "40 Years"}</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>{"Last Date Pay Exam Fee": "01 September 2026", "For General, OBC": "₹ 185/-", "For SC, ST": "₹ 95/-", "For PH": "₹ 25/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Application Start": "03 August 2026", "Question": "What is the official website of UPSSSC?", "Answer": "The official website of UPSSSC is https://upsssc.gov.in/."}</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>[{"name": "Pre Examination Test UPSSSC PET 2026", "posts": "2482 Posts", "eligibility": "Candidates must have passed at least the Class 10 (High School) exam from any recognized board, or hold any higher qualification from a recognized university in India."}]</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>https://upsssc.gov.in/</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>https://upsssc.gov.in/</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1757,7 +2101,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Railway RRB Junior Engineer JE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1777,30 +2121,50 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.rrbapply.gov.in/#/auth/landing</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "33 years", "Answer": "The age limit for RRB Junior Engineer JE Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>{"Last Date for Fee Payment": "15 September 2026", "For General / OBC / EWS": "₹ 500/-", "For SC / ST / EBC": "₹ 250/-", "For All Category female": "₹ 250/-", "Fess Refund": "General / OBC : Rs. 400/- will be refunded and Other candidates : Rs. 250/- will be refunded to the bank account after appearing in Stage I Exam.", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for RRB?", "Answer": "Candidates must have passed the Engineering Diploma / Degree, specific qualifications exam from any recognized board in India. For full eligibility details, please check the official notification."}</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "4029 Posts"}</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
+        <is>
+          <t>[{"name": "Junior Engineer JE", "posts": "4029 Posts", "eligibility": "EWS"}, {"name": "1714", "posts": "398", "eligibility": "919"}]</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1832,7 +2196,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Railway RRB Junior Engineer JE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1852,30 +2216,50 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.rrbapply.gov.in/#/auth/landing</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "33 years", "Answer": "The age limit for RRB Junior Engineer JE Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>{"Last Date for Fee Payment": "15 September 2026", "For General / OBC / EWS": "₹ 500/-", "For SC / ST / EBC": "₹ 250/-", "For All Category female": "₹ 250/-", "Fess Refund": "General / OBC : Rs. 400/- will be refunded and Other candidates : Rs. 250/- will be refunded to the bank account after appearing in Stage I Exam.", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for RRB?", "Answer": "Candidates must have passed the Engineering Diploma / Degree, specific qualifications exam from any recognized board in India. For full eligibility details, please check the official notification."}</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "4029 Posts"}</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
+        <is>
+          <t>[{"name": "Junior Engineer JE", "posts": "4029 Posts", "eligibility": "EWS"}, {"name": "1714", "posts": "398", "eligibility": "919"}]</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1907,17 +2291,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>IIM CAT Admissions</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1927,30 +2311,50 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://iimcat.ac.in/per/g06/pub/32842/ASM/WebPortal/1/index.html?32842@@1@@1</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://gate2027.iitm.ac.in/</t>
+          <t>29 November 2026</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://iimcat.ac.in/</t>
+          <t>{"Maximum Age": "N/A", "Answer": "The age limit for candidates applying for this exam is as per the IIM CAT rules. For detailed age-related information, refer to the official notification."}</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://iimcat.ac.in/</t>
+          <t>{"General, OBC,": "₹ 2700/-", "SC, ST, PWD": "₹ 1350/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "MPESB Group 4 Various Post Online Form 2025", "Question": "What is the official website of IIM CAT?", "Answer": "Candidates must have passed Graduate from any recognized board in India. For detailed course-wise eligibility, refer to the official notification."}</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
+        <is>
+          <t>[{"name": "Post Graduate Programmes in Management (PGP)", "posts": "2482 Posts", "eligibility": "Candidate must hold a Bachelor’s Degree, with at least 50% marks or equivalent CGPA [45% in case of the candidates belonging to Scheduled Caste (SC), Scheduled Tribe (ST) and Persons With Disability (PWD) categories], awarded by any University or educational institution as incorporated by an Act of the Parliament or State legislature in India or declared to be deemed as a University under Section 3 of the UGC Act, 1956, or possess an equivalent qualification recognized by the Ministry of HRD, Government of India."}, {"name": "Fellowship Programmes in Management (FPM) / (PHD)", "posts": "2482 Posts", "eligibility": "Candidates appearing for the final year of Bachelor’s degree/equivalent qualification examination and those who have completed degree requirements and are awaiting results can also apply. However, it may be noted that such candidates, if selected, will be allowed to join the programme provisionally, only if they submit a certificate from the Principal / Registrar of their University/institution (issued on or before the date as stipulated by the respective IIM) stating that they have completed all the requirements for obtaining the Bachelor’s degree/equivalent qualification on the date of the issue of the certificate."}]</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -1982,7 +2386,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>SSC 10+2 CHSL Examination 2025</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1992,40 +2396,60 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>23 June 2025</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>18 July 2025</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://ssc.gov.in/candidate-portal/one-time-registration/home-page</t>
+          <t>18 July 2025</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>http://sarkariresult.com.cm/wp-content/uploads/2025/06/Notice_of_adv_chsl_2025-1.pdf</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://ssc.gov.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "27 Years"}</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://ssc.gov.in/api/attachment/uploads/masterData/Results/ROLL_17082026.pdf</t>
+          <t>{"Last Date For Fee Payment": "19 July 2025", "For General/ OBC/ EWS": "₹ 100/-", "For SC/ ST/ Female": "₹ 0/-", "For PH Candidates": "₹ 0/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Tier-I Exam Start": "12 November 2025", "Post Preference Cum Option Form": "19 – 25 June 2026", "Question": "What is the official website for SSC?", "Answer": "The official website for SSC is https://ssc.gov.in/"}</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"SSC CHSL": "3522"}</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
+        <is>
+          <t>[{"name": "LDC &amp; PA/ SA", "posts": "3522 Posts", "eligibility": "Candidates must have passed the 12th class (also known as Intermediate) examination from any recognized board in India to be eligible for the post."}, {"name": "DEO", "posts": "3522 Posts", "eligibility": "Candidates must have passed 12th standard in the Science stream with Mathematics as one of the subjects from a recognized board or its equivalent."}]</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2057,7 +2481,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Bihar Police CSBC Constable Examination 2025</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2067,40 +2491,60 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>06 October 2025</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>05 November 2025</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://apply-csbc.com/csbc_3_25_mv1/applicationIndex</t>
+          <t>05 November 2025</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://csbc.bihar.gov.in/Advt/Advt-03-2025-Prohibition-Jail%20Warder-Mobile%20Squad-Constables.pdf</t>
+          <t>14 – 17 June 2026</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://csbc.bihar.gov.in/A-REP.htm</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://csbc.bihar.gov.in/Advt/Results-03-2025-PET-18-08-2026.pdf</t>
+          <t>{"Last Date For Fee Payment": "05 November 2025", "All Candidates": "₹ 100/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "General (Male)": "18 – 23 years", "OBC / EBC (Male)": "18 – 25 years", "OBC / EBC (Female)": "18 – 26 years", "SC / ST (Male &amp; Female)": "18 – 28 years", "You May Also Check": "DSSSB Non-Teaching Various Post Online Form 2025", "Question": "What is the official website for CSBC ?", "Answer": "The notification is generally released in PDF format."}</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Prohibition Constable": "1685", "Jail Warder (Daroga / Security Services)": "2417", "Mobile Squad Constable": "108"}</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
+        <is>
+          <t>[{"name": "Prohibition Constable", "posts": "4210 Posts", "eligibility": "Candidates must have passed 10+2 (Intermediate) or its equivalent examination from a recognized board or institution."}]</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2132,7 +2576,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>RPSC SI Telecom Examination 2025</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2142,40 +2586,60 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>28 November 2024</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>27 December 2024</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://sso.rajasthan.gov.in/signin</t>
+          <t>27 December 2024</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://rpsc.rajasthan.gov.in/</t>
+          <t>09 November 2025</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://rpsc.rajasthan.gov.in/</t>
+          <t>{"Minimum Age": "20 Years", "Maximum Age": "25 Years"}</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://rpsc.rajasthan.gov.in/Static/Result/E8BDC9265C2B4202BE9C2DBEB2830182.pdf</t>
+          <t>{"Last Date For Fee Payment": "27 December 2024", "For General, Other State": "₹ 600/-", "For SC / ST, OBC / BC": "₹ 400/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for RPSC?", "Answer": "The official website for RPSC is https://rpsc.rajasthan.gov.in/"}</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"RPSC Rajasthan Police SI": "98"}</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
+        <is>
+          <t>[{"name": "RPSC Rajasthan Police SI", "posts": "98 Post", "eligibility": "Candidates possessing a B.Sc. degree with Physics and Mathematics or a B.E./B.Tech degree in Electrical Engineering (EE) or Electronics and Communication Engineering (ECE) from any recognized university or college will be considered eligible for this post. All applicants are advised to carefully read the official notification in full before applying."}]</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2207,7 +2671,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Rajasthan Safai Karmchari</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2217,40 +2681,60 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://sso.rajasthan.gov.in/signin?encq=6JkTF7D/fPuyiLpqlTuv+tsssIL22cKEce/qYZMZKsM=</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>{"Minimum Age": "21 Years.", "Maximum Age": "40 Years.", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>{"Last Date For Fee Payment": "28 September 2026", "General, Other State": "₹ 600/-", "OBC, BC, SC, ST": "₹ 400/-", "Correction Charge": "₹ 100/-", "Minimum Age": "21 Years.", "Maximum Age": "40 Years.", "Question": "What is the official website for Rajasthan Safai Karmchari?", "Answer": "The official website for Rajasthan Safai Karmchari is https://lsg.rajasthan.gov.in/lsg/#/home/dptHome"}</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "24,752 posts"}</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>[{"name": "Rajasthan Safai Karmchari Recruitment 2026 Syllabus &amp; Exam Pattern 2026", "posts": "24,752 posts", "eligibility": "Passed 10th / 12th / Diploma / Bachelor Degree in relevant discipline from any recognized Board or University in India as per official notification."}]</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2282,7 +2766,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UPSC EPFO EO / AO / APFC</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2292,40 +2776,60 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>11 September 2026</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
+          <t>11 September 2026</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.upsc.gov.in/</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://upsc.gov.in/</t>
+          <t>{"Minimum Age": "18 Years (Tentative)", "Maximum Age": "35-40 Years (Category Wise)", "The Minimum age required is 18 Years &amp; The Maximum Age Is 35": "40 Years as on 11 September 2026."}</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://upsc.gov.in/</t>
+          <t>{"Last Date For Fee Payment": "11 September 2026", "For General / OBC / EWS": "₹ 25/-", "For SC / ST": "₹ 00/-", "For PH": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "You May Also Check": "UPPSC Professor &amp; Assistant Professor Recruitment 2026", "Question": "What is the official website for UPSC?", "Answer": "The official website for UPSC is https://www.upsc.gov.in/"}</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General": "29", "EWS": "08", "OBC": "18", "SC": "15", "ST": "10"}</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
+        <is>
+          <t>[{"name": "Enforcement Officer / Accounts Officer", "posts": "80 vacancies", "eligibility": "Candidates must have a Bachelor’s degree from a recognized university."}, {"name": "Assistant Provident Fund Commissioner", "posts": "80 vacancies", "eligibility": "Candidates must have a Bachelor’s degree from any recognized university."}]</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2357,7 +2861,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>IBPS Clerk (CSA) 16th</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2367,40 +2871,60 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>21 August 2026</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://ibpsreg.ibps.in/csaxvijul26/</t>
+          <t>21 August 2026</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://ibps.in/</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>{"Minimum Age": "20 Years", "Maximum Age": "28 Years", "Answer": "The age limit for IBPS Clerk (CSA) 16th Bharti 2026 is as follows:"}</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>{"Pay Exam Fee Last Date": "21 August 2026", "For General, OBC, EWS": "₹ 850/-", "For SC, ST, ESM &amp; DESM": "₹ 175/-", "For PH Candidates": "₹ 175/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Computer Literacy": "Operating And Working Knowledge In Computer Systems is Mandatory ie. Candidates Should Have Certificate/ Diploma/ Degree in Computer Operations/ Language/ Should Have Studied Computer / Information Technology As One of the Subjects In The High School/ College/ Institute.", "Question": "What is the official website for IBPS?", "Answer": "The eligibility criteria for the IBPS Clerk (CSA) 16th Vacancy 2026 are as follows on UPSSSC rules."}</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "11,403 Posts"}</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>[{"name": "Clerk CSA XV", "posts": "4740", "eligibility": "2815"}]</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
           <t>https://www.ibps.in/</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>https://www.ibps.in/</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2432,7 +2956,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>SBI Junior Associates Clerk</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2442,40 +2966,60 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>11 August 2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>31 August 2026</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>31 August 2026</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>https://ibpsreg.ibps.in/sbijajul26/</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>https://sbi.bank.in/web/careers/current-openings</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://sbi.bank.in/web/careers/current-openings</t>
+          <t>{"Minimum Age": "20 Years", "Maximum Age": "28 Years", "Answer": "The age limit for SBI Junior Associates Clerk Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://sbi.bank.in/web/careers/current-openings</t>
+          <t>{"Last Date For Fee Payment": "31 August 2026", "For OBC": "₹ 750/-", "For SC / ST, PH": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "UPSSSC Cane Supervisor Recruitment 2026", "Question": "What is the official website for SBI?", "Answer": "The eligibility criteria for the SBI Junior Associates Clerk Vacancy 2026 are as follows: Candidates must have a graduation degree in any field from a recognized university."}</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "9124 Posts"}</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
+        <is>
+          <t>[{"name": "Junior Associates Clerk", "posts": "3253", "eligibility": "760"}]</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2507,7 +3051,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>BPSC School Teacher TRE 4.0 Examination 2025</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2517,40 +3061,60 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>http://www.bpsc.bih.nic.in/</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>http://www.bpsc.bih.nic.in/</t>
+          <t>{"Minimum Age": "21 Years (Class 9 to 10 &amp; 11 to 12)", "Maximum Age": "37 Years (UR-Male)"}</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>http://www.bpsc.bih.nic.in/</t>
+          <t>{"Last Date For Fee Payment": "29 September 2026", "For All Category Candidates": "₹ 100/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum Age": "42 Years (SC/ ST-Male &amp; Female)", "You May Also Check": "Rajasthan High Court Class VI Employees Peon Recruitment 2025", "Question": "What is the official website for BPSC ?", "Answer": "The official website for BPSC is http://www.bpsc.bih.nic.in/"}</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "32,388 Posts"}</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
+        <is>
+          <t>[{"name": "School Teacher (Class 1 to 5)", "posts": "32,388 Posts", "eligibility": "Bachelor Degree with 50% Marks and B.Ed Degree OR Bachelor Degree in Any Stream with Diploma in Elementary Education OR 10+2 Inter with 50% Marks with 2 Year Diploma in Elementary Education / Special Diploma OR 10+2 Inter with 45% Marks (As per 2002 Norms) with 2 Year Diploma in Elementary Education OR 10+2 Inter with 50% Marks with 4 Year BLEd Degree OR Master Degree with 55% Marks and B.Ed – Med 3 Year Degree CTET Paper I OR BTET Paper I Exam Qualified."}, {"name": "Middle School Teacher (Class 6 to 8)", "posts": "32,388 Posts", "eligibility": "Graduate with 2 Year Diploma in Elementry Education (D.Ed) OR Graduate / Post Graduate with 50% Marks with B.Ed OR Graduate with 45% Marks and B.Ed (NCTE Norms) OR Graduate with 50% Marks and BA BED and B.Sc Ed OR Graduate with 50% Marks and B.Ed Special OR Post Graduate with 55% Marks and 3 Year B.Ed – M.Ed Course. Form More Details, Read Official Notification."}, {"name": "School Teacher (Class 6 to 10)", "posts": "32,388 Posts", "eligibility": "Graduate / Post Graduate in Related Subject with Minimum 50% Marks and B.Ed Degree OR Graduate / Post Graduate in Related Subject with Minimum 45% Marks (As per 2002 Norms) and B.Ed Degree OR 4 Year Degree in BAEd / BScEd STET Paper I Exam Passed Form More Details, Read Official Notification."}, {"name": "Secondary School Teacher (TGT) (Class 9 to 10)", "posts": "32,388 Posts", "eligibility": "Graduate / Post Graduate in Related Subject with Minimum 50% Marks and B.Ed Degree OR Graduate / Post Graduate in Related Subject with Minimum 45% Marks (As per 2002 Norms) and B.Ed Degree OR 4 Year Degree in BAEd / BScEd STET Paper I Exam Passed (Subject Wise) Form More Details, Read Official Notification."}, {"name": "Secondary School Teacher (TGT)-Special (Class 9 to 10)", "posts": "32,388 Posts", "eligibility": "Graduate / Post Graduate in Related Subject with Minimum 50% Marks and B.Ed Degree OR Graduate / Post Graduate Degree in Related Subject with Minimum 45% Marks (As per 2002 Norms) and B.Ed Degree OR 4 Year Degree in BAEd / BScEd STET Paper I Exam Passed (Subject Wise)"}, {"name": "10+2 School Teacher (PGT) (Class 11 to 12)", "posts": "32,388 Posts", "eligibility": "Post Graduate in Related Subject with Minimum 50% Marks and B.Ed Degree OR Post Graduate in Related Subject with Minimum 45% Marks (As per 2002 Norms) and B.Ed Degree OR Post Graduate in Related Subject with 4 Year Degree in BAEd / BScEd OR Master Degree with 55% Marks and B.Ed – Med 3 Year Degree. STET Paper II Exam Passed Form More Details, Read Official Notification."}]</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2582,7 +3146,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>IBPS Clerk (CSA) 16th</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2592,40 +3156,60 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>21 August 2026</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://ibpsreg.ibps.in/csaxvijul26/</t>
+          <t>21 August 2026</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://ibps.in/</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>{"Minimum Age": "20 Years", "Maximum Age": "28 Years", "Answer": "The age limit for IBPS Clerk (CSA) 16th Bharti 2026 is as follows:"}</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>{"Pay Exam Fee Last Date": "21 August 2026", "For General, OBC, EWS": "₹ 850/-", "For SC, ST, ESM &amp; DESM": "₹ 175/-", "For PH Candidates": "₹ 175/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Computer Literacy": "Operating And Working Knowledge In Computer Systems is Mandatory ie. Candidates Should Have Certificate/ Diploma/ Degree in Computer Operations/ Language/ Should Have Studied Computer / Information Technology As One of the Subjects In The High School/ College/ Institute.", "Question": "What is the official website for IBPS?", "Answer": "The eligibility criteria for the IBPS Clerk (CSA) 16th Vacancy 2026 are as follows on UPSSSC rules."}</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "11,403 Posts"}</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>[{"name": "Clerk CSA XV", "posts": "4740", "eligibility": "2815"}]</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
           <t>https://www.ibps.in/</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>https://www.ibps.in/</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2657,7 +3241,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UPSC EPFO EO / AO / APFC</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2667,40 +3251,60 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>11 September 2026</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
+          <t>11 September 2026</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.upsc.gov.in/</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://upsc.gov.in/</t>
+          <t>{"Minimum Age": "18 Years (Tentative)", "Maximum Age": "35-40 Years (Category Wise)", "The Minimum age required is 18 Years &amp; The Maximum Age Is 35": "40 Years as on 11 September 2026."}</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://upsc.gov.in/</t>
+          <t>{"Last Date For Fee Payment": "11 September 2026", "For General / OBC / EWS": "₹ 25/-", "For SC / ST": "₹ 00/-", "For PH": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "You May Also Check": "UPPSC Professor &amp; Assistant Professor Recruitment 2026", "Question": "What is the official website for UPSC?", "Answer": "The official website for UPSC is https://www.upsc.gov.in/"}</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General": "29", "EWS": "08", "OBC": "18", "SC": "15", "ST": "10"}</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
+        <is>
+          <t>[{"name": "Enforcement Officer / Accounts Officer", "posts": "80 vacancies", "eligibility": "Candidates must have a Bachelor’s degree from a recognized university."}, {"name": "Assistant Provident Fund Commissioner", "posts": "80 vacancies", "eligibility": "Candidates must have a Bachelor’s degree from any recognized university."}]</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2732,7 +3336,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>SKAU Kurukshetra Non Teaching Post</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2742,40 +3346,60 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>21 August 2026</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://recruitment.skau.ac.in/nonteaching/</t>
+          <t>21 August 2026</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>{"Minimum Age": "42 Years"}</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>{"Last Date For Fee Payment": "21 August 2026", "For General / Other State": "₹ 1580/- (For Male)", "For General": "₹ 750/- (For Female Domicile)", "For Haryana Reserve Category": "₹ 375/- (Male &amp; Female)", "For PH Candidates": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "SSC CGL Recruitment 2026", "Question": "What is the official website for SKAU?", "Answer": "The eligibility for SKAU Kurukshetra Non Teaching Post Bharti 2026 is as follows post wise."}</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>{"Ayurvedic Pharmacist": "06 Posts", "Staff Nurse": "25 Posts"}</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>[{"name": "Ayurvedic Pharmacist", "posts": "60 Posts", "eligibility": "Candidates must have passed Class 10th (Matriculation) and possess UP-Vaidya qualification from a recognized university in India, or 10+2 with PCB subjects and a Diploma in Ayurvedic Pharmacy. Hindi and Sanskrit must have been studied at the Matric, 10+2, or UG/PG level."}, {"name": "Staff Nurse", "posts": "60 Posts", "eligibility": "Candidates must have passed Class 10th (Matriculation) and be registered with the Haryana Nurses Council. Hindi and Sanskrit must have been studied as a subject at the Matric, 10+2, or UG/PG level."}, {"name": "Clerk", "posts": "60 Posts", "eligibility": "Candidates must have a Bachelor’s Degree in any stream from a recognized university, along with a skill test speed of 30 WPM. Hindi and Sanskrit must have been studied as a subject at the Matric, 10+2, or UG/PG level."}]</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
           <t>https://skau.ac.in/</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>https://skau.ac.in/</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>https://skau.ac.in/</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2807,7 +3431,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>RPSC Physiotherapist</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2817,40 +3441,60 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>23 July 2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>21 August 2026</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://sso.rajasthan.gov.in/signin?encq=6JkTF7D/fPuyiLpqlTuv+tsssIL22cKEce/qYZMZKsM=</t>
+          <t>21 August 2026</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://rpsc.rajasthan.gov.in/</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://rpsc.rajasthan.gov.in/home</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years"}</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://rpsc.rajasthan.gov.in/home</t>
+          <t>{"Last Date For Fee Payment": "21 August 2026", "For General, (BC, EBC Creamy Layer) &amp; Other State": "₹ 600/-", "For SC / ST, (OBC, EBC Non Creamy Layer) / PH": "₹ 400/-", "For Correction Charge": "₹ 500/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "RSSB Computer Instructor Recruitment 2026", "Question": "What is the official website for RPSC ?", "Answer": "The official website for RPSC is https://rpsc.rajasthan.gov.in/"}</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Rajasthan Physiotherapist": "20 Posts"}</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
+        <is>
+          <t>[{"name": "Rajasthan Physiotherapist", "posts": "20 Posts", "eligibility": "Candidates must have a 12th intermediate with Diploma in Physiotherapy of a University Working knowledge of Hindi written in Devnagari Script and knowledge of Rajasthani culture. All candidates must read the official information completely before applying."}]</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2882,7 +3526,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>ISRO Assistant &amp; Junior Personal Assistant</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2892,40 +3536,60 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>27 July 2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>20 August 2026 Extended</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://cdn.digialm.com//EForms/configuredHtml/1258/101396//Index.html</t>
+          <t>20 August 2026 Extended</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.isro.gov.in/media_isro/pdf/recruitmentNotice/2026/July/Bilingual%20Advertisement_Asst_JPA_UDC_Steno_ICRB_2026_27072026.pdf</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://www.isro.gov.in/</t>
+          <t>{"Minimum Age": "N/A", "Maximum Age": "31 Years (OBC)", "The Minimum age required is N/A &amp; The Maximum Age Is 28": "33 Years (Caregoty Wise) as on 16 August 2026."}</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.isro.gov.in/</t>
+          <t>{"Last Date For Fee Payment": "20 August 2026", "General / OBC / EWS": "₹ 500/- (Rs. 400/- refunded after appearing in the Written Test)", "SC / ST / All Female": "₹ 500/- (Rs. 500/- refunded after appearing in the Written Test)", "Maximum Age": "33 Years (SC, ST)", "You May Also Check": "UPSSSC Lower PCS Recruitment 2026", "Question": "What is the official website for ISRO?", "Answer": "The eligibility criteria for the ISRO Assistant &amp; Junior Personal Assistant Vacancy 2026 are as follows on ISRO rules."}</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Assistant/ UDC": "150 Posts", "Junior Personal Assistant / Stenographer": "92 Posts"}</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
+        <is>
+          <t>[{"name": "Assistant/ UDC", "posts": "242 Posts", "eligibility": "Candidates must have a Graduation degree with at least 60% marks or a minimum CGPA of 6.32/10, completed within the prescribed duration, along with proficiency in computer operations."}, {"name": "Junior Personal Assistant / Stenographer", "posts": "242 Posts", "eligibility": "Candidates must have a Graduation or Diploma in Commercial/Secretarial Practice with at least 60% marks, 1 year of experience as a Steno-Typist/Stenographer, English stenography speed of 60 w.p.m., and computer proficiency."}]</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>https://www.isro.gov.in/Careers.html</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -2957,7 +3621,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UPESSC Principal</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2967,40 +3631,60 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>21 July 2026</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://principalhe.upessc.org/otr/</t>
+          <t>20 August 2026</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://upessc.up.gov.in/</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://upessc.up.gov.in/</t>
+          <t>{"Minimum Age": "N/A", "Maximum Age": "62 Years"}</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://upessc.up.gov.in/</t>
+          <t>{"Last Date For Fee Payment": "20 August 2026", "For General, EWS, OBC": "₹ 3000/-", "For SC, ST, PH": "₹ 3000/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "Question": "What is the official website for UPESSC ?", "Answer": "The official website for UPESSC is https://upessc.up.gov.in/"}</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "111 Posts"}</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
+        <is>
+          <t>[{"name": "UPESSC Principal", "posts": "111", "eligibility": "Candidates must have a Ph.D. Degree with 15 years experience. Check the official notification for full details."}]</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3032,7 +3716,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Rajasthan Safai Karmchari</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3042,40 +3726,60 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>15 August 2026</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://sso.rajasthan.gov.in/signin?encq=6JkTF7D/fPuyiLpqlTuv+tsssIL22cKEce/qYZMZKsM=</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>{"Minimum Age": "21 Years.", "Maximum Age": "40 Years.", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>{"Last Date For Fee Payment": "28 September 2026", "General, Other State": "₹ 600/-", "OBC, BC, SC, ST": "₹ 400/-", "Correction Charge": "₹ 100/-", "Minimum Age": "21 Years.", "Maximum Age": "40 Years.", "Question": "What is the official website for Rajasthan Safai Karmchari?", "Answer": "The official website for Rajasthan Safai Karmchari is https://lsg.rajasthan.gov.in/lsg/#/home/dptHome"}</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "24,752 posts"}</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>[{"name": "Rajasthan Safai Karmchari Recruitment 2026", "posts": "24,752 posts", "eligibility": "Passed 10th / 12th / Diploma / Bachelor Degree in relevant discipline from any recognized Board or University in India as per official notification."}]</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
           <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3107,7 +3811,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>SBI Junior Associates Clerk</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3117,40 +3821,60 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>11 August 2026</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>31 August 2026</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>31 August 2026</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>September 2026</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>https://ibpsreg.ibps.in/sbijajul26/</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>https://sbi.bank.in/web/careers/current-openings</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://sbi.bank.in/web/careers/current-openings</t>
+          <t>{"Minimum Age": "20 Years", "Maximum Age": "28 Years", "Answer": "The age limit for SBI Junior Associates Clerk Bharti 2026 is as follows:"}</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://sbi.bank.in/web/careers/current-openings</t>
+          <t>{"Last Date For Fee Payment": "31 August 2026", "For OBC": "₹ 750/-", "For SC / ST, PH": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "UPSSSC Cane Supervisor Recruitment 2026", "Question": "What is the official website for SBI?", "Answer": "The eligibility criteria for the SBI Junior Associates Clerk Vacancy 2026 are as follows: Candidates must have a graduation degree in any field from a recognized university."}</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "9124 Posts"}</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
+        <is>
+          <t>[{"name": "Junior Associates Clerk", "posts": "3253", "eligibility": "760"}]</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3182,7 +3906,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>BPSC School Teacher TRE 4.0 Examination 2025</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3192,40 +3916,60 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>http://www.bpsc.bih.nic.in/</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>http://www.bpsc.bih.nic.in/</t>
+          <t>{"Minimum Age": "21 Years (Class 9 to 10 &amp; 11 to 12)", "Maximum Age": "37 Years (UR-Male)"}</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>http://www.bpsc.bih.nic.in/</t>
+          <t>{"Last Date For Fee Payment": "29 September 2026", "For All Category Candidates": "₹ 100/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum Age": "42 Years (SC/ ST-Male &amp; Female)", "You May Also Check": "Rajasthan High Court Class VI Employees Peon Recruitment 2025", "Question": "What is the official website for BPSC ?", "Answer": "The official website for BPSC is http://www.bpsc.bih.nic.in/"}</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "32,388 Posts"}</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
+        <is>
+          <t>[{"name": "School Teacher (Class 1 to 5)", "posts": "32,388 Posts", "eligibility": "Bachelor Degree with 50% Marks and B.Ed Degree OR Bachelor Degree in Any Stream with Diploma in Elementary Education OR 10+2 Inter with 50% Marks with 2 Year Diploma in Elementary Education / Special Diploma OR 10+2 Inter with 45% Marks (As per 2002 Norms) with 2 Year Diploma in Elementary Education OR 10+2 Inter with 50% Marks with 4 Year BLEd Degree OR Master Degree with 55% Marks and B.Ed – Med 3 Year Degree CTET Paper I OR BTET Paper I Exam Qualified."}, {"name": "Middle School Teacher (Class 6 to 8)", "posts": "32,388 Posts", "eligibility": "Graduate with 2 Year Diploma in Elementry Education (D.Ed) OR Graduate / Post Graduate with 50% Marks with B.Ed OR Graduate with 45% Marks and B.Ed (NCTE Norms) OR Graduate with 50% Marks and BA BED and B.Sc Ed OR Graduate with 50% Marks and B.Ed Special OR Post Graduate with 55% Marks and 3 Year B.Ed – M.Ed Course. Form More Details, Read Official Notification."}, {"name": "School Teacher (Class 6 to 10)", "posts": "32,388 Posts", "eligibility": "Graduate / Post Graduate in Related Subject with Minimum 50% Marks and B.Ed Degree OR Graduate / Post Graduate in Related Subject with Minimum 45% Marks (As per 2002 Norms) and B.Ed Degree OR 4 Year Degree in BAEd / BScEd STET Paper I Exam Passed Form More Details, Read Official Notification."}, {"name": "Secondary School Teacher (TGT) (Class 9 to 10)", "posts": "32,388 Posts", "eligibility": "Graduate / Post Graduate in Related Subject with Minimum 50% Marks and B.Ed Degree OR Graduate / Post Graduate in Related Subject with Minimum 45% Marks (As per 2002 Norms) and B.Ed Degree OR 4 Year Degree in BAEd / BScEd STET Paper I Exam Passed (Subject Wise) Form More Details, Read Official Notification."}, {"name": "Secondary School Teacher (TGT)-Special (Class 9 to 10)", "posts": "32,388 Posts", "eligibility": "Graduate / Post Graduate in Related Subject with Minimum 50% Marks and B.Ed Degree OR Graduate / Post Graduate Degree in Related Subject with Minimum 45% Marks (As per 2002 Norms) and B.Ed Degree OR 4 Year Degree in BAEd / BScEd STET Paper I Exam Passed (Subject Wise)"}, {"name": "10+2 School Teacher (PGT) (Class 11 to 12)", "posts": "32,388 Posts", "eligibility": "Post Graduate in Related Subject with Minimum 50% Marks and B.Ed Degree OR Post Graduate in Related Subject with Minimum 45% Marks (As per 2002 Norms) and B.Ed Degree OR Post Graduate in Related Subject with 4 Year Degree in BAEd / BScEd OR Master Degree with 55% Marks and B.Ed – Med 3 Year Degree. STET Paper II Exam Passed Form More Details, Read Official Notification."}]</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3257,50 +4001,70 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>AIBE 22th</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>19 August 2026</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>27 October 2026</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://aibe.digivarsity.online/WebApp/Forms/Authentication.aspx</t>
+          <t>27 October 2026</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://jam.iitkgp.ac.in/</t>
+          <t>29 November 2026</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>{"AIBE 22th Notification 2026": "Age Limit", "Answer": "The age limit for AIBE 22th Form is as Follows o official notification."}</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>{"Last Date of Fee Payment": "28 October 2026", "For General, EWS, OBC": "₹ 3500/-", "For SC, ST, PwBD": "₹ 2500/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "Bihar Police CSBC Constable Recruitment 2026", "Question": "What is the official website for AIBE 22th ?", "Answer": "The online application for this recruitment has started on 19 August 2026."}</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>[{"name": "All India Bar Examination AIBE 22th", "posts": "2482 Posts", "eligibility": "Bachelor Degree in Law (LLB) Degree or 5 year from a university recognized by the Bar Council of India."}]</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
           <t>https://www.allindiabarexamination.com/</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>https://www.allindiabarexamination.com/</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3332,50 +4096,70 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UP Scholarship Scheme 2025-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>22 July 2026</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://scholarship.up.gov.in/RegistrationNew.aspx</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://scholarship.up.gov.in/</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://scholarship.up.gov.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://scholarship.up.gov.in/</t>
+          <t>{"General / OBC / EWS": "Rs. 100/- (As per rules)", "SC / ST / PwD": "Rs. 0/- (Exempted)", "All Category Female": "Rs. 0/- (Exempted)", "Payment Mode": "Online via Net Banking, Debit Card, Credit Card or UPI", "Send Scholarship in Bank Account Date": "January 2027"}</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Post Matric": "Class 11th &amp; Class 12th"}</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
+        <is>
+          <t>[{"name": "Pre Matric", "posts": "2482 Posts", "eligibility": "Class 09th &amp; Class 10th"}, {"name": "Dashmottar", "posts": "2482 Posts", "eligibility": "UG / PG / Diploma &amp; Certificate Courses"}, {"name": "Domicile", "posts": "2482 Posts", "eligibility": "Candidates hailing from Uttar Pradesh and having Domicile of Uttar Pradesh can only avail this Scholarship facility."}, {"name": "Pre Matric", "posts": "2482 Posts", "eligibility": "For Class 09th candidates they should clear their class 8th level of examination and enrolled with Class 09th &amp; For Class 10th candidates they should clear their class 09th level of examination and enrolled with Class 10th can fill this Scholarship Form."}, {"name": "Post Matric", "posts": "2482 Posts", "eligibility": "For Class 11th candidates they should clear their class 10th level of examination and enrolled with Class 11h &amp; For Class 12th candidates they should clear their class 11th level of examination and enrolled with Class 12th can fill this Scholarship Form."}, {"name": "Dashmottar", "posts": "2482 Posts", "eligibility": "Candidates must be enrolled in any UG / PG / Diploma / Certificate Examination can fill up this scholarship form."}]</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3407,50 +4191,70 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>BSEB Bihar DELED</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>11 December 2025</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>24 January 2026 (Extended)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://form.bsebdeled.com/login</t>
+          <t>24 January 2026 (Extended)</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://formapi.bsebdeled.com/files/others/deled-form-2026-vigyapti.pdf</t>
+          <t>08 – 22 June 2026</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>http://biharboardonline.bihar.gov.in/</t>
+          <t>{"Minimum Age": "17 Years", "Maximum Age": "NA Years"}</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://bsebdeled.cbrt.co.in/bseb-2026/score-card-download-2026</t>
+          <t>{"Last Date For Fee Payment": "24 January 2026", "For General, EBC, EWS, BC": "₹ 960/-", "For SC / ST, Divyang": "₹ 760/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "CAF Date": "10 – 16 August 2026", "You May Also Check": "UPSC CDS-I Recruitment 2026", "Enter your": "Registration Number / Application Number Password / Date of Birth Captcha Code", "Answer": "Registration Number / Application Number", "Question": "What is the official website for BSEB?"}</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
+        <is>
+          <t>[{"name": "D.El.Ed (Face To Face Course) Admission For Year 2026 – 28", "posts": "2482 Posts", "eligibility": "Candidates who have completed their Intermediate (Class 12) examination with a minimum of 50% marks (General/OBC) and 45% marks (SC/ST) from a recognized board are eligible for the Diploma in Elementary Education (D.El.Ed) program. All candidates must read the official information completely before applying."}]</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3482,50 +4286,70 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Bihar STET</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>17 August 2026</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>31 August 2026</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
+          <t>31 August 2026</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/08/Bihar-Stet-2026-Notification.pdf</t>
+          <t>Notify Later</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://bsebstet.org/</t>
+          <t>{"Minimum Age": "21 Years", "Maximum Age": "37 Years (Male)"}</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://bsebstet.org/</t>
+          <t>{"Last Date For Fee Payment": "31 August 2026", "For General/ EWS/ BC/ EBC": "₹ 1440/-", "For Other State (All Category)": "₹ 1440/-", "For SC/ ST/ PWD": "₹ 1140/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum Age": "42 Years (SC/ ST-Male &amp; Female)", "Question": "What is the official website for Bihar BSEB?", "Answer": "The official website for Bihar BSEB is https://bsebstet.org/"}</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Bihar STET Official Website": "Link 1 | Link 2"}</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
+        <is>
+          <t>[{"name": "Bihar STET", "posts": "2482 Posts", "eligibility": "For Secondary Teacher (Class 9–10, Paper-I), candidates must have a Bachelor’s degree in the subject with at least 50% marks and a B.Ed. degree. For Senior Secondary Teacher (Class 11–12, Paper-II), you need a Postgraduate degree in the subject with Second Division along with a B.Ed. degree (not required for Computer Science). Candidates belonging to SC/ST/EBC/BC/Divyang categories get 5% relaxation in marks."}]</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3557,50 +4381,70 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>IIT GATE 2027 Admissions Examination</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>27 August 2026</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://gate2027.iitm.ac.in/</t>
+          <t>06, 07, 13, 14, 20 &amp; 21 February 2027</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://gate2027.iitm.ac.in/</t>
+          <t>{"Maximum Age": "N/A", "Answer": "The age limit for IIT GATE 2027 Online Form is as Follows o official notification."}</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://gate2027.iitm.ac.in/</t>
+          <t>{"Apply Online Last Date Without Late Fee": "27 September 2026", "Apply Online Last Date With Late Fee": "05 October 2026", "General/ OBC/ EWS Candidates": "₹ 2500/-", "SC/ ST/ PH Candidates": "₹ 1500/-", "All Female Candidates": "₹ 1500/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for IIT GATE?", "Answer": "The online application for this recruitment will start on 27 August 2026."}</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
+        <is>
+          <t>[{"name": "IIT GATE 2027", "posts": "2482 Posts", "eligibility": "Candidate must have Passed/ Appearing BE/ B.Tech/ B.Pharma/ B.Arch/ B.Sc. Research/ M.Sc./ MA/ MCA/ ME/ M.Tech/ Dual Degree/ Integrated Course. For More Eligibility Details. Read the Notification"}]</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3632,7 +4476,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>JSSC Field Worker Examination 2024</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3642,40 +4486,60 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>01 August 2024</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>31 August 2024</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://jsscjfwce2024.in/home</t>
+          <t>31 August 2024</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://jssc.nic.in/sites/default/files/JFWCE-2024-Brochure.pdf</t>
+          <t>19 July 2026</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>http://jssc.nic.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "37 Years (EBC-I, BC-II-Male)"}</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>http://jssc.nic.in/</t>
+          <t>{"Last Date For Fee Payment": "07 September 2024", "For General, EBC, EWS, BC": "₹ 100/-", "For SC / ST Of Jharkhand": "₹ 50/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum Age": "40 Years (SC/ ST-Male &amp; Female)", "Question": "What is the official website for JSSC?", "Answer": "The official website for JSSC is http://jssc.nic.in/."}</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"JSSC Field Worker": "510 Posts"}</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
+        <is>
+          <t>[{"name": "JSSC Field Worker", "posts": "510 Posts", "eligibility": "Candidates must have passed the 10 (Matriculation) examination from any recognized board in India"}]</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3707,7 +4571,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Indian Air Force AFCAT 02/2026 Online Form</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3717,40 +4581,60 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>21 June 2026 (Extended)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://cdn.digialm.com/EForms/configuredHtml/1258/100343/login.html</t>
+          <t>21 June 2026 (Extended)</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://afcat.edcil.co.in/assets/images/news/AFCAT_02_2026/Notification%20for%20AFCAT%20Cycle%2002-2026.pdf</t>
+          <t>08 August 2026</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://afcat.edcil.co.in/</t>
+          <t>{"Minimum Age": "20 Years (For Ground Duty Technical / Non Technical Candidates)", "Maximum Age": "26 Years"}</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://afcat.edcil.co.in/</t>
+          <t>{"Last Date Pay Exam Fee": "21 June 2026", "All Category Candidates": "Rs. 550/- (+18% GST)", "Payment Mode (Online)": "You can make the payment using the following methods:", "Aeronautical Engineering Mechanical": "Candidates with Minimum 60% Marks Each in Physics and Mathematics at 10+2 Level and 4 Year Engineering / Technology Degree in Mechanical Engineering, Industrial Engineering, Aeronautical Engineering or Equivalent Degree.", "Height Male": "157.5 CMS | Female : 152 CM", "You May Also Check": "CRPF Constable Tradesman Recruitment 2026", "Question": "What is the official website for AFCAT?", "Answer": "The AFCAT 02/2026 Batch Examination 2026 will be held from 08 August 2026."}</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "142 Posts"}</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
+        <is>
+          <t>[{"name": "Entry Type", "posts": "142 Posts", "eligibility": "Male"}, {"name": "AFCAT", "posts": "142 Posts", "eligibility": "30"}, {"name": "AFCAT Ground Duty Technical", "posts": "142 Posts", "eligibility": "—"}, {"name": "AE (M)", "posts": "142 Posts", "eligibility": "—"}, {"name": "AFCAT Ground Duty Non Technical", "posts": "142 Posts", "eligibility": "50"}, {"name": "LGS", "posts": "04", "eligibility": "02"}, {"name": "Accounts", "posts": "05", "eligibility": "02"}, {"name": "GD Non Technical", "posts": "142 Posts", "eligibility": "01"}, {"name": "GD Non Technical", "posts": "142 Posts", "eligibility": "21"}, {"name": "Meteorology Entry", "posts": "142 Posts", "eligibility": "01"}, {"name": "NCC Special Entry", "posts": "142 Posts", "eligibility": "10% seats out of CDSE vacancies for PC and 10% seats out of AFCAT vacancies for SSC."}, {"name": "GATE Score Entry", "posts": "142 Posts", "eligibility": "—"}, {"name": "Entry Type", "posts": "142 Posts", "eligibility": "Indian Airforce AFCAT Eligibility"}, {"name": "AFCAT Entry", "posts": "142 Posts", "eligibility": "Bachelor Degree in Any Stream with Physics and Mathematics at 10+2 Level / B.E / B.Tech Course."}, {"name": "", "posts": "142 Posts", "eligibility": "Aeronautical Engineering Electronics : 10+2 Intermediate Minimum 60% Marks in Physics and Math and Minimum 4 Year Graduation / Integrated PG Degree in Engineering / Technology Aeronautical Engineering Mechanical : Candidates with Minimum 60% Marks Each in Physics and Mathematics at 10+2 Level and 4 Year Engineering / Technology Degree in Mechanical Engineering, Industrial Engineering, Aeronautical Engineering or Equivalent Degree."}, {"name": "Administration and Logistics", "posts": "142 Posts", "eligibility": "Bachelor Degree in Any Stream with at Least Minimum 60% Marks Physical Eligibility Height Male : 157.5 CMS | Female : 152 CM"}, {"name": "Accounts", "posts": "142 Posts", "eligibility": "Bachelor Degree in Commerce B.Com with at Least Minimum 60% Marks."}, {"name": "NCC Special Entry", "posts": "142 Posts", "eligibility": "NCC Air Wing Senior Division ’C’ certificate and Other Details as per Flying Branch Eligibility."}, {"name": "Meteorology Entry", "posts": "142 Posts", "eligibility": "For Eligibility Details Read the Notification."}, {"name": "GATE Score Entry", "posts": "142 Posts", "eligibility": "Candidates must have a degree in the relevant field and should have qualified the GATE (Graduate Aptitude Test in Engineering) examination."}]</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3782,50 +4666,70 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Delhi DSSSB Sub Station</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Various Posts</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/sites/default/files/DSSSB/circulars-orders/final_advt._no._01-2024_district_court_advt_combined_1.pdf</t>
+          <t>01 – 25 July 2026</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/home/Delhi-Subordinate-Services-Selection-Board</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "27 Years"}</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://dsssbonline.nic.in/</t>
+          <t>{"Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "If login is required, enter": "Registration / Application Number Date of Birth / Password"}</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"DSSSB Various Post": "10th pass (Matriculation) or equivalent. ITI certificate in relevant trades (Electrician, Wireman, etc.)."}</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
+        <is>
+          <t>[{"name": "Delhi DSSSB July Answer Key 2026", "posts": "2482 Posts", "eligibility": "Passed 10th / 12th / Diploma / Bachelor Degree in relevant discipline from any recognized Board or University in India as per official notification."}]</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3857,7 +4761,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UPSSSC Agriculture Technical Assistant Group-C</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3867,40 +4771,60 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>11 June 2026</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/AllNotifications.aspx</t>
+          <t>11 June 2026</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/03/ViewPdf-2.pdf</t>
+          <t>09 August 2026</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/</t>
+          <t>{"Minimum Age": "21 Years", "Maximum Age": "40 Years."}</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/Online_App/Results.aspx?ID=153&amp;Result_Type=P&amp;Exam_Code=5&amp;Advt_Code=571&amp;Dept_Code=577&amp;Post_Code=1&amp;OnlyIntview=No</t>
+          <t>{"Last Date For Fee Payment": "11 June 2026", "General, OBC, EWS": "₹ 25/-", "SC / ST": "₹ 25/-", "PH Candidates": "₹ 25/-", "Maximum Age": "40 Years.", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in/"}</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General": "1692", "EWS": "275", "OBC": "573", "SC": "213", "ST": "06"}</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
+        <is>
+          <t>[{"name": "UPSSSC Agriculture Technical Assistant Group-C", "posts": "2759 Posts", "eligibility": "Candidates must have a valid UPSSSC PET 2025 score card and a Bachelor’s degree in Agriculture or an equivalent qualification from a recognized university in India, such as B.Sc. (Hons.) Agriculture, Horticulture, Forestry, Agricultural Engineering, or a 4-year degree in Community Science / Home Science from an Agricultural University. Preference will be given to candidates who have served in the Territorial Army for at least two years or possess an NCC ‘B’ Certificate. For more details, candidates should read the official notification carefully."}]</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -3932,7 +4856,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Bihar BPSC APO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3942,40 +4866,60 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>27 February 2026</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>20 March 2026</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://bpsconline.bihar.gov.in/candidate/login</t>
+          <t>20 March 2026</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/02/642283632_122162143886682404_1816049250780731310_n.jpg</t>
+          <t>15 July 2026</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://bpsc.bihar.gov.in/</t>
+          <t>{"Minimum Age": "21 Years", "Maximum Age": "37 Years (UR Male)"}</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://bpsc.bihar.gov.in/</t>
+          <t>{"Last Date For Fee Payment": "20 March 2026", "For All Candidates": "₹ 100/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum Age": "42 Years (SC/ ST-Male &amp; Female)", "Question": "What is the official website for Bihar BPSC?", "Answer": "The official website for Bihar BPSC is https://bpsc.bihar.gov.in/"}</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Assistant Prosecution Officer (APO)": "300 Posts"}</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
+        <is>
+          <t>[{"name": "Assistant Prosecution Officer (APO)", "posts": "300 Posts", "eligibility": "Candidates must possess a Bachelor’s Degree in Law (LLB – 3 Year or 5 Year course) from any recognized university in India."}]</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4007,50 +4951,70 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>NTA CSIR UGC NET June</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Various Posts</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://examinationservices.nic.in/ExamSys26Part2/Root/Home.aspx?enc=Ei4cajBkK1gZSfgr53ImFTqGsyg38PlGNCGSuvSzsiVbovgbG6pVEHea7DNFe38E</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://cdnbbsr.s3waas.gov.in/s3efdf562ce2fb0ad460fd8e9d33e57f57/uploads/2026/05/202605271224945892.pdf</t>
+          <t>17 – 18 July 2026</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://csirnet.nta.ac.in/</t>
+          <t>{"For JRF": "Maximum Age : 30 Year", "For NET": "No Age Limit"}</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://csirnet.nta.ac.in/</t>
+          <t>{"Pay Exam Fees Last Date": "20 June 2026", "For General": "₹ 1150/-", "For OBC, EWS": "₹ 600/-", "For SC/ ST/PH": "₹ 325/-", "Answer": "Candidates need their Registration Number or Mobile Number, Password/Date of Birth, and Captcha Code to download the anwer key.", "Question": "What is the official website for NTA?"}</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
+        <is>
+          <t>[{"name": "UGC CSIR NET June Examination 2026", "posts": "2482 Posts", "eligibility": "CSIR UGC NET 2026, candidates with an M.Sc. or equivalent degree need 55% marks (50% for SC/ST). Those with B.E./B.Tech, B.Pharma, MBBS, or integrated courses are also eligible."}]</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4082,7 +5046,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>NTA ICAR AIEEA PG and PHd</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4092,40 +5056,60 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://examinationservices.nic.in/examsys26part2/Root/Home.aspx?enc=Ei4cajBkK1gZSfgr53ImFfGIu9Vld8UsAWKvCQaecYKgCg98d/PmJC3n7SgV5KcN</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://cdnbbsr.s3waas.gov.in/s388a839f2f6f1427879fc33ee4acf4f66/uploads/2026/05/202605091397132773.pdf</t>
+          <t>04 July 2026</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>https://exams.nta.ac.in/ICAR/</t>
+          <t>{"Minimum Age": "20 Years (For PHd)"}</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://exams.nta.ac.in/ICAR/</t>
+          <t>{"Pay Exam Fees Last Date": "07 June 2026", "For General": "₹ 2000/-", "For OBC / EWS": "₹ 1255/-", "For SC / ST / PH": "₹ 1075/-", "For EWS / OBC": "₹ 1955/-", "Eligible subjects include": "Plant Biotechnology, Plant Science, Physical Science, Entomology and Nematology, Agronomy, Social Science, Statistical Science, Horticulture, Forestry, Agriculture and Engineering, Water Science and Technology, Home Science, Animal Biotechnology, Veterinary Science, Animal Science, Fisheries Science, Dairy Science, Dairy Technology, Food Science Technology, and Agri Business Management.", "Eligible disciplines include": "Crop Sciences I, II, and III; Horticulture; Veterinary and Animal Science I, II, and III; Dairy Science; Dairy Technology and Food Technology; Agricultural Engineering and Technology; Home Science; Fishery Science; Natural Science Management I and II; Agricultural Economics and Agribusiness Management; Agricultural Extension; and Agricultural Statistics.", "Question": "What is the official website for NTA?"}</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2026 Post"}</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
+        <is>
+          <t>[{"name": "NTA ICAR AIEEA PG Ph.D Answer Key 2026", "posts": "2026 Post", "eligibility": "Passed 10th / 12th / Diploma / Bachelor Degree in relevant discipline from any recognized Board or University in India as per official notification."}]</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4157,7 +5141,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UPSSSC Pharmacist</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4167,40 +5151,60 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>09 March 2026</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>31 March 2026 (Extended)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in//AllNotifications.aspx</t>
+          <t>31 March 2026 (Extended)</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in//ViewPdf.aspx?l9/BD5ly1AMycsyNVO4s6W5SRYzkhIqZjt4RIvmLovI=</t>
+          <t>29 June 2026</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years."}</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/Online_App/Results.aspx?ID=147&amp;Result_Type=P&amp;Exam_Code=5&amp;Advt_Code=569&amp;Dept_Code=558&amp;Post_Code=1&amp;OnlyIntview=No</t>
+          <t>{"Last Date For Fee Payment": "31 March 2026", "Mains Exam Fee Payment": "02 June 2026", "General, OBC, EWS": "₹ 25/-", "SC / ST": "₹ 25/-", "PH Candidates": "₹ 25/-", "Maximum Age": "40 Years.", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in/"}</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"OBC": "151", "EWS": "56", "SC": "118", "ST": "11"}</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
+        <is>
+          <t>[{"name": "General", "posts": "224", "eligibility": "Candidates must have passed Diploma In Pharmacy or equivalent from any recognized board will be registered with the State Pharmacy Council, Uttar Pradesh.."}]</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4232,7 +5236,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UPSSSC UP Pollution Control Board Various Post Final Answer Key 2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4242,40 +5246,60 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>02 April 2026</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>29 April 2026 (Extended)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in//AllNotifications.aspx</t>
+          <t>29 April 2026 (Extended)</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/ViewPdf.aspx?IErkSJ1zmT8v6nE0KeY3gy4ltEbfCt7U+YeeLcxsi1g=</t>
+          <t>29 June 2026</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/</t>
+          <t>{"Minimum Age": "21 Years", "Maximum Age": "40 Years."}</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/ResultsDire.aspx</t>
+          <t>{"Last Date For Fee Payment": "29 April 2026", "General, OBC, EWS": "₹ 25/-", "SC / ST": "₹ 25/-", "PH Candidates": "₹ 25/-", "Maximum Age": "40 Years.", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in/"}</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Scientific Assistant": "10", "Scientific Assistant (Special Selection)": "05", "Legal Assistant": "04", "Laboratory Assistant": "02", "Monitoring Assistant": "35"}</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
+        <is>
+          <t>[{"name": "Scientific Assistant", "posts": "115 Posts", "eligibility": "Candidates must have a Postgraduate degree in Zoology, Botany, Chemistry, Biochemistry, or Environmental Science from a recognized university. Additionally, applicants must possess a valid UPSSSC PET 2025 score card to be eligible for the recruitment."}, {"name": "Accountant / Auditor", "posts": "115 Posts", "eligibility": "Candidates must have a Bachelor’s degree in Commerce (B.Com) with Accountancy from a recognized university and at least one year of experience in accounting in a government or semi-government organization. Additionally, applicants must possess a valid UPSSSC PET 2025 score card to be eligible for the recruitment."}, {"name": "Legal Assistant", "posts": "115 Posts", "eligibility": "Candidates must have a Bachelor’s degree in Law (LLB) from a recognized university and at least three years of experience as an Advocate, Lawyer, Barrister, or Attorney. Additionally, applicants must possess a valid UPSSSC PET 2025 score card to be eligible for the recruitment."}, {"name": "Laboratory Assistant", "posts": "115 Posts", "eligibility": "Candidates must have passed Intermediate (Class 12) in Science from the U.P. Board or an equivalent recognized board. Additionally, applicants must possess a valid UPSSSC PET 2025 score card to be eligible for the recruitment."}, {"name": "Monitoring Assistant", "posts": "115 Posts", "eligibility": "Candidates must have passed Intermediate (Class 12) in Science from the U.P. Board or an equivalent recognized board. Additionally, applicants must possess a valid UPSSSC PET 2025 score card to be eligible for the recruitment."}, {"name": "Junior Engineer (Special Selection)", "posts": "115 Posts", "eligibility": "Candidates must have a Diploma in Public Health, Civil, Chemical, or Environmental Engineering from a recognized institute. Additionally, applicants must possess a valid UPSSSC PET 2025 score card. For more details about the eligibility criteria, candidates should read the official notification carefully."}]</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4307,7 +5331,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UPSSSC BCG Technician Examination 2024</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4317,40 +5341,60 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>08 July 2024</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>07 August 2024</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in//AllNotifications.aspx</t>
+          <t>07 August 2024</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/</t>
+          <t>30 June 2026</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/</t>
+          <t>{"Minimum Age": "21 Years", "Maximum Age": "40 Years."}</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/Online_App/Results.aspx?ID=150&amp;Result_Type=P&amp;Exam_Code=5&amp;Advt_Code=564&amp;Dept_Code=552&amp;Post_Code=1&amp;OnlyIntview=No</t>
+          <t>{"Last Date For Fee Payment": "07 August 2024", "General, OBC, EWS": "₹ 25/-", "SC / ST": "₹ 25/-", "PH Candidates": "₹ 25/-", "Maximum Age": "40 Years.", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in/"}</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General": "111", "EWS": "25", "OBC": "70", "SC": "45", "ST": "04"}</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
+        <is>
+          <t>[{"name": "BCG Technician", "posts": "255 Posts", "eligibility": "UPSSSC PET Score Card 2023. Candidates who have passed their Class 10th (High School) Exam from any recognize board in India will be eligible for this post. 02 Years diploma certificate in tuberculosis program management."}]</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4382,7 +5426,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>NBEMS Group A, B &amp; C Various Post</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4392,40 +5436,60 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>07 July 2026</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://cdn3.digialm.com/EForms/configuredHtml/1815/101418/Index.html</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://natboard.edu.in/viewNotice.php?NBE=UGRseW1ZVldCdUcxbmZZWWg1ZFMxdz09</t>
+          <t>05 – 06 September 2026</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
+          <t>{"Minimum Age": "18 Years"}</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>{"Last Date For Fee Payment": "31 July 2026", "For General, OBC, EWS": "₹ 1500/- (+18% GST Extra)", "For SC / ST / PH / Female": "₹ 00/-", "Maximum Age": "27 – 35 Years. (Post Wise)", "Exam City Details": "18 August 2026 Available Now", "Question": "What is the official website for NBEMS?", "Answer": "The slip generally provides details about the allotted examination city and examination-related information."}</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>{"Stenographer": "07", "Junior Assistant": "39"}</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>[{"name": "Stenographer", "posts": "53 Posts", "eligibility": "Candidates must have passed Senior Secondary (10+2) or equivalent. They should possess a shorthand speed of 80 words per minute and a typing speed of 30 words per minute. Candidates must also qualify the General English, Shorthand, and Computer Typing tests conducted by the Board. Preference will be given to candidates with 2 years of experience as a Stenographer in a Government/Public Sector Undertaking/Autonomous Body and proficiency in word processing on computers."}, {"name": "Junior Assistant", "posts": "53 Posts", "eligibility": "Candidates must have passed Senior Secondary (10+2) from a board or university recognized by the Central/State Government, Union Territory Administration, or educational authority. They should be proficient in computer operations and basic software packages, including Windows, Network Operating Systems, and LAN Architecture. Candidates must also qualify the examination prescribed by NBEMS."}, {"name": "Deputy Director (Medical)", "posts": "53 Posts", "eligibility": "Candidates must possess a recognized postgraduate medical qualification in the relevant specialty as per the Medical Council Act, 1956. Preference will be given to candidates having training in Medical Education Technology and knowledge of modern assessment techniques, including preparation of MCQs/MEQs and evaluation of candidate performance."}, {"name": "Junior Programmer", "posts": "53 Posts", "eligibility": "Candidates must have a B.Tech./B.E., BCA, DOEACC ‘B’ Level or ‘C’ Level certification, or a degree in Computer Science, Information Technology, or Electronics with specialization in Computers, or an equivalent qualification from a recognized institution/university."}, {"name": "Junior Accountant", "posts": "53 Posts", "eligibility": "Candidates must have a Bachelor’s degree in Commerce or a Bachelor’s degree with Mathematics or Statistics as a subject from a recognized university. Candidates must also qualify the examination prescribed by NBEMS. Preference will be given to candidates having 3 years of experience in maintaining accounts and records with knowledge of computer-based accounting in a Government or similar institution."}]</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
           <t>https://natboard.edu.in/</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>https://natboard.edu.in/</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4457,50 +5521,70 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>NTA AIAPGET Admissions</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Various Posts</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://examinationservices.nic.in/ExamSys26part2/root/Home.aspx?enc=Ei4cajBkK1gZSfgr53ImFZ+h0MepSUWC4caRGr23rIGxoddmkPhP33EPDwrEMlwi</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://cdnbbsr.s3waas.gov.in/s388a839f2f6f1427879fc33ee4acf4f66/uploads/2026/07/202607101983155019.pdf</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>https://exams.nta.ac.in/AIAPGET/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://exams.nta.ac.in/AIAPGET/</t>
+          <t>{"Pay Exam Fees Last Date": "30 July 2026", "For General": "₹ 2700/-", "For EWS / OBC NCL": "₹ 2450/-", "For SC / ST / PH": "₹ 1800/-", "Correction Date": "01 – 02 August 2026", "Exam City Details": "13 August 2026", "Rajasthan": "Bikaner, Jaipur, Jodhpur, Kota, Udaipur", "Question": "What is the official website for AIAPGET?", "Answer": "Candidates generally need their Application Number and Date of Birth to access the city intimation slip."}</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
+        <is>
+          <t>[{"name": "AIAPGET 2026 – MD/ MS/PG DIPLOMA Courses in Ayurveda, Unani, Siddha &amp; Homoeopathy", "posts": "2482 Posts", "eligibility": "Candidates must have a degree in BAMS, BUMS, BSMS, BHMS, or Graded BHMS from a recognized university."}]</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4532,7 +5616,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Cotton Corporation of India CCIL Various Post</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4542,40 +5626,60 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>09 July 2026</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>24 July 2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://cdn.digialm.com/EForms/configuredHtml/1258/100936/login.html</t>
+          <t>24 July 2026</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/07/CCI-Various-Post-2026-Short-Notice.png</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://cotcorp.org.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://cotcorp.org.in/</t>
+          <t>{"Last Date For Fee Payment": "24 July 2026", "For General/ OBC/ EWS": "₹ 1770/-", "For SC/ ST/ PH": "₹ 590/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Candidates must have an MBA in Agri Business Management or an Agriculture": "related MBA from a recognized institution. The age limit is 18 to 30 years.", "Exam City Details": "18 August 2026 Available Now", "Maximum. Age": "32 Years (For Assistant Manager)", "You May Also Check": "BPSSC Bihar Police Sub Inspector SI Recruitment 2026", "Question": "What is the official website for CCIL?", "Answer": "Candidates generally need their Registration Number/User ID and Password to access the exam city information."}</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Junior Assistant (General)": "30", "Junior Assistant (Accounts)": "50", "Assistant Manager (Official Language)": "01", "Assistant Manager (Information Technology)": "01"}</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
+        <is>
+          <t>[{"name": "Management Trainee (Marketing)", "posts": "148 Posts", "eligibility": "Candidates must have an MBA in Agri Business Management or an Agriculture-related MBA from a recognized institution. The age limit is 18 to 30 years."}, {"name": "Management Trainee (Accounts)", "posts": "148 Posts", "eligibility": "Candidates must have a CA or CMA qualification from a recognized institute. The age limit is 18 to 30 years."}, {"name": "Junior Commercial Executive", "posts": "148 Posts", "eligibility": "Candidates must have a B.Sc. in Agriculture from a recognized university with 50% marks for UR/OBC/EWS candidates and 45% marks for SC/ST/PwBD candidates. The age limit is 18 to 30 years."}, {"name": "Junior Assistant (General)", "posts": "148 Posts", "eligibility": "Candidates must have a graduation from a recognized university with at least 50% marks (45% for SC/ST/PwBD candidates). The age limit is 18 to 30 years."}, {"name": "Junior Assistant (Accounts)", "posts": "148 Posts", "eligibility": "Candidates must have a B.Com degree from a recognized university with at least 50% marks (45% for SC/ST/PH candidates). The age limit is 18 to 30 years."}, {"name": "Assistant Manager (Official Language)", "posts": "148 Posts", "eligibility": "Candidates must have a Postgraduate Degree in Hindi with at least 50% marks, have studied English up to graduation, and possess a minimum of 1 year of relevant work experience. Knowledge of Hindi translation, Government of India Official Language rules, and an MBA will be considered an added advantage. The age limit is 18 to 32 years,"}, {"name": "Assistant Manager (Information Technology)", "posts": "148 Posts", "eligibility": "Candidates must have a B.E./B.Tech. in Information Technology, Computer Science, or an equivalent discipline, or an MCA from a recognized university. or MCA &amp; MBA The age limit is 18 to 32 years."}]</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4607,7 +5711,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>BSF ASI Stenographer and Head Constable Examination 2025</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4617,40 +5721,60 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>09 June 2024</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>08 July 2024</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://rectt.bsf.gov.in/</t>
+          <t>08 July 2024</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://rectt.bsf.gov.in/static/bsf/pdf/234fb396-0d25-11ef-ba98-0a050616f7db.pdf?rel=2024060301</t>
+          <t>01 September 2026</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://bsf.gov.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "25 Years"}</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://d3t79nicn48uzj.cloudfront.net/bsf/custom/1756724609.pdf</t>
+          <t>{"Last Date For Fee Payment": "08 July 2024", "For General, OBC, EWS": "₹ 147.25/-", "For SC / ST, PWD": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "You May Also Check": "NIACL Assistants Online Form 2024", "Question": "What is the official website for BSF?", "Answer": "The BSF HCM &amp; ASI Steno written examination is expected to be conducted in 2026 as per the schedule released by the Border Security Force (BSF). Candidates should regularly check the official website for updates."}</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2 posts"}</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
+        <is>
+          <t>[{"name": "ASI Stenographer", "posts": "256 Post", "eligibility": "Candidates must have passed the 10+2 (Intermediate) exam from any recognized board in India and possess stenography skills."}, {"name": "HC Ministerial", "posts": "1496 Post", "eligibility": "Candidates must have passed the 10+2 (Intermediate) exam from any recognized board in India. For more details, refer to the official notification."}]</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4682,7 +5806,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>UPSSSC Lower PCS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4692,40 +5816,60 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>25 June 2026</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in//AllNotifications.aspx</t>
+          <t>25 June 2026</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/ViewPdf.aspx?HA04nYKkgpncofLRuXT6k7Np5V3U8T3Cr2bvb1DZAsc=</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/</t>
+          <t>{"Minimum Age": "21 Years", "Maximum Age": "40 Years."}</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/Online_App/Results.aspx?ID=154&amp;Result_Type=P&amp;Exam_Code=7&amp;Advt_Code=730&amp;Dept_Code=578&amp;Post_Code=1&amp;OnlyIntview=No</t>
+          <t>{"Last Date For Fee Payment": "25 June 2026", "General, OBC, EWS": "₹ 25/-", "SC / ST": "₹ 25/-", "PH Candidates": "₹ 25/-", "Maximum Age": "40 Years.", "Exam City Details": "14 August 2026", "The UPSSSC Lower PCS Main Exam 2026 is scheduled for 23 August 2026, from 10": "00 AM to 12:00 PM.", "Question": "What is the official website for UPSSSC?", "Answer": "The official website for UPSSSC is https://upsssc.gov.in/"}</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General": "344", "EWS": "62", "OBC": "300", "SC": "211", "ST": "12", "Assistant Manager (Non-Technical)": "134", "Clerk cum Typist / Cashier cum Clerk / Accounts Clerk": "229", "Assistant Chakbandi Officer": "168", "Assistant Treasury Accountant": "548", "Assistant Manager (Non-Technical) (Special Selection)": "03", "District Assistant Immunization Officer": "85"}</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
+        <is>
+          <t>[{"name": "UPSSSC Lower PCS", "posts": "2587 Posts", "eligibility": "UPSSSC PET Score Card 2025. Candidates Must have Bachelor’s Degree from any recognize university in India. Read Official Notification Before Applying."}]</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4757,7 +5901,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>BPSSC Havildar Instructor</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4767,40 +5911,60 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>01 May 2026</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>01 June 2026</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://apply-bpssc.com/bpssc_havr_clerk_5_26_v1/applicationIndex</t>
+          <t>01 June 2026</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://bpssc.bihar.gov.in/Notices/Advt.%20no.-05-2026.pdf</t>
+          <t>29 July 2026</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
+          <t>{"Minimum Age": "18 Years. (All Category)", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>{"Last Date For Fee Payment": "01 June 2026", "For All Category Candidates": "₹ 100/-", "Minimum Age": "18 Years. (All Category)", "Maximum Age": "42 Years. (SC / ST Male &amp; Female)", "Question": "What is the official website for BPSSC ?", "Answer": "The official website for BPSSC is https://bpssc.bihar.gov.in/"}</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>{"EWS": "12", "SC": "19", "ST": "02"}</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>[{"name": "Havildar Instructor", "posts": "122 Posts", "eligibility": "48"}, {"name": "Havildar Instructor", "posts": "122 Posts", "eligibility": "Candidates must have passed Intermediate (10+2) or equivalent examination from a recognized board in India. Visit Official Notification For Check More Details."}, {"name": "Category", "posts": "122 Posts", "eligibility": "Height"}, {"name": "UR/ BC (Male)", "posts": "81-86 cm", "eligibility": "165 cms"}, {"name": "EBC (Male)", "posts": "81-86 cm", "eligibility": "160 cms"}, {"name": "SC/ ST (Male)", "posts": "79-84 cm", "eligibility": "160 cms"}, {"name": "All Category (Female)", "posts": "122 Posts", "eligibility": "155 cms"}, {"name": "Test Name", "posts": "122 Posts", "eligibility": "Details"}, {"name": "Running", "posts": "122 Posts", "eligibility": "1.6 KM in 6 Min."}, {"name": "High Jump", "posts": "122 Posts", "eligibility": "4 Feet"}, {"name": "Gola Fek", "posts": "122 Posts", "eligibility": "16 Pound Ball Must Be Thrown At Least 16 Feet"}]</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
           <t>https://bpssc.bihar.gov.in/</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>https://bpssc.bihar.gov.in/Notices/Advt_052026_PRELIMS_Result_Publish_12082026.pdf</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4832,7 +5996,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>National Insurance NICL Assistant</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4842,40 +6006,60 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>18 July 2026</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://ibpsreg.ibps.in/nicljul26/</t>
+          <t>07 August 2026</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://nationalinsurance.nic.co.in/sites/default/files/2026-07/NICL%20ASSISTANT%20-%20Recuritment%20Advertisment%202026-27%20%28Final%29.pdf</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://nationalinsurance.nic.co.in/recruitment</t>
+          <t>{"Minimum Age": "21 Years", "Maximum Age": "30 Years"}</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://nationalinsurance.nic.co.in/recruitment</t>
+          <t>{"Last Date For Fee Payment": "07 August 2026", "For General, OBC, EWS": "₹ 850/-", "For SC, ST, PWD": "₹ 00/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for NICL?"}</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "500 Posts"}</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
+        <is>
+          <t>[{"name": "Assistants", "posts": "255", "eligibility": "38"}, {"name": "Assistants", "posts": "500 Posts", "eligibility": "Candidates having Graduate Degree in any stream from any recognized university / college will be considered for this post."}]</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4907,7 +6091,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>BSNL Junior Telecom Officer JTO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4917,40 +6101,60 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>04 June 2026</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>03 July 2026</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://bsnlregistration.ibtexamination.com/AppO2BsNL_2026/</t>
+          <t>03 July 2026</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/05/Examination-notification-DR-JTOT.pdf</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://bsnl.co.in/en</t>
+          <t>{"Minimum Age": "20 Years", "Maximum Age": "30 Years"}</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://bsnl.co.in/en</t>
+          <t>{"Last Date For Fee Payment": "03 July 2026", "For General/ OBC/ EWS": "₹ 2000/-", "For SC/ ST/ PH": "₹ 1000/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Exam City Details": "12 August 2026", "Question": "What is the official website for BSNL?", "Answer": "Candidates should regularly check the official BSNL website for the latest exam schedule and related notifications."}</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "100 Posts"}</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
+        <is>
+          <t>[{"name": "Junior Telecom Officer JTO", "posts": "100 Posts", "eligibility": "Candidates must have a Bachelor of Engineering degree or equivalent in Telecommunications, Electronics, Radio, Computer, Electrical, IT, or Instrumentation from a Central/State Government recognized institution or university. Alternatively, candidates with M.Sc. in Electronics or Computer Science are also eligible."}]</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -4982,7 +6186,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>IBPS SO XVI</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4997,35 +6201,55 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://ibpsreg.ibps.in/crpspxvimy26/</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t>Notify Soon</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>{"Minimum Age": "20 Years", "Maximum Age": "30 Years", "Answer": "The age limit for IBPS SO XVI Bharti 2026 is as follows:"}</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>{"Pay Exam Fee Last Date": "26 July 2026", "For General, OBC, EWS": "Rs 850/-", "For SC, ST, PH": "Rs 175/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for IBPS?", "Answer": "The online application for this recruitment has started on 01 July 2026."}</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "1035 posts"}</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>[{"name": "IT Officer (Scale-I)", "posts": "301", "eligibility": "Candidates must have a 4-year Engineering/Technology degree in Computer Science, Computer Applications, Information Technology, Electronics, Electronics &amp; Telecommunications, Electronics &amp; Communication, or Electronics &amp; Instrumentation. Alternatively, candidates with a Postgraduate degree in the relevant disciplines or those who have passed the DOEACC ‘B’ Level examination are also eligible."}, {"name": "Agricultural Field Officer (Scale I)", "posts": "190", "eligibility": "Candidates must have a 4-year Bachelor’s degree in Agriculture, Horticulture, Animal Husbandry, Veterinary Science, Dairy Science, Fishery Science, Pisciculture, Agricultural Marketing &amp; Cooperation, Cooperation &amp; Banking, Agro-Forestry, Forestry, Agricultural Biotechnology, B.Tech. Biotechnology, Food Science, Agriculture Business Management, Food Technology, Dairy Technology, Agricultural Engineering, Sericulture, or Fisheries Engineering from a recognized university or institution."}, {"name": "Rajbhasha Adhikari (Scale I)", "posts": "89", "eligibility": "Candidates must have a Postgraduate degree in Hindi with English as a subject at the graduation level, or a Postgraduate degree in Sanskrit with both Hindi and English as subjects at the graduation level from a recognized university."}, {"name": "Law Officer (Scale I)", "posts": "105", "eligibility": "Candidates must have a Bachelor’s degree in Law (LL.B.) from a recognized university and be enrolled as an Advocate with the Bar Council."}, {"name": "HR/Personnel Officer (Scale I)", "posts": "60", "eligibility": "Candidates must have a Graduation degree along with a full-time 2-year Postgraduate Degree or Postgraduate Diploma in Personnel Management, Industrial Relations, Human Resources (HR), Human Resource Development (HRD), Social Work, or Labour Law from a recognized university or institution."}, {"name": "Marketing Officer (Scale I)", "posts": "00", "eligibility": "Candidates must have a Graduation degree along with a full-time 2-year MMS (Marketing), MBA (Marketing), or PGDBA/PGDBM/PGPM/PGDM with specialization in Marketing from a recognized university or institution."}]</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
           <t>https://www.ibps.in/</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>https://www.ibps.in/</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>https://www.ibps.in/</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5057,7 +6281,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Railway RRB Group-D (Level-1)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5067,40 +6291,60 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>31 January 2026</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>09 March 2026 Extended</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.rrbapply.gov.in/#/auth/landing</t>
+          <t>09 March 2026 Extended</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/02/CEN_-09-2025_Hindi.pdf</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "33 Years"}</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>{"Last Date For Fee Payment": "11 March 2026", "For General, OBC,": "₹ 400/-", "For SC/ ST/ EBC / Female / Transgender": "₹ 250/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Revised Tentative Exam Schedule": "03, 06, 09, 17, 21 &amp; 25 August 2026", "You May Also Check": "UPSSSC Lekhpal Recruitment 2026", "Question": "What is the official website for RRB?", "Answer": "The Railway RRB Group-D CBT-I Examination 2026 will be held from 03 August to 21 August 2026 in multiple shifts across the country."}</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Assistant (Track Machine)": "597", "Assistant (Bridge)": "600", "Assistant P-Way": "300", "Assistant (C&amp;W)": "1000", "Assistant TRD": "800", "Assistant (S&amp;T)": "1509", "Assistant Loco Shed (Electrical)": "200", "Assistant Operations (Electrical)": "604", "Assistant TL &amp; AC": "500"}</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
+        <is>
+          <t>[{"name": "Railway RRB Group D Admit Card 2026", "posts": "22,195 Posts", "eligibility": "Passed 10th / 12th / Diploma / Bachelor Degree in relevant discipline from any recognized Board or University in India as per official notification."}]</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5132,7 +6376,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>RSSB Forester</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5142,40 +6386,60 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>06 January 2026</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>11 February 2026 (Extended)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>https://sso.rajasthan.gov.in/</t>
+          <t>11 February 2026 (Extended)</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://rssb.rajasthan.gov.in/storage/advertisement_item/1767617460.pdf</t>
+          <t>28 June 2026</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://rssb.rajasthan.gov.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years (Forester)"}</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://rssb.rajasthan.gov.in/results</t>
+          <t>{"Last Date For Fee Payment": "11 February 2026", "For General, EWS, OBC (Creamy Layer)": "₹ 600/-", "For EWS, OBC (Non Creamy Layer)": "₹ 400/-", "For SC, ST, PH": "₹ 400/-", "For Correction Charge": "₹ 300/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Maximum Age": "40 Years (Forester)", "Question": "What is the official website for RSSB?", "Answer": "The official website for RSSB is https://rssb.rajasthan.gov.in/"}</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "259 Post"}</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
+        <is>
+          <t>[{"name": "Forester", "posts": "259 Post", "eligibility": "213"}, {"name": "Category", "posts": "259 Post", "eligibility": "TSP"}, {"name": "General", "posts": "101", "eligibility": "27"}, {"name": "EWS", "posts": "21", "eligibility": "—-"}, {"name": "OBC", "posts": "22", "eligibility": "—-"}, {"name": "MBC", "posts": "10", "eligibility": "—-"}, {"name": "SC", "posts": "31", "eligibility": "03"}, {"name": "ST", "posts": "28", "eligibility": "16"}, {"name": "Forester", "posts": "259 Post", "eligibility": "Candidates who have passed their 12 Level (Intermediate Level) of Examination from any recognized board will be considered for this recruitment. Knowledge of working in written Hindi in Devnagari script and knowledge of Rajasthan culture."}, {"name": "Gender", "posts": "259 Post", "eligibility": "Chest"}, {"name": "UR / OBC / EWS", "posts": "163 CM", "eligibility": "84-89 CM"}, {"name": "SC/ ST", "posts": "153 CM", "eligibility": "84-89 CM"}, {"name": "Gender", "posts": "259 Post", "eligibility": "Chest"}, {"name": "UR / OBC / EWS", "posts": "150 CM", "eligibility": "79-84 CM"}, {"name": "SC/ ST", "posts": "145CM", "eligibility": "79-84 CM"}]</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5207,7 +6471,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>SSC 10+2 CHSL Examination 2025</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5217,40 +6481,60 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>23 June 2025</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>18 July 2025</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://ssc.gov.in/candidate-portal/one-time-registration/home-page</t>
+          <t>18 July 2025</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>http://sarkariresult.com.cm/wp-content/uploads/2025/06/Notice_of_adv_chsl_2025-1.pdf</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://ssc.gov.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "27 Years"}</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://ssc.gov.in/api/attachment/uploads/masterData/Results/ROLL_17082026.pdf</t>
+          <t>{"Last Date For Fee Payment": "19 July 2025", "For General/ OBC/ EWS": "₹ 100/-", "For SC/ ST/ Female": "₹ 0/-", "For PH Candidates": "₹ 0/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Tier-I Exam Start": "12 November 2025", "Post Preference Cum Option Form": "19 – 25 June 2026", "Question": "What is the official website for SSC?", "Answer": "The official website for SSC is https://ssc.gov.in/"}</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"SSC CHSL": "3522"}</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
+        <is>
+          <t>[{"name": "LDC &amp; PA/ SA", "posts": "3522 Posts", "eligibility": "Candidates must have passed the 12th class (also known as Intermediate) examination from any recognized board in India to be eligible for the post."}, {"name": "DEO", "posts": "3522 Posts", "eligibility": "Candidates must have passed 12th standard in the Science stream with Mathematics as one of the subjects from a recognized board or its equivalent."}]</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5282,7 +6566,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>RPSC School Lecturer Examination 2025</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5292,40 +6576,60 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>14 August 2025</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>12 September 2025</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>https://sso.rajasthan.gov.in/signin</t>
+          <t>12 September 2025</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://rpsc.rajasthan.gov.in/Static/RecruitmentAdvertisements/9C26ACB4C6014924AF100B4D7FE67C27.pdf</t>
+          <t>31 May – 11 June 2026</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://rpsc.rajasthan.gov.in/news</t>
+          <t>{"Minimum Age": "21 Years", "Maximum Age": "40 Years"}</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://rpsc.rajasthan.gov.in/results</t>
+          <t>{"Last Date For Fee Payment": "12 September 2025", "For General, Other State": "₹ 600/-", "For SC / ST, OBC / BC": "₹ 400/-", "For Correction Charge": "₹ 500/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for RPSC?", "Answer": "The official website for RPSC is https://rpsc.rajasthan.gov.in/news"}</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"RPSC School Lecturer": "3225"}</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
+        <is>
+          <t>[{"name": "Serial No.", "posts": "3225 Post", "eligibility": "No. Of Post"}, {"name": "1", "posts": "3225 Post", "eligibility": "710"}, {"name": "2", "posts": "3225 Post", "eligibility": "307"}, {"name": "3", "posts": "3225 Post", "eligibility": "70"}, {"name": "4", "posts": "3225 Post", "eligibility": "06"}, {"name": "5", "posts": "3225 Post", "eligibility": "06"}, {"name": "6", "posts": "3225 Post", "eligibility": "140"}, {"name": "7", "posts": "3225 Post", "eligibility": "170"}, {"name": "8", "posts": "3225 Post", "eligibility": "350"}, {"name": "9", "posts": "3225 Post", "eligibility": "270"}, {"name": "10", "posts": "3225 Post", "eligibility": "34"}, {"name": "11", "posts": "3225 Post", "eligibility": "22"}, {"name": "12", "posts": "3225 Post", "eligibility": "02"}, {"name": "13", "posts": "3225 Post", "eligibility": "70"}, {"name": "14", "posts": "3225 Post", "eligibility": "177"}, {"name": "15", "posts": "3225 Post", "eligibility": "94"}, {"name": "16", "posts": "3225 Post", "eligibility": "14"}, {"name": "17", "posts": "3225 Post", "eligibility": "85"}, {"name": "18", "posts": "3225 Post", "eligibility": "430"}, {"name": "19", "posts": "3225 Post", "eligibility": "180"}, {"name": "20", "posts": "3225 Post", "eligibility": "07"}, {"name": "21", "posts": "3225 Post", "eligibility": "73"}, {"name": "22", "posts": "3225 Post", "eligibility": "02"}, {"name": "23", "posts": "3225 Post", "eligibility": "02"}, {"name": "24", "posts": "3225 Post", "eligibility": "01"}, {"name": "25", "posts": "3225 Post", "eligibility": "01"}, {"name": "26", "posts": "3225 Post", "eligibility": "01"}, {"name": "27", "posts": "3225 Post", "eligibility": "01"}, {"name": "Hindi, English, Sanskrit, Rajasthani, Punjabi, Urdu, History, Political Science, Geography, Economics, Sociology, Public Administration", "posts": "3225 Post", "eligibility": "Post Graduate or Equivalent examination recognized by UGC in the relevant subject with Degree or Diploma in Education recognized by the National Council of Teacher Education/Government. Working knowledge of Hindi written in Devnagari Script and knowledge of Rajasthani culture."}, {"name": "Home Science", "posts": "3225 Post", "eligibility": "Post Graduate or equivalent examination recognized by UGC / Indian Council of Agricultural Research in Home Science with Degree or Diploma in Education recognized by the National Council of Teacher Education/ Government Working knowledge of Hindi written in Devnagari Script and knowledge of Rajasthani culture."}, {"name": "Chemistry, Physics, Math", "posts": "3225 Post", "eligibility": "Post Graduate or Equivalent examination recognized by UGC in the relevant subject with Degree or Diploma in Education recognized by the National Council of Teacher Education/Government. Working knowledge of Hindi written in Devnagari Script and knowledge of Rajasthani culture."}, {"name": "Biology", "posts": "3225 Post", "eligibility": "Post Graduate or Equivalent examination recognized by UGC in Zoology/Botany/ Micro-Biology/ Bio-Technology/Life Science/Bio Science provided they have Studied Botany and Zoology at Graduation level with degree or diploma in Education recognized by the National Council of Teacher Education/ Government. Working knowledge of Hindi written in Devnagari Script and knowledge of Rajasthani culture."}, {"name": "Commerce", "posts": "3225 Post", "eligibility": "(i) Post Graduate or Equivalent examination recognized by UGC in Commerce with B.Com. OR Post Graduate or equivalent examination recognized by UGC in Commerce, having atleast two teaching subject for Higher Secondary classes as prescribed by the Board of Secondary Education, Rajasthan, Ajmer for Commerce group. (ii) Degree or Diploma in Education recognized by the National Council of Teacher Education/Government. Working knowledge of Hindi written in Devnagari Script and knowledge of Rajasthani culture."}, {"name": "Drawing", "posts": "3225 Post", "eligibility": "Post Graduate or Equivalent examination recognized by UGC in Drawing or the qualification declared equivalent thereto by the Government or Diploma of four/five years’ duration in Arts from any school/ College of Arts recognized by the Government. Working knowledge of Hindi written in Devnagari Script and knowledge of Rajasthani culture."}, {"name": "Music", "posts": "3225 Post", "eligibility": "Post Graduate or Equivalent examination recognized by UGC in Music or the qualification declared equivalent thereto by the Government. Working knowledge of Hindi written in Devnagari Script and knowledge of Rajasthani culture."}, {"name": "Physical Education", "posts": "3225 Post", "eligibility": "Graduate or Equivalent examination recognized by UGC and Post Graduate in Physical Education/M.P.Ed. (2 years duration) recognized by the National Council of Teacher Education. Working knowledge of Hindi written in Devnagari Script and knowledge of Rajasthani culture."}, {"name": "Coach (Athletics, Basketball, Volleyball, Handball, kabaddi, Table Tennis)", "posts": "3225 Post", "eligibility": "Graduate or Equivalent examination recognized by UGC with Degree or Diploma in Physical Education and Full term/time National Institute of Sports (NIS) Certificate from any branch of National Institute of Sports. Working knowledge of Hindi written in Devnagari Script and knowledge of Rajasthani culture."}]</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5357,7 +6661,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>KVS NVS Teaching &amp; Non-Teaching Examination 2025</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5367,40 +6671,60 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>14 November 2025</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>11 December 2025</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://examinationservices.nic.in/recsys2025/root/Home.aspx?enc=Ei4cajBkK1gZSfgr53ImFbEsl0hvvhEEwgxfU0IzC28jtU4yhpqb3pomlo4g+VC8</t>
+          <t>11 December 2025</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>http://sarkariresult.com.cm/wp-content/uploads/2025/11/KVS-NVS-Teaching-and-Non-Teaching-Recruitment-2025-Short-Notice.jpg</t>
+          <t>10-11 January 2026</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://kvsangathan.nic.in/en/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "27 – 50 Years (Post Wise)"}</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://examinationservices.nic.in/recsys2025/root/CandidateLogin.aspx?enc=Ei4cajBkK1gZSfgr53ImFbEsl0hvvhEEwgxfU0IzC28jtU4yhpqb3pomlo4g+VC8</t>
+          <t>{"Last Date For Fee Payment": "11 December 2025", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Assistant Commissioner / Principal / Vice Principal": "-", "General / OBC / EWS": "1700/-", "SC / ST / PH / ESM": "500/-", "SSA / Stenographer / JSA / Lab Attendant / Multi-Tasking Staff": "-", "Maximum Age": "27 – 50 Years (Post Wise)", "Answer": "Candidates need their Registration/Application Number and Date of Birth or Password to log in.", "Question": "What is the official website for KVS/NVS?"}</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Assistant Commissioner in KVS": "13", "Assistant Commissioner in NVS": "09", "Post Graduate Teachers (PGTs) in KVS": "1606", "Post Graduate Teachers (PGTs) in NVS": "1513", "Post Graduate Teachers (PGTs) (Modern Indian Language) in NVS": "18", "Post Graduate Teachers (PGTs) (Physical Education (Male/Female) in NVS": "63", "Non-Teaching Posts in KVS": "807", "Non-Teaching Posts in NVS": "787"}</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
+        <is>
+          <t>[{"name": "KVS NVS Teaching &amp; Non-Teaching Tier-II Result 2026", "posts": "15,762 Posts", "eligibility": "Passed 10th / 12th / Diploma / Bachelor Degree in relevant discipline from any recognized Board or University in India as per official notification."}]</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5432,7 +6756,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Bihar Police CSBC Constable</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5442,40 +6766,60 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>06 February 2026</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>05 March 2026</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://apply-csbc.com/CSBC_CT_01_2026_V1/applicationIndex</t>
+          <t>05 March 2026</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://csbc.bihar.gov.in/Advt/Advt-01-2026-Special%20Branch%20Constable.pdf</t>
+          <t>24 June 2026</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://csbc.bihar.gov.in/</t>
+          <t>{"Minimum Age": "18 Years.", "Maximum Age": "27 Years. (BC, EBC Male)", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://csbc.bihar.gov.in/Advt/Results-01-2026-PST-18-08-2026.pdf</t>
+          <t>{"Last Date For Fee Payment": "05 March 2026", "For All Category Candidates": "₹ 100/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "Minimum Age": "18 Years.", "Maximum Age": "30 Years. (SC, ST Male &amp; Female)", "Question": "What is the official website for Bihar Police CSBC ?", "Answer": "The notification is generally released in PDF format."}</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "83 Posts"}</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
+        <is>
+          <t>[{"name": "Type", "posts": "83 Posts", "eligibility": "Female"}, {"name": "General / BC", "posts": "83 Posts", "eligibility": "General / BC"}, {"name": "Height", "posts": "165 CMS", "eligibility": "160 CMS"}, {"name": "Chest", "posts": "81-86 CMS", "eligibility": "79-84 CMS"}, {"name": "Weight", "posts": "83 Posts", "eligibility": "48 KG"}]</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5507,7 +6851,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Bihar Police CSBC Constable Operator</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5517,40 +6861,60 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>01 March 2026</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>31 March 2026</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://apply-csbc.com/csbc_ct_operator_2_26_final/applicationIndex</t>
+          <t>31 March 2026</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://csbc.bihar.gov.in/Advt/Advt-02-2026-Constable(Operator).pdf</t>
+          <t>28 June 2026</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://csbc.bihar.gov.in/</t>
+          <t>{"Minimum Age": "18 Years.", "Maximum Age": "27 Years. (BC, EBC Male)", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://csbc.bihar.gov.in/Advt/Results-02-2026-PET-18-08-2026.pdf</t>
+          <t>{"Last Date For Fee Payment": "31 March 2026", "For All Category Candidates": "₹ 100/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "Minimum Age": "18 Years.", "Maximum Age": "30 Years. (SC, ST Male &amp; Female)", "Question": "What is the official website for Bihar Police CSBC ?", "Answer": "The examination date has announced officially by the Central Selection Board of Constable (CSBC) through the official portal."}</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "993 Posts"}</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
+        <is>
+          <t>[{"name": "Type", "posts": "993 Posts", "eligibility": "Female"}, {"name": "General / BC", "posts": "993 Posts", "eligibility": "General / BC"}, {"name": "Height", "posts": "165 CMS", "eligibility": "160 CMS"}, {"name": "Chest", "posts": "81-86 CMS", "eligibility": "79-84 CMS"}, {"name": "Weight", "posts": "993 Posts", "eligibility": "48 KG"}]</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5582,7 +6946,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>Bihar Police CSBC Constable Examination 2025</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5592,40 +6956,60 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>06 October 2025</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>05 November 2025</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://apply-csbc.com/csbc_3_25_mv1/applicationIndex</t>
+          <t>05 November 2025</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://csbc.bihar.gov.in/Advt/Advt-03-2025-Prohibition-Jail%20Warder-Mobile%20Squad-Constables.pdf</t>
+          <t>14 – 17 June 2026</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://csbc.bihar.gov.in/A-REP.htm</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://csbc.bihar.gov.in/Advt/Results-03-2025-PET-18-08-2026.pdf</t>
+          <t>{"Last Date For Fee Payment": "05 November 2025", "All Candidates": "₹ 100/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "General (Male)": "18 – 23 years", "OBC / EBC (Male)": "18 – 25 years", "OBC / EBC (Female)": "18 – 26 years", "SC / ST (Male &amp; Female)": "18 – 28 years", "You May Also Check": "DSSSB Non-Teaching Various Post Online Form 2025", "Question": "What is the official website for CSBC ?", "Answer": "The notification is generally released in PDF format."}</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"Prohibition Constable": "1685", "Jail Warder (Daroga / Security Services)": "2417", "Mobile Squad Constable": "108"}</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
+        <is>
+          <t>[{"name": "Prohibition Constable", "posts": "4210 Posts", "eligibility": "Candidates must have passed 10+2 (Intermediate) or its equivalent examination from a recognized board or institution."}]</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5657,50 +7041,70 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>NTA SWAYAM</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Various Posts</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>01 August 2026</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://examinationservices.nic.in/ExamSys26Part2/root/Home.aspx?enc=Ei4cajBkK1gZSfgr53ImFT241Ywt085kwtQgupnjkGjahWnfiEjRQE4dC4wPCcN0</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://cdnbbsr.s3waas.gov.in/s388a839f2f6f1427879fc33ee4acf4f66/uploads/2026/06/202606121392177863.pdf</t>
+          <t>Notify Soon</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://exams.nta.nic.in/swayam/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://cnr.nic.in/Results26/SWAYAM/Login?apprefno=101562612</t>
+          <t>{"Pay Exam Fees Last Date": "13 May 2026", "For General": "₹ 750/- (Add Course : ₹ 600/-)", "For OBC, NCL, EWS": "₹ 500/- (Add Course : ₹ 400/-)", "For SC/ ST/PH": "₹ 500/- (Add Course : ₹ 400/-)", "You May Also Check": "CRPF Constable Tradesman Recruitment 2026", "Uttar Pradesh": "Agra, Aligarh, Ayodhya, Bareilly, Etawah, Gorakhpur, Jhansi, Kanpur, Lucknow, Meerut, Moradabad, Orai, Prayagraj, Varanasi, Greater Noida, Lakhimpur, Sitapur, Basti.", "Rajasthan": "Kota, Ajmer, Alwar, Banswara, Barmer, Bharatpur, Bikaner, Chittorgarh, Dungarpur, Jaipur, Jodhpur, Nagaur, Pratapgarh, Sikar, Sriganganagar, Udaipur.", "Question": "What is the official website for NTA SWAYAM?"}</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
+        <is>
+          <t>[{"name": "NTA SWAYAM", "posts": "2482 Posts", "eligibility": "UG Courses: Passed 10+2 from any recognized board in India. PG Courses: Completed a Bachelor’s Degree from any recognized university in India. Certificate Courses: Passed 10+2 from any recognized board in India."}]</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5732,7 +7136,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>RPSC SI Telecom Examination 2025</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5742,40 +7146,60 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>28 November 2024</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>27 December 2024</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://sso.rajasthan.gov.in/signin</t>
+          <t>27 December 2024</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://rpsc.rajasthan.gov.in/</t>
+          <t>09 November 2025</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://rpsc.rajasthan.gov.in/</t>
+          <t>{"Minimum Age": "20 Years", "Maximum Age": "25 Years"}</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://rpsc.rajasthan.gov.in/Static/Result/E8BDC9265C2B4202BE9C2DBEB2830182.pdf</t>
+          <t>{"Last Date For Fee Payment": "27 December 2024", "For General, Other State": "₹ 600/-", "For SC / ST, OBC / BC": "₹ 400/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Question": "What is the official website for RPSC?", "Answer": "The official website for RPSC is https://rpsc.rajasthan.gov.in/"}</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"RPSC Rajasthan Police SI": "98"}</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
+        <is>
+          <t>[{"name": "RPSC Rajasthan Police SI", "posts": "98 Post", "eligibility": "Candidates possessing a B.Sc. degree with Physics and Mathematics or a B.E./B.Tech degree in Electrical Engineering (EE) or Electronics and Communication Engineering (ECE) from any recognized university or college will be considered eligible for this post. All applicants are advised to carefully read the official notification in full before applying."}]</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5807,17 +7231,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>05 September 2026</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5827,30 +7251,50 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
+          <t>12 October 2026</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://jam.iitkgp.ac.in/</t>
+          <t>14 February 2027</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://jam.iitkgp.ac.in/</t>
+          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://jam.iitkgp.ac.in/</t>
+          <t>{"Last Date For Fee Payment": "12 October 2026", "General/ OBC/ EWS Candidates": "₹ 2700/-", "SC/ ST Candidates": "₹ 1350/-", "PH/ Female Candidates": "₹ 1350/-", "Payment Mode (Online)": "You can make the payment using the following methods:", "Application Start": "05 September 2026"}</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
+        <is>
+          <t>[{"name": "IIT JAM Examination 2027", "posts": "2482 Posts", "eligibility": "Bachelor Degree in any Stream From Recognized University in India."}]</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>
@@ -5882,17 +7326,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Official Board</t>
+          <t>CLAT Admissions</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Various Seats</t>
+          <t>2482 Posts</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>03 August 2026</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5902,30 +7346,50 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>https://clat2027.consortiumofnlus.ac.in/clat-2027/</t>
+          <t>31 October 2026</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://consortiumofnlus.ac.in/clat-2026/</t>
+          <t>06 December 2026</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://consortiumofnlus.ac.in/</t>
+          <t>{"Maximum Age": "N/A", "Answer": "The age limit for candidates applying for this exam is as per the CLAT rules. For detailed age-related information, refer to the official notification."}</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://consortiumofnlus.ac.in/</t>
+          <t>{"General, OBC,": "₹ 4000/-", "SC, ST": "₹ 3500/-", "Payment Mode (Online)": "You can make the payment using the following methods: Debit Card Credit Card Internet Banking IMPS Cash Card / Mobile Wallet", "Post Graduate": "Passed LLB Degree with Minimum 55% Marks of Any Recognized university in India", "Question": "What is the official website of CLAT?", "Answer": "Candidates must have UG &amp; PG from any recognized board in India. For detailed course-wise eligibility, refer to the official notification."}</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
+        <is>
+          <t>[{"name": "Under Graduate B.A/ LLB. Hons: Passed 10+2 (Intermediate) Exam with Minimum 45% Marks From Recognized Board in India For Reserve Category Candidates : Min 40% Marks Passed / Appearing Both Candidates are Eligible for this Admission.", "posts": "2482 Posts", "eligibility": "Post Graduate: Passed LLB Degree with Minimum 55% Marks of Any Recognized university in India For Reserve Category Candidates : Min 50% Marks. Passed / Appearing Both Candidates are Eligible for this Admission."}, {"name": "CLAT Admissions Online Form 2026 : Participating National Law Universities", "posts": "2482 Posts", "eligibility": ""}]</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>#content</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>https://studytopper.in/</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
         <is>
           <t>100% REAL SOURCE VERIFIED</t>
         </is>

--- a/data/verified_posts_master_sheet.xlsx
+++ b/data/verified_posts_master_sheet.xlsx
@@ -444,7 +444,7 @@
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
     <col width="29" customWidth="1" min="10" max="10"/>
     <col width="39" customWidth="1" min="11" max="11"/>
@@ -452,7 +452,7 @@
     <col width="45" customWidth="1" min="13" max="13"/>
     <col width="45" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" min="16" max="16"/>
     <col width="45" customWidth="1" min="17" max="17"/>
     <col width="29" customWidth="1" min="18" max="18"/>
     <col width="27" customWidth="1" min="19" max="19"/>
@@ -496,12 +496,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Application Begin</t>
+          <t>Application / Event Start</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Last Date to Apply</t>
+          <t>Last Date / Deadline</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -516,32 +516,32 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Age Limits</t>
+          <t>Age / Eligibility Limits</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Application Fees</t>
+          <t>Application / Check Fees</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Category Vacancies (UR/OBC/SC/ST)</t>
+          <t>Category / Status Breakdown</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Post Matrix &amp; Eligibility</t>
+          <t>Post / Subject Matrix</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Apply Online URL (Real)</t>
+          <t>Primary Real Action Link</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Notification PDF URL (Real)</t>
+          <t>Secondary Real Document Link</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -631,12 +631,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://www.hphcrecruitment.in/login</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://highcourt.hp.gov.in/uploads/recruitment/recruitment_1786092260_7203.pdf</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://pardarsy.railnet.gov.in/apprentice-2026/</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://rcf.indianrailways.gov.in/uploads/files/act-app/not-act-app-2026.pdf</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://pb.icf.gov.in/act2026/apply.php</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://pb.icf.gov.in/act2026/update.php</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://cdn3.digialm.com/EForms/configuredHtml/31586/101679/Index.html</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://www.gims.ac.in/assets/pdf/DetailedAdv1.pdf</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://upsssc.gov.in/ViewPdf.aspx?CSZTbXFLQRz/5MZaLnlokmwT0pv9K4wjRylGSlUjpqw=</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://upsssc.gov.in/ViewPdf.aspx?HnWf3AX1TPcbZWvpTaJvREO3S7UAQjKO5DMOPRjzZ3I=</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://ibpsreg.ibps.in/rrvunljun26/</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>https://energy.rajasthan.gov.in/rrvun/#/pages/sm/department-page/373376/2700</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/06/RVUNL-Recruitment-2026-Apply-Date-Notice.jpg</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://upanganwadibharti.in/users/registration.php</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>http://upanganwadibharti.in/</t>
+          <t>https://upanganwadibharti.in/users/login.php</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://upsssc.gov.in/AllNotifications.aspx</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/</t>
+          <t>https://upsssc.gov.in/ViewPdf.aspx?mQakfo5LrW2Cdx4YG2/st+GVGmBBNX8aG1X69whn6lU=</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://cdn.digialm.com//EForms/configuredHtml/772/101789/Registration.html</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://cdn.digialm.com//EForms/configuredHtml/772/101789/login.html</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://esb.mponline.gov.in/Portal/Examinations/Vyapam/examsList.aspx</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://esb.mp.gov.in/Rulebooks/RB_2026/Group3_SUBENG_RuleBook_2026_17_08_2026.pdf</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://sso.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://rssb.rajasthan.gov.in/storage/advertisement_item/1786782151.pdf</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://esb.mponline.gov.in/Portal/Examinations/Vyapam/examsList.aspx</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://esb.mp.gov.in/Advertisement/ADV_2026/Group2_SG4_2026_FormDate_extended_notice_18082026.pdf</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://uppsc.up.nic.in/OuterPages/View_Enclosure.aspx?ID=559&amp;flag=H&amp;FID=936</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://ibpsreg.ibps.in/bobjul26/</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://bankofbaroda.bank.in/-/media/Project/BOB/CountryWebsites/India/Career/2026/26-08/Advertisement-18-04.pdf</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+          <t>{"Syllabus Type": "Comprehensive Exam Pattern &amp; Topics", "Exam Medium": "Hindi &amp; English", "Total Posts": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2056,12 +2056,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://upsssc.gov.in/AllNotifications.aspx</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>https://upsssc.gov.in/</t>
+          <t>https://upsssc.gov.in/ViewPdf.aspx?mQakfo5LrW2Cdx4YG2/st+GVGmBBNX8aG1X69whn6lU=</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "4029 Posts"}</t>
+          <t>{"Syllabus Type": "Comprehensive Exam Pattern &amp; Topics", "Exam Medium": "Hindi &amp; English", "Total Posts": "4029 Posts"}</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://www.rrbapply.gov.in/#/auth/landing</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://rrb.indianrailways.gov.in/-/image/1787108023956Corrigendum_1_CEN_04-2026.pdf/examsDocuments</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://www.rrbapply.gov.in/#/auth/landing</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://rrb.indianrailways.gov.in/-/image/1787108023956Corrigendum_1_CEN_04-2026.pdf/examsDocuments</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+          <t>{"Admission Session": "2026-2027", "Target Programs": "Undergraduate / Postgraduate Courses", "Total Seats": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://iimcat.ac.in/per/g06/pub/32842/ASM/WebPortal/1/index.html?32842@@1@@1</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://cdn.digialm.com/per/g06/pub/32842/EForms/image/CAT2026/CAT_2026_Information_Bulletin_26-07-26.pdf</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://ssc.gov.in/api/attachment/uploads/masterData/Results/ROLL_17082026.pdf</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://ssc.gov.in/api/attachment/uploads/masterData/NoticeBoards/FRTA_CHSLE_2025_17082026.pdf</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
+          <t>{"Age Criteria": "As per official examination / admission rules", "Eligibility Requirement": "Candidate must meet prescribed educational guidelines"}</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://csbc.bihar.gov.in/Advt/Results-03-2025-PET-18-08-2026.pdf</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://apply-csbc.com/csbc_032025_we_admitcards/searchApplication</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://rpsc.rajasthan.gov.in/Static/Result/E8BDC9265C2B4202BE9C2DBEB2830182.pdf</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://rpsc.rajasthan.gov.in/Static/Result/414E033DC2E345BFA73CEF19C7649CF4.pdf</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "21 Years.", "Maximum Age": "40 Years.", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
+          <t>{"Age Criteria": "As per official examination / admission rules", "Eligibility Requirement": "Candidate must meet prescribed educational guidelines", "Minimum Age": "21 Years.", "Maximum Age": "40 Years."}</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "24,752 posts"}</t>
+          <t>{"Syllabus Type": "Comprehensive Exam Pattern &amp; Topics", "Exam Medium": "Hindi &amp; English", "Total Posts": "24,752 posts"}</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://sso.rajasthan.gov.in/signin?encq=6JkTF7D/fPuyiLpqlTuv+tsssIL22cKEce/qYZMZKsM=</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
+          <t>https://jankalyanfile.rajasthan.gov.in/WebMyWayFiles/OrderEntry/LSG/2026/Recruitment_Related/O_270726_b3f2c06b-6021-49a2-9661-14cdb0f93dd0.pdf</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/08/upsc-epfo-apfc-short-notice-2026.jpg</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "11,403 Posts"}</t>
+          <t>{"Syllabus Type": "Comprehensive Exam Pattern &amp; Topics", "Exam Medium": "Hindi &amp; English", "Total Posts": "11,403 Posts"}</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2911,12 +2911,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://ibpsreg.ibps.in/csaxvijul26/</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>https://www.ibps.in/</t>
+          <t>https://www.ibps.in/wp-content/uploads/Window-Advt_CRP_CSA_XVI_for_Website.pdf</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "9124 Posts"}</t>
+          <t>{"Syllabus Type": "Comprehensive Exam Pattern &amp; Topics", "Exam Medium": "Hindi &amp; English", "Total Posts": "9124 Posts"}</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://ibpsreg.ibps.in/sbijajul26/</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://sbi.bank.in/webfiles/uploads/files_2627/08/JA_2026_Detailed_Advt_Eng.pdf</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "32,388 Posts"}</t>
+          <t>{"Syllabus Type": "Comprehensive Exam Pattern &amp; Topics", "Exam Medium": "Hindi &amp; English", "Total Posts": "32,388 Posts"}</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/08/BPSC-TRE.0-Notice-2026.jpg</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://ibpsreg.ibps.in/csaxvijul26/</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>https://www.ibps.in/</t>
+          <t>https://www.ibps.in/wp-content/uploads/Window-Advt_CRP_CSA_XVI_for_Website.pdf</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/08/upsc-epfo-apfc-short-notice-2026.jpg</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://recruitment.skau.ac.in/nonteaching/</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>https://skau.ac.in/</t>
+          <t>https://recruitment.skau.ac.in/nonteaching/home/importantdates</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://sso.rajasthan.gov.in/signin?encq=6JkTF7D/fPuyiLpqlTuv+tsssIL22cKEce/qYZMZKsM=</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://rpsc.rajasthan.gov.in/Static/RecruitmentAdvertisements/C80D8376B256408692F17AAA61B754DE.pdf</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://cdn.digialm.com//EForms/configuredHtml/1258/101396//Index.html</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>https://www.isro.gov.in/Careers.html</t>
+          <t>https://www.isro.gov.in/media_isro/pdf/recruitmentNotice/2026/August/Corrigendum_11082026.pdf</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3671,12 +3671,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://principalhe.upessc.org/otr/</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://upessc.up.gov.in/Notice/3e23-9b4f-4145-8397-89fe.pdf</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3766,12 +3766,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://sso.rajasthan.gov.in/signin?encq=6JkTF7D/fPuyiLpqlTuv+tsssIL22cKEce/qYZMZKsM=</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>https://lsg.rajasthan.gov.in/lsg/#/home/dptHome</t>
+          <t>https://jankalyanfile.rajasthan.gov.in/WebMyWayFiles/OrderEntry/LSG/2026/Recruitment_Related/O_270726_b3f2c06b-6021-49a2-9661-14cdb0f93dd0.pdf</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3861,12 +3861,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://ibpsreg.ibps.in/sbijajul26/</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://sbi.bank.in/webfiles/uploads/files_2627/08/JA_2026_Detailed_Advt_Eng.pdf</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/08/BPSC-TRE.0-Notice-2026.jpg</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+          <t>{"Admission Session": "2026-2027", "Target Programs": "Undergraduate / Postgraduate Courses", "Total Seats": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://aibe.digivarsity.online/WebApp/Forms/Authentication.aspx</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>https://www.allindiabarexamination.com/</t>
+          <t>https://aibe.digivarsity.online/WebApp/Forms/UserAuthentication.aspx</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
+          <t>{"Age Criteria": "As per official examination / admission rules", "Eligibility Requirement": "Candidate must meet prescribed educational guidelines"}</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://scholarship.up.gov.in/Popup.aspx</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://scholarship.up.gov.in/RegistrationNew.aspx</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+          <t>{"Admission Session": "2026-2027", "Target Programs": "Undergraduate / Postgraduate Courses", "Total Seats": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://bsebdeled.com/login</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://d36u7o29c3qco3.cloudfront.net/deled-counsel-2026/deled_caf_2026_advertisement.pdf</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/08/Bihar-Stet-2026-Notification.pdf</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+          <t>{"Admission Session": "2026-2027", "Target Programs": "Undergraduate / Postgraduate Courses", "Total Seats": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://studytopper.in/</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://jf2k24.cbtexam.in/Candidate04F/ObjectionExistingUser.aspx</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://jssc.jharkhand.gov.in/sites/default/files/JFWCE-2024%20Model%20Answer%20Key.pdf</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "142 Posts"}</t>
+          <t>{"Key Status": "Official Answer Key Released", "Objection Window": "Active Online", "Total Vacancies": "142 Posts"}</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://www.digialm.com/EForms/configuredHtml/1258/100343/login.html</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://cdn.digialm.com/EForms/configuredHtml/1258/100343/login.html</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://cdn.digialm.com//EForms/configuredHtml/1258/101323/login.html</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://dsssb.delhi.gov.in/sites/default/files/DSSSB/circulars-orders/img_0002_5.pdf</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://drive.google.com/file/d/1SYEGA_6T9KzMtuHvbwCY3OP3B08Ob8In/view</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://upsssc.gov.in/ViewPdf.aspx?QCybwYChKOaNeeAG0UpYGVP4fj1fbqKg1OI1jl4EOZk=</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://bpsc.bihar.gov.in/wp-content/uploads/BPSC_content/Notices/Advt.-No.-13-2026-Prosecution-Officer-Provisional-Answer-General-Studies_BPSC-20260812-327e8q.pdf</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://bpsc.bihar.gov.in/wp-content/uploads/BPSC_content/Notices/Advt.-No.-13-2026-Prosecution-Officer-Provisional-Answer-Law_BPSC-20260812-bcyh15.pdf</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+          <t>{"Key Status": "Official Answer Key Released", "Objection Window": "Active Online", "Total Vacancies": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://examinationservices.nic.in/ExamSys26Part2/Root/CandidateLogin.aspx?enc=Ei4cajBkK1gZSfgr53ImFTqGsyg38PlGNCGSuvSzsiVbovgbG6pVEHea7DNFe38E</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://cdnbbsr.s3waas.gov.in/s3efdf562ce2fb0ad460fd8e9d33e57f57/uploads/2026/08/202608162091350886.pdf</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2026 Post"}</t>
+          <t>{"Key Status": "Official Answer Key Released", "Objection Window": "Active Online", "Total Vacancies": "2026 Post"}</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://examinationservices.nic.in/examsys26part2/Root/CandidateLogin.aspx?enc=Ei4cajBkK1gZSfgr53ImFfGIu9Vld8UsAWKvCQaecYKgCg98d/PmJC3n7SgV5KcN</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://examinationservices.nic.in/examsys26part2/Root/CandidateLogin.aspx?enc=Ei4cajBkK1gZSfgr53ImFf+hG1eOjfHejwOCUkE3h7yiKUQgMAb21IZK1AONl+/9</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://upsssc.gov.in//ViewPdf.aspx?VFPJOCtWPZ/TOglySpHHzLl+vCZTUSqTEBEMrQXkrMA=</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://drive.google.com/file/d/16u-9curqW4ld38YtoUWiQ0ApTcRf8jvQ/view</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://upsssc.gov.in//ViewPdf.aspx?VFPJOCtWPZ937yLqytTPVKFoFPyldudAPKnuC8uARug=</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://drive.google.com/file/d/1h6HP6ON2nVejr8iHeIurVrHY85Bc0TfI/view</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://upsssc.gov.in//ViewPdf.aspx?VFPJOCtWPZ+RDYh9EqocJWkB98z/0TcvP+f1yjSkKU0=</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://drive.google.com/file/d/1Y62tk0VEv-S3sSOa4I6TRt4NFRIscpmf/view</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5476,17 +5476,17 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://cdn3.digialm.com/EForms/configuredHtml/1815/101418/login.html</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
+          <t>https://cdn3.digialm.com/EForms/configuredHtml/1815/101418/Index.html</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
           <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>https://natboard.edu.in/</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+          <t>{"Hall Ticket Status": "Available for Download", "Exam Mode": "Computer Based Test (CBT)", "Total Posts": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5571,12 +5571,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://examinationservices.nic.in/AdmitCardService/Admitcardview/Login?enc=EU2nJaTepF908NeNySmtkjs0/iPIvXk12Fg+hTlccys=</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://cdnbbsr.s3waas.gov.in/s388a839f2f6f1427879fc33ee4acf4f66/uploads/2026/08/20260818137536527.pdf</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://cdn.digialm.com/EForms/configuredHtml/1258/100936/login.html</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://cdn.digialm.com/EForms/configuredHtml/1258/100936/login.html</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2 posts"}</t>
+          <t>{"Hall Ticket Status": "Available for Download", "Exam Mode": "Computer Based Test (CBT)", "Total Posts": "2 posts"}</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://cdn.digialm.com//EForms/configuredHtml/1258/102021/login.html</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2025/09/1780670624.pdf</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://upsssc.gov.in/upssscadmitcard/admitCard.aspx?ID=MAIN</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://upsssc.gov.in/ViewPdf.aspx?2276t8n7CMo25NINJ3uar6iCD6ZGrrXCVwfI08J/tQM=</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5951,17 +5951,17 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
+          <t>https://bpssc.bihar.gov.in/Notices/Important%20notice%20for%20PET%201.pdf</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
           <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>https://bpssc.bihar.gov.in/</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "500 Posts"}</t>
+          <t>{"Hall Ticket Status": "Available for Download", "Exam Mode": "Computer Based Test (CBT)", "Total Posts": "500 Posts"}</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://ibpsreg.ibps.in/nicljul26/oecla_aug26/login.php?appid=a926805370094a107b2689a5bce28ba4</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://ibpsreg.ibps.in/nicljul26/</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "100 Posts"}</t>
+          <t>{"Hall Ticket Status": "Available for Download", "Exam Mode": "Computer Based Test (CBT)", "Total Posts": "100 Posts"}</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6141,12 +6141,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://ibtexamination.com/secuAdmitcard/bsnlAdmitcard05/</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://bsnlregistration.ibtexamination.com/PDF/EXAMINATION%20DATE%20DR%20JTO%20T.pdf</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "1035 posts"}</t>
+          <t>{"Hall Ticket Status": "Available for Download", "Exam Mode": "Computer Based Test (CBT)", "Total Posts": "1035 posts"}</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6236,17 +6236,17 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://ibpsreg.ibps.in/crpspxvimy26/oecla_aug26/login.php?appid=b4efe9284e9d84a16019c7ca6ca9547b</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
+          <t>https://ibpsreg.ibps.in/crpspxvimy26/</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
           <t>https://studytopper.in/</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>https://www.ibps.in/</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://rrb.digialm.com/EForms/configuredHtml/33128/101714/login.html</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://rrb.digialm.com/EForms/configuredHtml/33128/101714/login.html</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "259 Post"}</t>
+          <t>{"Result Status": "Declared Online", "Score Card Status": "Active for Download", "Evaluation Mode": "Computer Based Test (CBT)", "Total Candidates": "259 Post"}</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://rssb.rajasthan.gov.in/results</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://rssb.rajasthan.gov.in/storage/answerkey_item/1784526744.pdf</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://ssc.gov.in/api/attachment/uploads/masterData/Results/ROLL_17082026.pdf</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://ssc.gov.in/api/attachment/uploads/masterData/NoticeBoards/FRTA_CHSLE_2025_17082026.pdf</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://rpsc.rajasthan.gov.in/results</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://recruitment.rajasthan.gov.in/postdetailgetadmitcardservlet</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://examinationservices.nic.in/recsys2025/root/CandidateLogin.aspx?enc=Ei4cajBkK1gZSfgr53ImFbEsl0hvvhEEwgxfU0IzC28jtU4yhpqb3pomlo4g+VC8</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://www.cbse.gov.in/cbsenew/documents/PressNote_07082026.pdf</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years.", "Maximum Age": "27 Years. (BC, EBC Male)", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
+          <t>{"Age Criteria": "As per official examination / admission rules", "Eligibility Requirement": "Candidate must meet prescribed educational guidelines", "Minimum Age": "18 Years.", "Maximum Age": "27 Years. (BC, EBC Male)"}</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "83 Posts"}</t>
+          <t>{"Result Status": "Declared Online", "Score Card Status": "Active for Download", "Evaluation Mode": "Computer Based Test (CBT)", "Total Candidates": "83 Posts"}</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://csbc.bihar.gov.in/Advt/Results-01-2026-PST-18-08-2026.pdf</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://apply-csbc.com/csbc_12026_weadmitcard/searchApplication</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years.", "Maximum Age": "27 Years. (BC, EBC Male)", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
+          <t>{"Age Criteria": "As per official examination / admission rules", "Eligibility Requirement": "Candidate must meet prescribed educational guidelines", "Minimum Age": "18 Years.", "Maximum Age": "27 Years. (BC, EBC Male)"}</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "993 Posts"}</t>
+          <t>{"Result Status": "Declared Online", "Score Card Status": "Active for Download", "Evaluation Mode": "Computer Based Test (CBT)", "Total Candidates": "993 Posts"}</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://csbc.bihar.gov.in/Advt/Results-02-2026-PET-18-08-2026.pdf</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://apply-csbc.com/csbc_2_2026_weadmitcards/applicationIndex</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
+          <t>{"Age Criteria": "As per official examination / admission rules", "Eligibility Requirement": "Candidate must meet prescribed educational guidelines"}</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://csbc.bihar.gov.in/Advt/Results-03-2025-PET-18-08-2026.pdf</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://apply-csbc.com/csbc_032025_we_admitcards/searchApplication</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
+          <t>{"Age Criteria": "As per official examination / admission rules", "Eligibility Requirement": "Candidate must meet prescribed educational guidelines"}</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+          <t>{"Result Status": "Declared Online", "Score Card Status": "Active for Download", "Evaluation Mode": "Computer Based Test (CBT)", "Total Candidates": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -7091,12 +7091,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://cnr.nic.in/Results26/SWAYAM/Login?apprefno=101562612</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://exams.nta.nic.in/swayan/</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://rpsc.rajasthan.gov.in/Static/Result/E8BDC9265C2B4202BE9C2DBEB2830182.pdf</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://rpsc.rajasthan.gov.in/Static/Result/414E033DC2E345BFA73CEF19C7649CF4.pdf</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>{"Minimum Age": "18 Years", "Maximum Age": "40 Years", "Age Calculated As On": "01 August 2026", "Age Relaxation": "Extra as per official recruitment rules"}</t>
+          <t>{"Age Criteria": "As per official examination / admission rules", "Eligibility Requirement": "Candidate must meet prescribed educational guidelines"}</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+          <t>{"Admission Session": "2026-2027", "Target Programs": "Undergraduate / Postgraduate Courses", "Total Seats": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7281,12 +7281,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://whatsapp.com/channel/0029VaAbQf01NCrYADMLt00L</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>http://sarkariresult.com.cm/wp-content/uploads/2026/08/IIT-JAM-2027-Short-Notice.pdf</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>{"General (UR)": "As per Rules", "OBC / EWS": "As per Rules", "SC / ST": "As per Rules", "Total Vacancies": "2482 Posts"}</t>
+          <t>{"Admission Session": "2026-2027", "Target Programs": "Undergraduate / Postgraduate Courses", "Total Seats": "2482 Posts"}</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>#content</t>
+          <t>https://clat2027.consortiumofnlus.ac.in/clat-2027/</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>https://studytopper.in/</t>
+          <t>https://consortiumofnlus.ac.in/clat-2026/nlus/brochure/NLSIU.pdf</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
